--- a/site/data/florida-open-bids.xlsx
+++ b/site/data/florida-open-bids.xlsx
@@ -2050,7 +2050,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -12098,7 +12098,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
@@ -13792,7 +13792,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -16288,7 +16288,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -17940,7 +17940,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Concessions &amp; Programs</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -20566,7 +20566,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -21930,7 +21930,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
@@ -22034,7 +22034,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -22090,7 +22090,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -22202,7 +22202,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Notices &amp; Events</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
@@ -22308,7 +22308,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -22364,7 +22364,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Concessions &amp; Programs</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -25084,7 +25084,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -27376,7 +27376,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
@@ -27532,7 +27532,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Concessions &amp; Programs</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
@@ -27792,7 +27792,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -27888,7 +27888,7 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -27934,7 +27934,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -28030,7 +28030,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -28264,7 +28264,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -28448,7 +28448,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -29735,7 +29735,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 2026-10-24 09:42 PM (Eastern time)</t>
+          <t>Updated 2026-10-24 09:51 PM (Eastern time)</t>
         </is>
       </c>
     </row>

--- a/site/data/florida-open-bids.xlsx
+++ b/site/data/florida-open-bids.xlsx
@@ -29735,7 +29735,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 2026-10-24 09:51 PM (Eastern time)</t>
+          <t>Updated 2026-10-24 10:52 PM (Eastern time)</t>
         </is>
       </c>
     </row>

--- a/site/data/florida-open-bids.xlsx
+++ b/site/data/florida-open-bids.xlsx
@@ -29735,7 +29735,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 2026-10-24 10:52 PM (Eastern time)</t>
+          <t>Updated 2026-10-25 12:23 AM (Eastern time)</t>
         </is>
       </c>
     </row>

--- a/site/data/florida-open-bids.xlsx
+++ b/site/data/florida-open-bids.xlsx
@@ -29735,7 +29735,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 2026-10-25 12:23 AM (Eastern time)</t>
+          <t>Updated 2026-10-25 12:24 AM (Eastern time)</t>
         </is>
       </c>
     </row>

--- a/site/data/florida-open-bids.xlsx
+++ b/site/data/florida-open-bids.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Open solicitations'!$A$1:$L$539</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Open solicitations'!$A$1:$L$582</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L539"/>
+  <dimension ref="A1:L582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21960,110 +21960,104 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Volusia</t>
+          <t>St. Lucie</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Volusia County</t>
+          <t>St. Lucie County BOCC</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>27-B-08LB</t>
+          <t>BID-27-011-0-2027/DC</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>London Foggers Truck-Mounted Generators</t>
+          <t>MLB Stadium (Clover Park) Concrete Traffic Coating</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H410" s="3" t="n">
         <v>46344</v>
       </c>
       <c r="I410" s="3" t="n">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="J410" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/volusia</t>
+          <t>https://www.demandstar.com/app/limited/bids/554954/details</t>
         </is>
       </c>
       <c r="K410" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/volusia</t>
-        </is>
-      </c>
-      <c r="L410" t="inlineStr">
-        <is>
-          <t>Added by one-time backfill.</t>
-        </is>
-      </c>
+          <t>https://www.demandstar.com/app/agencies/florida/st-lucie-county-purchasing-department/procurement-opportunities/dba839e8-c1f1-4ea4-8e46-57cbc2d9aad2</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Volusia</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Charlotte County BOCC</t>
+          <t>Volusia County</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>26-640</t>
+          <t>27-B-08LB</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>Boca Grande Fishing Pier Recovery Repairs</t>
+          <t>London Foggers Truck-Mounted Generators</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>Bid</t>
-        </is>
-      </c>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr"/>
       <c r="G411" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="H411" s="5" t="n">
-        <v>46344.58333333334</v>
-      </c>
-      <c r="I411" s="3" t="inlineStr"/>
+      <c r="H411" s="3" t="n">
+        <v>46344</v>
+      </c>
+      <c r="I411" s="3" t="n">
+        <v>46316</v>
+      </c>
       <c r="J411" s="4" t="inlineStr">
         <is>
-          <t>https://purchasingbids.charlottecountyfl.gov/ContractsCatalogs/ShowDoc/266403?tp=D</t>
+          <t>https://procurement.opengov.com/portal/volusia</t>
         </is>
       </c>
       <c r="K411" s="4" t="inlineStr">
         <is>
-          <t>https://purchasingbids.charlottecountyfl.gov/ContractsCatalogs</t>
+          <t>https://procurement.opengov.com/portal/volusia</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>Contact: Michael.Gallagher@charlottecountyfl.gov</t>
+          <t>Added by one-time backfill.</t>
         </is>
       </c>
     </row>
@@ -22080,17 +22074,17 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>27-023</t>
+          <t>26-640</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>Utilities Print-Ready Customer Bills, Notices, and Envelopes - Annual Contract</t>
+          <t>Boca Grande Fishing Pier Recovery Repairs</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -22109,7 +22103,7 @@
       <c r="I412" s="3" t="inlineStr"/>
       <c r="J412" s="4" t="inlineStr">
         <is>
-          <t>https://purchasingbids.charlottecountyfl.gov/ContractsCatalogs/ShowDoc/270233?tp=D</t>
+          <t>https://purchasingbids.charlottecountyfl.gov/ContractsCatalogs/ShowDoc/266403?tp=D</t>
         </is>
       </c>
       <c r="K412" s="4" t="inlineStr">
@@ -22119,39 +22113,39 @@
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>Contact: Krista.Vigne@CharlotteCountyFl.gov</t>
+          <t>Contact: Michael.Gallagher@charlottecountyfl.gov</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Hillsborough County BOCC</t>
+          <t>Charlotte County BOCC</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>IFB-26-00406</t>
+          <t>27-023</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>Valrico Reclaimed Water Facility Diesel Generator Project</t>
+          <t>Utilities Print-Ready Customer Bills, Notices, and Envelopes - Annual Contract</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
@@ -22165,49 +22159,49 @@
       <c r="I413" s="3" t="inlineStr"/>
       <c r="J413" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://purchasingbids.charlottecountyfl.gov/ContractsCatalogs/ShowDoc/270233?tp=D</t>
         </is>
       </c>
       <c r="K413" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://purchasingbids.charlottecountyfl.gov/ContractsCatalogs</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>Added by one-time backfill.</t>
+          <t>Contact: Krista.Vigne@CharlotteCountyFl.gov</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>EVN0037412</t>
+          <t>IFB-26-00406</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>Notice of Intent to Extend Pool No. RTQ-01954</t>
+          <t>Valrico Reclaimed Water Facility Diesel Generator Project</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Notices &amp; Events</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>Notice</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
@@ -22218,48 +22212,54 @@
       <c r="H414" s="5" t="n">
         <v>46344.58333333334</v>
       </c>
-      <c r="I414" s="3" t="n">
-        <v>46314</v>
-      </c>
-      <c r="J414" t="inlineStr"/>
+      <c r="I414" s="3" t="inlineStr"/>
+      <c r="J414" s="4" t="inlineStr">
+        <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
       <c r="K414" s="4" t="inlineStr">
         <is>
-          <t>https://supplier.miamidade.gov/psc/EXTSUPP/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_BID_CMP_FL.GBL</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>Find event EVN0037412 on the INFORMS public bidding page.</t>
+          <t>Added by one-time backfill.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Palm Beach</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Solid Waste Authority of Palm Beach County</t>
+          <t>Miami-Dade County</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>RFEI 27-501/JH</t>
+          <t>EVN0037412</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>Request for Expressions of Interest for Demolition, Design, Build, Operation and Maintenance of a New Mass-Burn Waste to Energy Facility</t>
+          <t>Notice of Intent to Extend Pool No. RTQ-01954</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F415" t="inlineStr"/>
+          <t>Notices &amp; Events</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Notice</t>
+        </is>
+      </c>
       <c r="G415" t="inlineStr">
         <is>
           <t>Open</t>
@@ -22268,214 +22268,206 @@
       <c r="H415" s="5" t="n">
         <v>46344.58333333334</v>
       </c>
-      <c r="I415" s="3" t="inlineStr"/>
-      <c r="J415" s="4" t="inlineStr">
-        <is>
-          <t>https://swa.bonfirehub.com/portal/?tab=openOpportunities</t>
-        </is>
-      </c>
+      <c r="I415" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="J415" t="inlineStr"/>
       <c r="K415" s="4" t="inlineStr">
         <is>
-          <t>https://swa.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://supplier.miamidade.gov/psc/EXTSUPP/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_BID_CMP_FL.GBL</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>Added by one-time backfill.</t>
+          <t>Find event EVN0037412 on the INFORMS public bidding page.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Palm Beach</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Charlotte County BOCC</t>
+          <t>Solid Waste Authority of Palm Beach County</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>26-690</t>
+          <t>RFEI 27-501/JH</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>Design - Charlotte County Sheriff's Office District 2 Headquarters</t>
+          <t>Request for Expressions of Interest for Demolition, Design, Build, Operation and Maintenance of a New Mass-Burn Waste to Energy Facility</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
-        </is>
-      </c>
-      <c r="F416" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr"/>
       <c r="G416" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
-        <v>46344.625</v>
+        <v>46344.58333333334</v>
       </c>
       <c r="I416" s="3" t="inlineStr"/>
       <c r="J416" s="4" t="inlineStr">
         <is>
-          <t>https://purchasingbids.charlottecountyfl.gov/ContractsCatalogs/ShowDoc/266903?tp=D</t>
+          <t>https://swa.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="K416" s="4" t="inlineStr">
         <is>
-          <t>https://purchasingbids.charlottecountyfl.gov/ContractsCatalogs</t>
+          <t>https://swa.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>Contact: Kimberly.Chamberlain@charlottecountyfl.gov</t>
+          <t>Added by one-time backfill.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Duval</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Duval County Public Schools</t>
+          <t>Charlotte County BOCC</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>RFP-08-0-2027/DMB</t>
+          <t>26-690</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>Student Transportation Services GSA 4</t>
+          <t>Design - Charlotte County Sheriff's Office District 2 Headquarters</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Concessions &amp; Programs</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>RFP</t>
+          <t>Proposal</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H417" s="3" t="n">
-        <v>46345</v>
-      </c>
-      <c r="I417" s="3" t="n">
-        <v>46311</v>
-      </c>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H417" s="5" t="n">
+        <v>46344.625</v>
+      </c>
+      <c r="I417" s="3" t="inlineStr"/>
       <c r="J417" s="4" t="inlineStr">
         <is>
-          <t>https://www.demandstar.com/app/limited/bids/554369/details</t>
+          <t>https://purchasingbids.charlottecountyfl.gov/ContractsCatalogs/ShowDoc/266903?tp=D</t>
         </is>
       </c>
       <c r="K417" s="4" t="inlineStr">
         <is>
-          <t>https://www.demandstar.com/app/agencies/florida/duval-county-public-schools-purchasing-services/procurement-opportunities/70ee73c4-883b-4d02-adf7-859f473fd9e1</t>
-        </is>
-      </c>
-      <c r="L417" t="inlineStr"/>
+          <t>https://purchasingbids.charlottecountyfl.gov/ContractsCatalogs</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Contact: Kimberly.Chamberlain@charlottecountyfl.gov</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Duval</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>City of Plant City</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr"/>
+          <t>Duval County Public Schools</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>RFP-08-0-2027/DMB</t>
+        </is>
+      </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>Lift Station Communication Improvement (FEMA)</t>
+          <t>Student Transportation Services GSA 4</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F418" t="inlineStr"/>
+          <t>Concessions &amp; Programs</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>RFP</t>
+        </is>
+      </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H418" s="3" t="n">
         <v>46345</v>
       </c>
       <c r="I418" s="3" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="J418" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/plantcitygov</t>
+          <t>https://www.demandstar.com/app/limited/bids/554369/details</t>
         </is>
       </c>
       <c r="K418" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/plantcitygov</t>
-        </is>
-      </c>
-      <c r="L418" t="inlineStr">
-        <is>
-          <t>Added by one-time backfill.</t>
-        </is>
-      </c>
+          <t>https://www.demandstar.com/app/agencies/florida/duval-county-public-schools-purchasing-services/procurement-opportunities/70ee73c4-883b-4d02-adf7-859f473fd9e1</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>City of Clermont</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>RFB 27-016</t>
-        </is>
-      </c>
+          <t>City of Plant City</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr"/>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>Purchase of Sixteen (16) Handheld Lidar Speed Detection Devices</t>
+          <t>Lift Station Communication Improvement (FEMA)</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>ITB</t>
-        </is>
-      </c>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
       <c r="G419" t="inlineStr">
         <is>
           <t>Open</t>
@@ -22485,16 +22477,16 @@
         <v>46345</v>
       </c>
       <c r="I419" s="3" t="n">
-        <v>46315</v>
+        <v>46310</v>
       </c>
       <c r="J419" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/clermontfl</t>
+          <t>https://procurement.opengov.com/portal/plantcitygov</t>
         </is>
       </c>
       <c r="K419" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/clermontfl</t>
+          <t>https://procurement.opengov.com/portal/plantcitygov</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
@@ -22506,23 +22498,27 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Monroe</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Monroe County School District</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr"/>
+          <t>City of Clermont</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>RFB 27-016</t>
+        </is>
+      </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>ITB 2026023 - AC Repairs and Replacements</t>
+          <t>Purchase of Sixteen (16) Handheld Lidar Speed Detection Devices</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -22539,16 +22535,16 @@
         <v>46345</v>
       </c>
       <c r="I420" s="3" t="n">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="J420" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/keyschools-mcsd</t>
+          <t>https://procurement.opengov.com/portal/clermontfl</t>
         </is>
       </c>
       <c r="K420" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/keyschools-mcsd</t>
+          <t>https://procurement.opengov.com/portal/clermontfl</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
@@ -22560,26 +22556,30 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Monroe</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>City of Orlando</t>
+          <t>Monroe County School District</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>Virginia Dr., Forest Dr., and Corrine Dr., Complete Streets Project</t>
+          <t>ITB 2026023 - AC Repairs and Replacements</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr"/>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>ITB</t>
+        </is>
+      </c>
       <c r="G421" t="inlineStr">
         <is>
           <t>Open</t>
@@ -22589,16 +22589,16 @@
         <v>46345</v>
       </c>
       <c r="I421" s="3" t="n">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="J421" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/orlando</t>
+          <t>https://procurement.opengov.com/portal/keyschools-mcsd</t>
         </is>
       </c>
       <c r="K421" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/orlando</t>
+          <t>https://procurement.opengov.com/portal/keyschools-mcsd</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
@@ -22610,27 +22610,23 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Osceola</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>City of St. Cloud</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>2026-142</t>
-        </is>
-      </c>
+          <t>City of Orlando</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr"/>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>Custodial Services</t>
+          <t>Virginia Dr., Forest Dr., and Corrine Dr., Complete Streets Project</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F422" t="inlineStr"/>
@@ -22643,16 +22639,16 @@
         <v>46345</v>
       </c>
       <c r="I422" s="3" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="J422" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/stcloud</t>
+          <t>https://procurement.opengov.com/portal/orlando</t>
         </is>
       </c>
       <c r="K422" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/stcloud</t>
+          <t>https://procurement.opengov.com/portal/orlando</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
@@ -22664,22 +22660,22 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Palm Beach</t>
+          <t>Osceola</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>City of Greenacres</t>
+          <t>City of St. Cloud</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Bid-27-001-0-2026/RW</t>
+          <t>2026-142</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>Fence Installation, Maintenance and Repair Services</t>
+          <t>Custodial Services</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -22690,26 +22686,30 @@
       <c r="F423" t="inlineStr"/>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H423" s="3" t="n">
         <v>46345</v>
       </c>
       <c r="I423" s="3" t="n">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="J423" s="4" t="inlineStr">
         <is>
-          <t>https://www.demandstar.com/app/limited/bids/554467/details</t>
+          <t>https://procurement.opengov.com/portal/stcloud</t>
         </is>
       </c>
       <c r="K423" s="4" t="inlineStr">
         <is>
-          <t>https://www.demandstar.com/app/agencies/florida/city-of-greenacres/procurement-opportunities/63133434-ac0d-48fb-84cb-d1289ae4b212/</t>
-        </is>
-      </c>
-      <c r="L423" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/stcloud</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Added by one-time backfill.</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -22724,17 +22724,17 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Bid-27-003-0-2026/RW</t>
+          <t>Bid-27-001-0-2026/RW</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>Parks Court Resurfacing</t>
+          <t>Fence Installation, Maintenance and Repair Services</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F424" t="inlineStr"/>
@@ -22751,7 +22751,7 @@
       </c>
       <c r="J424" s="4" t="inlineStr">
         <is>
-          <t>https://www.demandstar.com/app/limited/bids/554470/details</t>
+          <t>https://www.demandstar.com/app/limited/bids/554467/details</t>
         </is>
       </c>
       <c r="K424" s="4" t="inlineStr">
@@ -22774,17 +22774,17 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Bid-27-002-0-2026/RW</t>
+          <t>Bid-27-003-0-2026/RW</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>Printing Services for City Publications</t>
+          <t>Parks Court Resurfacing</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
@@ -22801,7 +22801,7 @@
       </c>
       <c r="J425" s="4" t="inlineStr">
         <is>
-          <t>https://www.demandstar.com/app/limited/bids/554468/details</t>
+          <t>https://www.demandstar.com/app/limited/bids/554470/details</t>
         </is>
       </c>
       <c r="K425" s="4" t="inlineStr">
@@ -22814,18 +22814,22 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Pinellas</t>
+          <t>Palm Beach</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>City of St. Petersburg</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr"/>
+          <t>City of Greenacres</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Bid-27-002-0-2026/RW</t>
+        </is>
+      </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>Chemical, 50% Sodium Hydroxide (Caustic Soda)</t>
+          <t>Printing Services for City Publications</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -22836,51 +22840,47 @@
       <c r="F426" t="inlineStr"/>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H426" s="3" t="n">
         <v>46345</v>
       </c>
       <c r="I426" s="3" t="n">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="J426" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/stpete</t>
+          <t>https://www.demandstar.com/app/limited/bids/554468/details</t>
         </is>
       </c>
       <c r="K426" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/stpete</t>
-        </is>
-      </c>
-      <c r="L426" t="inlineStr">
-        <is>
-          <t>Added by one-time backfill.</t>
-        </is>
-      </c>
+          <t>https://www.demandstar.com/app/agencies/florida/city-of-greenacres/procurement-opportunities/63133434-ac0d-48fb-84cb-d1289ae4b212/</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Sarasota</t>
+          <t>Pinellas</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Sarasota County BOCC</t>
+          <t>City of St. Petersburg</t>
         </is>
       </c>
       <c r="C427" t="inlineStr"/>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>Physical Map Revision for Little Sarasota Bay, Lemon Bay, and Phillippi Creek Watersheds</t>
+          <t>Chemical, 50% Sodium Hydroxide (Caustic Soda)</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F427" t="inlineStr"/>
@@ -22893,16 +22893,16 @@
         <v>46345</v>
       </c>
       <c r="I427" s="3" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="J427" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/scgov</t>
+          <t>https://procurement.opengov.com/portal/stpete</t>
         </is>
       </c>
       <c r="K427" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/scgov</t>
+          <t>https://procurement.opengov.com/portal/stpete</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
@@ -22914,27 +22914,23 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>St. Lucie</t>
+          <t>Sarasota</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>City of Port St. Lucie</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>20260277</t>
-        </is>
-      </c>
+          <t>Sarasota County BOCC</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr"/>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>Emergency Catering Services</t>
+          <t>Physical Map Revision for Little Sarasota Bay, Lemon Bay, and Phillippi Creek Watersheds</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Concessions &amp; Programs</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F428" t="inlineStr"/>
@@ -22947,16 +22943,16 @@
         <v>46345</v>
       </c>
       <c r="I428" s="3" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="J428" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/cityofpsl</t>
+          <t>https://procurement.opengov.com/portal/scgov</t>
         </is>
       </c>
       <c r="K428" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/cityofpsl</t>
+          <t>https://procurement.opengov.com/portal/scgov</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
@@ -22968,27 +22964,27 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Volusia</t>
+          <t>St. Lucie</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>City of Daytona Beach</t>
+          <t>City of Port St. Lucie</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>2709ITB</t>
+          <t>20260277</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>2709ITB - Citywide Banner Printing &amp; Fabrication</t>
+          <t>Emergency Catering Services</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Concessions &amp; Programs</t>
         </is>
       </c>
       <c r="F429" t="inlineStr"/>
@@ -23001,16 +22997,16 @@
         <v>46345</v>
       </c>
       <c r="I429" s="3" t="n">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="J429" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/codb</t>
+          <t>https://procurement.opengov.com/portal/cityofpsl</t>
         </is>
       </c>
       <c r="K429" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/codb</t>
+          <t>https://procurement.opengov.com/portal/cityofpsl</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
@@ -23022,27 +23018,27 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Broward</t>
+          <t>Volusia</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>City of Margate</t>
+          <t>City of Daytona Beach</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>2026-006</t>
+          <t>2709ITB</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>2026-006 BID Winfield Blvd Pedestrian Sidewalk and Bridge</t>
+          <t>2709ITB - Citywide Banner Printing &amp; Fabrication</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F430" t="inlineStr"/>
@@ -23051,21 +23047,27 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="H430" s="5" t="n">
-        <v>46345.45833333334</v>
-      </c>
-      <c r="I430" s="3" t="inlineStr"/>
+      <c r="H430" s="3" t="n">
+        <v>46345</v>
+      </c>
+      <c r="I430" s="3" t="n">
+        <v>46317</v>
+      </c>
       <c r="J430" s="4" t="inlineStr">
         <is>
-          <t>https://www.margatefl.com/bids.aspx?bidID=142</t>
+          <t>https://procurement.opengov.com/portal/codb</t>
         </is>
       </c>
       <c r="K430" s="4" t="inlineStr">
         <is>
-          <t>https://www.margatefl.com/bids.aspx</t>
-        </is>
-      </c>
-      <c r="L430" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/codb</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Added by one-time backfill.</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -23075,22 +23077,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Broward County BOCC</t>
+          <t>City of Margate</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>GEN2132533P1</t>
+          <t>2026-006</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>External Audit Services</t>
+          <t>2026-006 BID Winfield Blvd Pedestrian Sidewalk and Bridge</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F431" t="inlineStr"/>
@@ -23100,49 +23102,45 @@
         </is>
       </c>
       <c r="H431" s="5" t="n">
-        <v>46345.58333333334</v>
+        <v>46345.45833333334</v>
       </c>
       <c r="I431" s="3" t="inlineStr"/>
       <c r="J431" s="4" t="inlineStr">
         <is>
-          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://www.margatefl.com/bids.aspx?bidID=142</t>
         </is>
       </c>
       <c r="K431" s="4" t="inlineStr">
         <is>
-          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
-        </is>
-      </c>
-      <c r="L431" t="inlineStr">
-        <is>
-          <t>Added by one-time backfill.</t>
-        </is>
-      </c>
+          <t>https://www.margatefl.com/bids.aspx</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>University of Central Florida</t>
+          <t>Broward County BOCC</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Fire Alarm Contractors Continuing Services</t>
+          <t>GEN2132533P1</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>Fire Alarm Contractors Continuing Services</t>
+          <t>External Audit Services</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -23152,17 +23150,17 @@
         </is>
       </c>
       <c r="H432" s="5" t="n">
-        <v>46345.70833333334</v>
+        <v>46345.58333333334</v>
       </c>
       <c r="I432" s="3" t="inlineStr"/>
       <c r="J432" s="4" t="inlineStr">
         <is>
-          <t>https://ucf.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="K432" s="4" t="inlineStr">
         <is>
-          <t>https://ucf.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
@@ -23174,23 +23172,27 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Pinellas</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>City of Clearwater</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr"/>
+          <t>University of Central Florida</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Fire Alarm Contractors Continuing Services</t>
+        </is>
+      </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>Athletic Field Sod Material &amp; Installation</t>
+          <t>Fire Alarm Contractors Continuing Services</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
@@ -23199,20 +23201,18 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="H433" s="3" t="n">
-        <v>46346</v>
-      </c>
-      <c r="I433" s="3" t="n">
-        <v>46316</v>
-      </c>
+      <c r="H433" s="5" t="n">
+        <v>46345.70833333334</v>
+      </c>
+      <c r="I433" s="3" t="inlineStr"/>
       <c r="J433" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/myclearwater</t>
+          <t>https://ucf.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="K433" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/myclearwater</t>
+          <t>https://ucf.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
@@ -23224,30 +23224,26 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Pinellas</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>City of Winter Haven</t>
+          <t>City of Clearwater</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>RFQ-27-02 Design Build Services for Sertoma Park Football Renovations</t>
+          <t>Athletic Field Sod Material &amp; Installation</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>Quote</t>
-        </is>
-      </c>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr">
         <is>
           <t>Open</t>
@@ -23261,12 +23257,12 @@
       </c>
       <c r="J434" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/winterhavenfl</t>
+          <t>https://procurement.opengov.com/portal/myclearwater</t>
         </is>
       </c>
       <c r="K434" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/winterhavenfl</t>
+          <t>https://procurement.opengov.com/portal/myclearwater</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
@@ -23283,21 +23279,25 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>City of Lakeland</t>
+          <t>City of Winter Haven</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>Rose St Streetscape Improvements</t>
+          <t>RFQ-27-02 Design Build Services for Sertoma Park Football Renovations</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr"/>
+          <t>Engineering &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
       <c r="G435" t="inlineStr">
         <is>
           <t>Open</t>
@@ -23307,16 +23307,16 @@
         <v>46346</v>
       </c>
       <c r="I435" s="3" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="J435" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/lakelandgov</t>
+          <t>https://procurement.opengov.com/portal/winterhavenfl</t>
         </is>
       </c>
       <c r="K435" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/lakelandgov</t>
+          <t>https://procurement.opengov.com/portal/winterhavenfl</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
@@ -23328,23 +23328,23 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Santa Rosa</t>
+          <t>Polk</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Santa Rosa County BOCC</t>
+          <t>City of Lakeland</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>Sale and Master Planning of County-Owned Property on Berryhill Road</t>
+          <t>Rose St Streetscape Improvements</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -23357,16 +23357,16 @@
         <v>46346</v>
       </c>
       <c r="I436" s="3" t="n">
-        <v>46097</v>
+        <v>46315</v>
       </c>
       <c r="J436" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/santarosafl</t>
+          <t>https://procurement.opengov.com/portal/lakelandgov</t>
         </is>
       </c>
       <c r="K436" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/santarosafl</t>
+          <t>https://procurement.opengov.com/portal/lakelandgov</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
@@ -23378,27 +23378,23 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>St. Lucie</t>
+          <t>Santa Rosa</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>City of Port St. Lucie</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>20270001</t>
-        </is>
-      </c>
+          <t>Santa Rosa County BOCC</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr"/>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>Federal Legislative Advocacy Services</t>
+          <t>Sale and Master Planning of County-Owned Property on Berryhill Road</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -23411,16 +23407,16 @@
         <v>46346</v>
       </c>
       <c r="I437" s="3" t="n">
-        <v>46314</v>
+        <v>46097</v>
       </c>
       <c r="J437" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/cityofpsl</t>
+          <t>https://procurement.opengov.com/portal/santarosafl</t>
         </is>
       </c>
       <c r="K437" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/cityofpsl</t>
+          <t>https://procurement.opengov.com/portal/santarosafl</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
@@ -23442,17 +23438,17 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>20260170</t>
+          <t>20270001</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>Pressure Cleaning Services</t>
+          <t>Federal Legislative Advocacy Services</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -23465,7 +23461,7 @@
         <v>46346</v>
       </c>
       <c r="I438" s="3" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="J438" s="4" t="inlineStr">
         <is>
@@ -23486,22 +23482,22 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Broward</t>
+          <t>St. Lucie</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Broward County BOCC</t>
+          <t>City of Port St. Lucie</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>PNC2132739C1</t>
+          <t>20260170</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>Broward County Judicial Court West Tower Repairs</t>
+          <t>Pressure Cleaning Services</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -23515,18 +23511,20 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="H439" s="5" t="n">
-        <v>46346.58333333334</v>
-      </c>
-      <c r="I439" s="3" t="inlineStr"/>
+      <c r="H439" s="3" t="n">
+        <v>46346</v>
+      </c>
+      <c r="I439" s="3" t="n">
+        <v>46315</v>
+      </c>
       <c r="J439" s="4" t="inlineStr">
         <is>
-          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://procurement.opengov.com/portal/cityofpsl</t>
         </is>
       </c>
       <c r="K439" s="4" t="inlineStr">
         <is>
-          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://procurement.opengov.com/portal/cityofpsl</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
@@ -23538,27 +23536,27 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
+          <t>Broward County BOCC</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>ITB0000025</t>
+          <t>PNC2132739C1</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>Body Bags and Evidence Bags</t>
+          <t>Broward County Judicial Court West Tower Repairs</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -23570,108 +23568,102 @@
       <c r="H440" s="5" t="n">
         <v>46346.58333333334</v>
       </c>
-      <c r="I440" s="3" t="n">
-        <v>46316</v>
-      </c>
-      <c r="J440" t="inlineStr"/>
+      <c r="I440" s="3" t="inlineStr"/>
+      <c r="J440" s="4" t="inlineStr">
+        <is>
+          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
       <c r="K440" s="4" t="inlineStr">
         <is>
-          <t>https://supplier.miamidade.gov/psc/EXTSUPP/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_BID_CMP_FL.GBL</t>
+          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>Find event ITB0000025 on the INFORMS public bidding page.</t>
+          <t>Added by one-time backfill.</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Alachua</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Gainesville Regional Utilities</t>
+          <t>Miami-Dade County</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>ITB-E 2027-011</t>
+          <t>ITB0000025</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>SCAFFOLDING SERVICES</t>
+          <t>Body Bags and Evidence Bags</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>ITB</t>
-        </is>
-      </c>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr"/>
       <c r="G441" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="H441" s="3" t="n">
-        <v>46349</v>
+      <c r="H441" s="5" t="n">
+        <v>46346.58333333334</v>
       </c>
       <c r="I441" s="3" t="n">
-        <v>46317</v>
-      </c>
-      <c r="J441" s="4" t="inlineStr">
-        <is>
-          <t>https://procurement.opengov.com/portal/gru</t>
-        </is>
-      </c>
+        <v>46316</v>
+      </c>
+      <c r="J441" t="inlineStr"/>
       <c r="K441" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/gru</t>
+          <t>https://supplier.miamidade.gov/psc/EXTSUPP/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_BID_CMP_FL.GBL</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>Added by one-time backfill.</t>
+          <t>Find event ITB0000025 on the INFORMS public bidding page.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Clay</t>
+          <t>Alachua</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Clay County BOCC</t>
+          <t>Gainesville Regional Utilities</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>25/26-114</t>
+          <t>ITB-E 2027-011</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>Lease of County Owned Property at 3245 Bear Run Blvd, Orange Park, FL 32065</t>
+          <t>SCAFFOLDING SERVICES</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Property &amp; Real Estate</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Property sale / lease</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
@@ -23683,16 +23675,16 @@
         <v>46349</v>
       </c>
       <c r="I442" s="3" t="n">
-        <v>46289</v>
+        <v>46317</v>
       </c>
       <c r="J442" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/claycounty</t>
+          <t>https://procurement.opengov.com/portal/gru</t>
         </is>
       </c>
       <c r="K442" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/claycounty</t>
+          <t>https://procurement.opengov.com/portal/gru</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
@@ -23704,30 +23696,34 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Escambia</t>
+          <t>Clay</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Escambia County BOCC</t>
+          <t>Clay County BOCC</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>PD 26-27.004</t>
+          <t>25/26-114</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>CDBG-DR HS004 New Escambia County Area Transit (ECAT) Facility</t>
+          <t>Lease of County Owned Property at 3245 Bear Run Blvd, Orange Park, FL 32065</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F443" t="inlineStr"/>
+          <t>Property &amp; Real Estate</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Property sale / lease</t>
+        </is>
+      </c>
       <c r="G443" t="inlineStr">
         <is>
           <t>Open</t>
@@ -23737,16 +23733,16 @@
         <v>46349</v>
       </c>
       <c r="I443" s="3" t="n">
-        <v>46318</v>
+        <v>46289</v>
       </c>
       <c r="J443" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/escambiacountyfl</t>
+          <t>https://procurement.opengov.com/portal/claycounty</t>
         </is>
       </c>
       <c r="K443" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/escambiacountyfl</t>
+          <t>https://procurement.opengov.com/portal/claycounty</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
@@ -23758,23 +23754,27 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Escambia</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>City of Doral</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr"/>
+          <t>Escambia County BOCC</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>PD 26-27.004</t>
+        </is>
+      </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>Youth Soccer Programming at Doral Central Park</t>
+          <t>CDBG-DR HS004 New Escambia County Area Transit (ECAT) Facility</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Concessions &amp; Programs</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -23791,12 +23791,12 @@
       </c>
       <c r="J444" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/cityofdoral</t>
+          <t>https://procurement.opengov.com/portal/escambiacountyfl</t>
         </is>
       </c>
       <c r="K444" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/cityofdoral</t>
+          <t>https://procurement.opengov.com/portal/escambiacountyfl</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
@@ -23808,23 +23808,23 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>City of Orlando</t>
+          <t>City of Doral</t>
         </is>
       </c>
       <c r="C445" t="inlineStr"/>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>Grounds Maintenance for City Easements, Right-of-Ways and Brick Streets</t>
+          <t>Youth Soccer Programming at Doral Central Park</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Concessions &amp; Programs</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -23837,16 +23837,16 @@
         <v>46349</v>
       </c>
       <c r="I445" s="3" t="n">
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="J445" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/orlando</t>
+          <t>https://procurement.opengov.com/portal/cityofdoral</t>
         </is>
       </c>
       <c r="K445" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/orlando</t>
+          <t>https://procurement.opengov.com/portal/cityofdoral</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
@@ -23858,34 +23858,26 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Seminole</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Orlando Sanford International Airport</t>
-        </is>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>2027-006-RFP</t>
-        </is>
-      </c>
+          <t>City of Orlando</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr"/>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>Airport Digital Twin Platform Implementation and Support Services</t>
+          <t>Grounds Maintenance for City Easements, Right-of-Ways and Brick Streets</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>IT &amp; Technology</t>
-        </is>
-      </c>
-      <c r="F446" t="inlineStr">
-        <is>
-          <t>RFP</t>
-        </is>
-      </c>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr"/>
       <c r="G446" t="inlineStr">
         <is>
           <t>Open</t>
@@ -23895,16 +23887,16 @@
         <v>46349</v>
       </c>
       <c r="I446" s="3" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="J446" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/flysfb</t>
+          <t>https://procurement.opengov.com/portal/orlando</t>
         </is>
       </c>
       <c r="K446" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/flysfb</t>
+          <t>https://procurement.opengov.com/portal/orlando</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
@@ -23916,27 +23908,27 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Palm Beach</t>
+          <t>Seminole</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>City of Boca Raton</t>
+          <t>Orlando Sanford International Airport</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2026-015-VG</t>
+          <t>2027-006-RFP</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>Installation and/or Replacement of Potable and/or Reclaimed Water Meters with AMI Transponders (Addendum 1)</t>
+          <t>Airport Digital Twin Platform Implementation and Support Services</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -23949,16 +23941,20 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="H447" s="5" t="n">
-        <v>46349.625</v>
+      <c r="H447" s="3" t="n">
+        <v>46349</v>
       </c>
       <c r="I447" s="3" t="n">
-        <v>46315</v>
-      </c>
-      <c r="J447" t="inlineStr"/>
+        <v>46317</v>
+      </c>
+      <c r="J447" s="4" t="inlineStr">
+        <is>
+          <t>https://procurement.opengov.com/portal/flysfb</t>
+        </is>
+      </c>
       <c r="K447" s="4" t="inlineStr">
         <is>
-          <t>https://brpurch.ionwave.net/SourcingEvents.aspx?SourceType=1</t>
+          <t>https://procurement.opengov.com/portal/flysfb</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
@@ -23970,22 +23966,22 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Citrus</t>
+          <t>Palm Beach</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Citrus County BOCC</t>
+          <t>City of Boca Raton</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>ITB 26-196</t>
+          <t>2026-015-VG</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>ITB 26-196 Southwest Regional Water Reclamation Facility (SWRWRF) - Reclaimed Water System</t>
+          <t>Installation and/or Replacement of Potable and/or Reclaimed Water Meters with AMI Transponders (Addendum 1)</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -23995,7 +23991,7 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>RFP</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
@@ -24003,20 +23999,16 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="H448" s="3" t="n">
-        <v>46350</v>
+      <c r="H448" s="5" t="n">
+        <v>46349.625</v>
       </c>
       <c r="I448" s="3" t="n">
-        <v>46312</v>
-      </c>
-      <c r="J448" s="4" t="inlineStr">
-        <is>
-          <t>https://procurement.opengov.com/portal/citrusfl</t>
-        </is>
-      </c>
+        <v>46315</v>
+      </c>
+      <c r="J448" t="inlineStr"/>
       <c r="K448" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/citrusfl</t>
+          <t>https://brpurch.ionwave.net/SourcingEvents.aspx?SourceType=1</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
@@ -24028,22 +24020,22 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Columbia</t>
+          <t>Citrus</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Columbia County BOCC</t>
+          <t>Citrus County BOCC</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>T27-04</t>
+          <t>ITB 26-196</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>2026-2027 Annual Resurfacing - SE Hillcrest Lane, SW Fedora Way, SW Young Place</t>
+          <t>ITB 26-196 Southwest Regional Water Reclamation Facility (SWRWRF) - Reclaimed Water System</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -24051,7 +24043,11 @@
           <t>Construction</t>
         </is>
       </c>
-      <c r="F449" t="inlineStr"/>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>ITB</t>
+        </is>
+      </c>
       <c r="G449" t="inlineStr">
         <is>
           <t>Open</t>
@@ -24060,34 +24056,44 @@
       <c r="H449" s="3" t="n">
         <v>46350</v>
       </c>
-      <c r="I449" s="3" t="inlineStr"/>
+      <c r="I449" s="3" t="n">
+        <v>46312</v>
+      </c>
       <c r="J449" s="4" t="inlineStr">
         <is>
-          <t>https://www.columbiacountyfla.com/PurchasingBid.aspx?Id=1767</t>
+          <t>https://procurement.opengov.com/portal/citrusfl</t>
         </is>
       </c>
       <c r="K449" s="4" t="inlineStr">
         <is>
-          <t>https://www.columbiacountyfla.com/PurchasingBids.aspx</t>
-        </is>
-      </c>
-      <c r="L449" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/citrusfl</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Added by one-time backfill.</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Gadsden</t>
+          <t>Columbia</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Gadsden County BOCC</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr"/>
+          <t>Columbia County BOCC</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>T27-04</t>
+        </is>
+      </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>CR12 5th Avenue – Pedestrian Improvements</t>
+          <t>2026-2027 Annual Resurfacing - SE Hillcrest Lane, SW Fedora Way, SW Young Place</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -24104,44 +24110,34 @@
       <c r="H450" s="3" t="n">
         <v>46350</v>
       </c>
-      <c r="I450" s="3" t="n">
-        <v>46317</v>
-      </c>
+      <c r="I450" s="3" t="inlineStr"/>
       <c r="J450" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/gadsdencountyfl</t>
+          <t>https://www.columbiacountyfla.com/PurchasingBid.aspx?Id=1767</t>
         </is>
       </c>
       <c r="K450" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/gadsdencountyfl</t>
-        </is>
-      </c>
-      <c r="L450" t="inlineStr">
-        <is>
-          <t>Added by one-time backfill.</t>
-        </is>
-      </c>
+          <t>https://www.columbiacountyfla.com/PurchasingBids.aspx</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Gadsden</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>City of North Miami Beach</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>ITB-2026-050</t>
-        </is>
-      </c>
+          <t>Gadsden County BOCC</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr"/>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>INVITATION TO BID: Highland Village Stormwater Improvements Project (Phase 1)</t>
+          <t>CR12 5th Avenue – Pedestrian Improvements</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -24149,11 +24145,7 @@
           <t>Construction</t>
         </is>
       </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>ITB</t>
-        </is>
-      </c>
+      <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr">
         <is>
           <t>Open</t>
@@ -24163,16 +24155,16 @@
         <v>46350</v>
       </c>
       <c r="I451" s="3" t="n">
-        <v>46295</v>
+        <v>46317</v>
       </c>
       <c r="J451" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/citynmb</t>
+          <t>https://procurement.opengov.com/portal/gadsdencountyfl</t>
         </is>
       </c>
       <c r="K451" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/citynmb</t>
+          <t>https://procurement.opengov.com/portal/gadsdencountyfl</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
@@ -24184,22 +24176,22 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Pasco</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Pasco County BOCC</t>
+          <t>City of North Miami Beach</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>IFB-KM-27-016</t>
+          <t>ITB-2026-050</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>BEXLEY ELEMENTARY SIDEWALK PROJECT (BALLANTRAE BLVD FROM STRATON PL TO BUD BEXLEY PKWY)</t>
+          <t>INVITATION TO BID: Highland Village Stormwater Improvements Project (Phase 1)</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -24217,18 +24209,20 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="H452" s="5" t="n">
-        <v>46350.5625</v>
-      </c>
-      <c r="I452" s="3" t="inlineStr"/>
+      <c r="H452" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="I452" s="3" t="n">
+        <v>46295</v>
+      </c>
       <c r="J452" s="4" t="inlineStr">
         <is>
-          <t>https://pascocountyfl.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://procurement.opengov.com/portal/citynmb</t>
         </is>
       </c>
       <c r="K452" s="4" t="inlineStr">
         <is>
-          <t>https://pascocountyfl.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://procurement.opengov.com/portal/citynmb</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
@@ -24240,45 +24234,51 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Alachua</t>
+          <t>Pasco</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Alachua County BOCC</t>
-        </is>
-      </c>
-      <c r="C453" t="inlineStr"/>
+          <t>Pasco County BOCC</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>IFB-KM-27-016</t>
+        </is>
+      </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>Annual Crack Filling and Pavement Distress Repair with Asphalt Repair Mastic</t>
+          <t>BEXLEY ELEMENTARY SIDEWALK PROJECT (BALLANTRAE BLVD FROM STRATON PL TO BUD BEXLEY PKWY)</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="F453" t="inlineStr"/>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>ITB</t>
+        </is>
+      </c>
       <c r="G453" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="H453" s="3" t="n">
-        <v>46351</v>
-      </c>
-      <c r="I453" s="3" t="n">
-        <v>46316</v>
-      </c>
+      <c r="H453" s="5" t="n">
+        <v>46350.5625</v>
+      </c>
+      <c r="I453" s="3" t="inlineStr"/>
       <c r="J453" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/alachuacounty</t>
+          <t>https://pascocountyfl.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="K453" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/alachuacounty</t>
+          <t>https://pascocountyfl.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
@@ -24301,12 +24301,12 @@
       <c r="C454" t="inlineStr"/>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>Annual Limited Width (Strip) Milling and Resurfacing</t>
+          <t>Annual Crack Filling and Pavement Distress Repair with Asphalt Repair Mastic</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -24351,7 +24351,7 @@
       <c r="C455" t="inlineStr"/>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>Annual Pothole Repair with Hot Mix Asphalt</t>
+          <t>Annual Limited Width (Strip) Milling and Resurfacing</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -24390,18 +24390,18 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Broward</t>
+          <t>Alachua</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>City of Hollywood</t>
+          <t>Alachua County BOCC</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>SW-2 Bypass Pumping &amp; Rehabilitation (Project No. 25-11070A)</t>
+          <t>Annual Pothole Repair with Hot Mix Asphalt</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -24419,16 +24419,16 @@
         <v>46351</v>
       </c>
       <c r="I456" s="3" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="J456" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/hollywoodfl</t>
+          <t>https://procurement.opengov.com/portal/alachuacounty</t>
         </is>
       </c>
       <c r="K456" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/hollywoodfl</t>
+          <t>https://procurement.opengov.com/portal/alachuacounty</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
@@ -24451,12 +24451,12 @@
       <c r="C457" t="inlineStr"/>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>Water Treatment Plant Maintenance Package ‘A’; Project No. 25-4261</t>
+          <t>SW-2 Bypass Pumping &amp; Rehabilitation (Project No. 25-11070A)</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -24490,27 +24490,23 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>City of Bartow</t>
-        </is>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>27-02</t>
-        </is>
-      </c>
+          <t>City of Hollywood</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr"/>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>Main Street Concrete Curbing, Sidewalk, and Driveways.</t>
+          <t>Water Treatment Plant Maintenance Package ‘A’; Project No. 25-4261</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -24527,12 +24523,12 @@
       </c>
       <c r="J458" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/bartowfl</t>
+          <t>https://procurement.opengov.com/portal/hollywoodfl</t>
         </is>
       </c>
       <c r="K458" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/bartowfl</t>
+          <t>https://procurement.opengov.com/portal/hollywoodfl</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
@@ -24544,49 +24540,49 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Putnam</t>
+          <t>Polk</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Putnam County School District</t>
-        </is>
-      </c>
-      <c r="C459" t="inlineStr"/>
+          <t>City of Bartow</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>27-02</t>
+        </is>
+      </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>Request for Qualifications – Professional Architectural Services for Bond-Funded School Renovation Projects</t>
+          <t>Main Street Concrete Curbing, Sidewalk, and Driveways.</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
-        </is>
-      </c>
-      <c r="F459" t="inlineStr">
-        <is>
-          <t>RFQ (qualifications)</t>
-        </is>
-      </c>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr"/>
       <c r="G459" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
       <c r="H459" s="3" t="n">
-        <v>46353</v>
+        <v>46351</v>
       </c>
       <c r="I459" s="3" t="n">
-        <v>46304</v>
+        <v>46315</v>
       </c>
       <c r="J459" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/myputnamschools</t>
+          <t>https://procurement.opengov.com/portal/bartowfl</t>
         </is>
       </c>
       <c r="K459" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/myputnamschools</t>
+          <t>https://procurement.opengov.com/portal/bartowfl</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
@@ -24598,49 +24594,49 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Clay</t>
+          <t>Putnam</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Clay County BOCC</t>
-        </is>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>25/26-119</t>
-        </is>
-      </c>
+          <t>Putnam County School District</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr"/>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>County Road 220 Phase 2 – Milling and Resurfacing</t>
+          <t>Request for Qualifications – Professional Architectural Services for Bond-Funded School Renovation Projects</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F460" t="inlineStr"/>
+          <t>Engineering &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>RFQ (qualifications)</t>
+        </is>
+      </c>
       <c r="G460" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
       <c r="H460" s="3" t="n">
-        <v>46356</v>
+        <v>46353</v>
       </c>
       <c r="I460" s="3" t="n">
-        <v>46310</v>
+        <v>46304</v>
       </c>
       <c r="J460" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/claycounty</t>
+          <t>https://procurement.opengov.com/portal/myputnamschools</t>
         </is>
       </c>
       <c r="K460" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/claycounty</t>
+          <t>https://procurement.opengov.com/portal/myputnamschools</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
@@ -24662,12 +24658,12 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>26/27-004</t>
+          <t>25/26-119</t>
         </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>Orange Park Neighborhoods - Milling and Resurfacing</t>
+          <t>County Road 220 Phase 2 – Milling and Resurfacing</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -24706,22 +24702,22 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Clay</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
+          <t>Clay County BOCC</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>MCC 7360 RPQ No P16319</t>
+          <t>26/27-004</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>Pump Station 0812 Relocation and Upgrade</t>
+          <t>Orange Park Neighborhoods - Milling and Resurfacing</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -24736,43 +24732,51 @@
         </is>
       </c>
       <c r="H462" s="3" t="n">
-        <v>46357</v>
+        <v>46356</v>
       </c>
       <c r="I462" s="3" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="J462" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/SolicitationDetails?solNumber=MCC%207360%20RPQ%20No%20P16319</t>
+          <t>https://procurement.opengov.com/portal/claycounty</t>
         </is>
       </c>
       <c r="K462" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/CurrentSolicitations</t>
-        </is>
-      </c>
-      <c r="L462" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/claycounty</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>Added by one-time backfill.</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Pinellas</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>City of St. Petersburg</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr"/>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>MCC 7360 RPQ No P16319</t>
+        </is>
+      </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>Fireworks Displays</t>
+          <t>Pump Station 0812 Relocation and Upgrade</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Concessions &amp; Programs</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -24789,40 +24793,36 @@
       </c>
       <c r="J463" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/stpete</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/SolicitationDetails?solNumber=MCC%207360%20RPQ%20No%20P16319</t>
         </is>
       </c>
       <c r="K463" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/stpete</t>
-        </is>
-      </c>
-      <c r="L463" t="inlineStr">
-        <is>
-          <t>Added by one-time backfill.</t>
-        </is>
-      </c>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/CurrentSolicitations</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Alachua</t>
+          <t>Pinellas</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Alachua County BOCC</t>
+          <t>City of St. Petersburg</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>Alachua County Civil Sheriff New Office Buildout at the New Court Complex Parking Garage</t>
+          <t>Fireworks Displays</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Concessions &amp; Programs</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -24832,19 +24832,19 @@
         </is>
       </c>
       <c r="H464" s="3" t="n">
-        <v>46358</v>
+        <v>46357</v>
       </c>
       <c r="I464" s="3" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="J464" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/alachuacounty</t>
+          <t>https://procurement.opengov.com/portal/stpete</t>
         </is>
       </c>
       <c r="K464" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/alachuacounty</t>
+          <t>https://procurement.opengov.com/portal/stpete</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
@@ -24856,18 +24856,18 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Broward</t>
+          <t>Alachua</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>City of Pompano Beach</t>
+          <t>Alachua County BOCC</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>Water Treatment Plant Improvements Phase 1: Buildout of the Existing Nanofiltration Facility (State Revolving Fund)</t>
+          <t>Alachua County Civil Sheriff New Office Buildout at the New Court Complex Parking Garage</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -24885,16 +24885,16 @@
         <v>46358</v>
       </c>
       <c r="I465" s="3" t="n">
-        <v>46296</v>
+        <v>46309</v>
       </c>
       <c r="J465" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/copbfl</t>
+          <t>https://procurement.opengov.com/portal/alachuacounty</t>
         </is>
       </c>
       <c r="K465" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/copbfl</t>
+          <t>https://procurement.opengov.com/portal/alachuacounty</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
@@ -24906,22 +24906,18 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
-        </is>
-      </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>20260191 (MCC 7360)</t>
-        </is>
-      </c>
+          <t>City of Pompano Beach</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr"/>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>Drainage Improvements Multiple Sites</t>
+          <t>Water Treatment Plant Improvements Phase 1: Buildout of the Existing Nanofiltration Facility (State Revolving Fund)</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -24939,19 +24935,23 @@
         <v>46358</v>
       </c>
       <c r="I466" s="3" t="n">
-        <v>46318</v>
+        <v>46296</v>
       </c>
       <c r="J466" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/SolicitationDetails?solNumber=20260191%20%28MCC%207360%29</t>
+          <t>https://procurement.opengov.com/portal/copbfl</t>
         </is>
       </c>
       <c r="K466" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/CurrentSolicitations</t>
-        </is>
-      </c>
-      <c r="L466" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/copbfl</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>Added by one-time backfill.</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -24961,29 +24961,25 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>City of North Miami Beach</t>
+          <t>Miami-Dade County</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>RFP-2026-091</t>
+          <t>20260191 (MCC 7360)</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>STATE LOBBYING SERVICES FOR WATER AND WASTEWATER INFRASTRUCTURE AND UTILITY POLICY</t>
+          <t>Drainage Improvements Multiple Sites</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
-        </is>
-      </c>
-      <c r="F467" t="inlineStr">
-        <is>
-          <t>RFP</t>
-        </is>
-      </c>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr"/>
       <c r="G467" t="inlineStr">
         <is>
           <t>Open</t>
@@ -24993,23 +24989,19 @@
         <v>46358</v>
       </c>
       <c r="I467" s="3" t="n">
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="J467" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/citynmb</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/SolicitationDetails?solNumber=20260191%20%28MCC%207360%29</t>
         </is>
       </c>
       <c r="K467" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/citynmb</t>
-        </is>
-      </c>
-      <c r="L467" t="inlineStr">
-        <is>
-          <t>Added by one-time backfill.</t>
-        </is>
-      </c>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/CurrentSolicitations</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -25019,25 +25011,29 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
+          <t>City of North Miami Beach</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>20260169 (MCC 7360)</t>
+          <t>RFP-2026-091</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>Traffic Circle at SW 62nd Ave. And SW 48th Street</t>
+          <t>STATE LOBBYING SERVICES FOR WATER AND WASTEWATER INFRASTRUCTURE AND UTILITY POLICY</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F468" t="inlineStr"/>
+          <t>Consulting &amp; Professional Services</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>RFP</t>
+        </is>
+      </c>
       <c r="G468" t="inlineStr">
         <is>
           <t>Open</t>
@@ -25047,39 +25043,43 @@
         <v>46358</v>
       </c>
       <c r="I468" s="3" t="n">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="J468" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/SolicitationDetails?solNumber=20260169%20%28MCC%207360%29</t>
+          <t>https://procurement.opengov.com/portal/citynmb</t>
         </is>
       </c>
       <c r="K468" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/CurrentSolicitations</t>
-        </is>
-      </c>
-      <c r="L468" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/citynmb</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>Added by one-time backfill.</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Charlotte County BOCC</t>
+          <t>Miami-Dade County</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>26-684</t>
+          <t>20260169 (MCC 7360)</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>Live Oak Point- Shoreline Stabilization</t>
+          <t>Traffic Circle at SW 62nd Ave. And SW 48th Street</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -25087,106 +25087,106 @@
           <t>Construction</t>
         </is>
       </c>
-      <c r="F469" t="inlineStr">
-        <is>
-          <t>Bid</t>
-        </is>
-      </c>
+      <c r="F469" t="inlineStr"/>
       <c r="G469" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="H469" s="5" t="n">
-        <v>46358.58333333334</v>
-      </c>
-      <c r="I469" s="3" t="inlineStr"/>
+      <c r="H469" s="3" t="n">
+        <v>46358</v>
+      </c>
+      <c r="I469" s="3" t="n">
+        <v>46318</v>
+      </c>
       <c r="J469" s="4" t="inlineStr">
         <is>
-          <t>https://purchasingbids.charlottecountyfl.gov/ContractsCatalogs/ShowDoc/266843?tp=D</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/SolicitationDetails?solNumber=20260169%20%28MCC%207360%29</t>
         </is>
       </c>
       <c r="K469" s="4" t="inlineStr">
         <is>
-          <t>https://purchasingbids.charlottecountyfl.gov/ContractsCatalogs</t>
-        </is>
-      </c>
-      <c r="L469" t="inlineStr">
-        <is>
-          <t>Contact: Ariel.Johnson@charlottecountyfl.gov</t>
-        </is>
-      </c>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/CurrentSolicitations</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Broward</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>City of Pompano Beach</t>
-        </is>
-      </c>
-      <c r="C470" t="inlineStr"/>
+          <t>Charlotte County BOCC</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>26-684</t>
+        </is>
+      </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>Emergency Rental, Delivery, Installation, Maintenance, and Removal of Tents, Canopies, and Related Temporary Shelter Equipment</t>
+          <t>Live Oak Point- Shoreline Stabilization</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
-        </is>
-      </c>
-      <c r="F470" t="inlineStr"/>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
       <c r="G470" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="H470" s="3" t="n">
-        <v>46359</v>
-      </c>
-      <c r="I470" s="3" t="n">
-        <v>46317</v>
-      </c>
+      <c r="H470" s="5" t="n">
+        <v>46358.58333333334</v>
+      </c>
+      <c r="I470" s="3" t="inlineStr"/>
       <c r="J470" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/copbfl</t>
+          <t>https://purchasingbids.charlottecountyfl.gov/ContractsCatalogs/ShowDoc/266843?tp=D</t>
         </is>
       </c>
       <c r="K470" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/copbfl</t>
+          <t>https://purchasingbids.charlottecountyfl.gov/ContractsCatalogs</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>Added by one-time backfill.</t>
+          <t>Contact: Ariel.Johnson@charlottecountyfl.gov</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>City of Plant City</t>
+          <t>City of Pompano Beach</t>
         </is>
       </c>
       <c r="C471" t="inlineStr"/>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>Plant City Utilities Communication Tower Generator Replacement (FEMA)</t>
+          <t>Emergency Rental, Delivery, Installation, Maintenance, and Removal of Tents, Canopies, and Related Temporary Shelter Equipment</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -25203,12 +25203,12 @@
       </c>
       <c r="J471" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/plantcitygov</t>
+          <t>https://procurement.opengov.com/portal/copbfl</t>
         </is>
       </c>
       <c r="K471" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/plantcitygov</t>
+          <t>https://procurement.opengov.com/portal/copbfl</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
@@ -25220,34 +25220,26 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>City of Clermont</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>RFB 27-018</t>
-        </is>
-      </c>
+          <t>City of Plant City</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr"/>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>Public Safety Vehicle Equipment and Upfitting Services</t>
+          <t>Plant City Utilities Communication Tower Generator Replacement (FEMA)</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
-        </is>
-      </c>
-      <c r="F472" t="inlineStr">
-        <is>
-          <t>ITB</t>
-        </is>
-      </c>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr"/>
       <c r="G472" t="inlineStr">
         <is>
           <t>Open</t>
@@ -25261,12 +25253,12 @@
       </c>
       <c r="J472" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/clermontfl</t>
+          <t>https://procurement.opengov.com/portal/plantcitygov</t>
         </is>
       </c>
       <c r="K472" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/clermontfl</t>
+          <t>https://procurement.opengov.com/portal/plantcitygov</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
@@ -25278,30 +25270,34 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Volusia</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Volusia County</t>
+          <t>City of Clermont</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>27-SQ-14KO, C2102</t>
+          <t>RFB 27-018</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>Professional Construction Management/General Contracting Services for the Volusia County Branch Jail Air Handler and Fire Alarm Project</t>
+          <t>Public Safety Vehicle Equipment and Upfitting Services</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F473" t="inlineStr"/>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>ITB</t>
+        </is>
+      </c>
       <c r="G473" t="inlineStr">
         <is>
           <t>Open</t>
@@ -25315,12 +25311,12 @@
       </c>
       <c r="J473" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/volusia</t>
+          <t>https://procurement.opengov.com/portal/clermontfl</t>
         </is>
       </c>
       <c r="K473" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/volusia</t>
+          <t>https://procurement.opengov.com/portal/clermontfl</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
@@ -25332,27 +25328,27 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Volusia</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Hillsborough County BOCC</t>
+          <t>Volusia County</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>RPS-26-00423</t>
+          <t>27-SQ-14KO, C2102</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>Waters Avenue Force Main Replacement CEI Services</t>
+          <t>Professional Construction Management/General Contracting Services for the Volusia County Branch Jail Air Handler and Fire Alarm Project</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -25361,18 +25357,20 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="H474" s="5" t="n">
-        <v>46360.58333333334</v>
-      </c>
-      <c r="I474" s="3" t="inlineStr"/>
+      <c r="H474" s="3" t="n">
+        <v>46359</v>
+      </c>
+      <c r="I474" s="3" t="n">
+        <v>46317</v>
+      </c>
       <c r="J474" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://procurement.opengov.com/portal/volusia</t>
         </is>
       </c>
       <c r="K474" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://procurement.opengov.com/portal/volusia</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
@@ -25384,27 +25382,27 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>RFP0000016</t>
+          <t>RPS-26-00423</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>Prosper 27 Development</t>
+          <t>Waters Avenue Force Main Replacement CEI Services</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -25416,41 +25414,47 @@
       <c r="H475" s="5" t="n">
         <v>46360.58333333334</v>
       </c>
-      <c r="I475" s="3" t="n">
-        <v>46315</v>
-      </c>
-      <c r="J475" t="inlineStr"/>
+      <c r="I475" s="3" t="inlineStr"/>
+      <c r="J475" s="4" t="inlineStr">
+        <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
       <c r="K475" s="4" t="inlineStr">
         <is>
-          <t>https://supplier.miamidade.gov/psc/EXTSUPP/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_BID_CMP_FL.GBL</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>Find event RFP0000016 on the INFORMS public bidding page.</t>
+          <t>Added by one-time backfill.</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>City of Orlando</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr"/>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>RFP0000016</t>
+        </is>
+      </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>Annual External Financial Audit Services</t>
+          <t>Prosper 27 Development</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -25459,47 +25463,39 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="H476" s="3" t="n">
-        <v>46363</v>
+      <c r="H476" s="5" t="n">
+        <v>46360.58333333334</v>
       </c>
       <c r="I476" s="3" t="n">
-        <v>46318</v>
-      </c>
-      <c r="J476" s="4" t="inlineStr">
-        <is>
-          <t>https://procurement.opengov.com/portal/orlando</t>
-        </is>
-      </c>
+        <v>46315</v>
+      </c>
+      <c r="J476" t="inlineStr"/>
       <c r="K476" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/orlando</t>
+          <t>https://supplier.miamidade.gov/psc/EXTSUPP/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_BID_CMP_FL.GBL</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>Added by one-time backfill.</t>
+          <t>Find event RFP0000016 on the INFORMS public bidding page.</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Volusia</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Volusia County</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>26-P-124JJ</t>
-        </is>
-      </c>
+          <t>City of Orlando</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr"/>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>Ocean Center Event Staffing and Event Security Services</t>
+          <t>Annual External Financial Audit Services</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -25514,19 +25510,19 @@
         </is>
       </c>
       <c r="H477" s="3" t="n">
-        <v>46365</v>
+        <v>46363</v>
       </c>
       <c r="I477" s="3" t="n">
-        <v>46308</v>
+        <v>46318</v>
       </c>
       <c r="J477" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/volusia</t>
+          <t>https://procurement.opengov.com/portal/orlando</t>
         </is>
       </c>
       <c r="K477" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/volusia</t>
+          <t>https://procurement.opengov.com/portal/orlando</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
@@ -25538,81 +25534,81 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Volusia</t>
+          <t>St. Lucie</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Volusia County</t>
+          <t>St. Lucie County BOCC</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>27-B-09CW</t>
+          <t>RFQ-27-009-0-2027/DC</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>Tomoka Landfill Roadway Improvement and Scale Addition</t>
+          <t>Professional Engineering Services - Edwards Rd from S. Jenkins Rd to Selvitz Rd PD&amp;E Study</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F478" t="inlineStr"/>
+          <t>Engineering &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H478" s="3" t="n">
-        <v>46372</v>
+        <v>46365</v>
       </c>
       <c r="I478" s="3" t="n">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="J478" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/volusia</t>
+          <t>https://www.demandstar.com/app/limited/bids/554953/details</t>
         </is>
       </c>
       <c r="K478" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/volusia</t>
-        </is>
-      </c>
-      <c r="L478" t="inlineStr">
-        <is>
-          <t>Added by one-time backfill.</t>
-        </is>
-      </c>
+          <t>https://www.demandstar.com/app/agencies/florida/st-lucie-county-purchasing-department/procurement-opportunities/dba839e8-c1f1-4ea4-8e46-57cbc2d9aad2</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Pasco</t>
+          <t>Volusia</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Pasco County BOCC</t>
+          <t>Volusia County</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>NOA-KM-27-014</t>
+          <t>26-P-124JJ</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>COOLING TOWER REPLACEMENT - PASCO FACILITY</t>
+          <t>Ocean Center Event Staffing and Event Security Services</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -25621,18 +25617,20 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="H479" s="5" t="n">
-        <v>46372.5625</v>
-      </c>
-      <c r="I479" s="3" t="inlineStr"/>
+      <c r="H479" s="3" t="n">
+        <v>46365</v>
+      </c>
+      <c r="I479" s="3" t="n">
+        <v>46308</v>
+      </c>
       <c r="J479" s="4" t="inlineStr">
         <is>
-          <t>https://pascocountyfl.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://procurement.opengov.com/portal/volusia</t>
         </is>
       </c>
       <c r="K479" s="4" t="inlineStr">
         <is>
-          <t>https://pascocountyfl.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://procurement.opengov.com/portal/volusia</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
@@ -25644,51 +25642,49 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Palm Beach</t>
+          <t>Volusia</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Solid Waste Authority of Palm Beach County</t>
+          <t>Volusia County</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>RFP No.: 27-202/DL</t>
+          <t>27-B-09CW</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>DISCLOSURE COUNSEL SERVICES</t>
+          <t>Tomoka Landfill Roadway Improvement and Scale Addition</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
-        </is>
-      </c>
-      <c r="F480" t="inlineStr">
-        <is>
-          <t>RFP</t>
-        </is>
-      </c>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr"/>
       <c r="G480" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="H480" s="5" t="n">
-        <v>46372.58333333334</v>
-      </c>
-      <c r="I480" s="3" t="inlineStr"/>
+      <c r="H480" s="3" t="n">
+        <v>46372</v>
+      </c>
+      <c r="I480" s="3" t="n">
+        <v>46316</v>
+      </c>
       <c r="J480" s="4" t="inlineStr">
         <is>
-          <t>https://swa.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://procurement.opengov.com/portal/volusia</t>
         </is>
       </c>
       <c r="K480" s="4" t="inlineStr">
         <is>
-          <t>https://swa.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://procurement.opengov.com/portal/volusia</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
@@ -25700,27 +25696,27 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Pasco</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Miami-Dade County – Clerk of Courts</t>
+          <t>Pasco County BOCC</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>CL00000013</t>
+          <t>NOA-KM-27-014</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>Clerk Banking &amp; Third-Party Custodial Svcs</t>
+          <t>COOLING TOWER REPLACEMENT - PASCO FACILITY</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -25730,69 +25726,73 @@
         </is>
       </c>
       <c r="H481" s="5" t="n">
-        <v>46373.58333333334</v>
-      </c>
-      <c r="I481" s="3" t="n">
-        <v>45968</v>
-      </c>
-      <c r="J481" t="inlineStr"/>
+        <v>46372.5625</v>
+      </c>
+      <c r="I481" s="3" t="inlineStr"/>
+      <c r="J481" s="4" t="inlineStr">
+        <is>
+          <t>https://pascocountyfl.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
       <c r="K481" s="4" t="inlineStr">
         <is>
-          <t>https://supplier.miamidade.gov/psc/EXTSUPP/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_BID_CMP_FL.GBL</t>
+          <t>https://pascocountyfl.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>Find event CL00000013 on the INFORMS public bidding page.</t>
+          <t>Added by one-time backfill.</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Volusia</t>
+          <t>Palm Beach</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Volusia County</t>
+          <t>Solid Waste Authority of Palm Beach County</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>26-B-120KW</t>
+          <t>RFP No.: 27-202/DL</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>CDBG-DR SMA Healthcare Ridgewood Flood Mitigation Construction</t>
+          <t>DISCLOSURE COUNSEL SERVICES</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F482" t="inlineStr"/>
+          <t>Consulting &amp; Professional Services</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>RFP</t>
+        </is>
+      </c>
       <c r="G482" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="H482" s="3" t="n">
-        <v>46387</v>
-      </c>
-      <c r="I482" s="3" t="n">
-        <v>46248</v>
-      </c>
+      <c r="H482" s="5" t="n">
+        <v>46372.58333333334</v>
+      </c>
+      <c r="I482" s="3" t="inlineStr"/>
       <c r="J482" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/volusia</t>
+          <t>https://swa.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="K482" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/volusia</t>
+          <t>https://swa.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
@@ -25804,23 +25804,27 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Broward</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>City of Pompano Beach</t>
-        </is>
-      </c>
-      <c r="C483" t="inlineStr"/>
+          <t>Miami-Dade County – Clerk of Courts</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>CL00000013</t>
+        </is>
+      </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>VOIP Phone System</t>
+          <t>Clerk Banking &amp; Third-Party Custodial Svcs</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>IT &amp; Technology</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -25829,25 +25833,21 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="H483" s="3" t="n">
-        <v>46391</v>
+      <c r="H483" s="5" t="n">
+        <v>46373.58333333334</v>
       </c>
       <c r="I483" s="3" t="n">
-        <v>46317</v>
-      </c>
-      <c r="J483" s="4" t="inlineStr">
-        <is>
-          <t>https://procurement.opengov.com/portal/copbfl</t>
-        </is>
-      </c>
+        <v>45968</v>
+      </c>
+      <c r="J483" t="inlineStr"/>
       <c r="K483" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/copbfl</t>
+          <t>https://supplier.miamidade.gov/psc/EXTSUPP/SUPPLIER/ERP/c/SCP_PUBLIC_MENU_FL.SCP_PUB_BID_CMP_FL.GBL</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>Added by one-time backfill.</t>
+          <t>Find event CL00000013 on the INFORMS public bidding page.</t>
         </is>
       </c>
     </row>
@@ -25859,17 +25859,17 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>City of New Smyrna Beach</t>
+          <t>Volusia County</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>04-26-ENG</t>
+          <t>26-B-120KW</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>Construction of the Washington Street Roadway Improvements FPID NO. 447711-1-54-01</t>
+          <t>CDBG-DR SMA Healthcare Ridgewood Flood Mitigation Construction</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -25884,19 +25884,19 @@
         </is>
       </c>
       <c r="H484" s="3" t="n">
-        <v>46400</v>
+        <v>46387</v>
       </c>
       <c r="I484" s="3" t="n">
-        <v>46311</v>
+        <v>46248</v>
       </c>
       <c r="J484" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/cityofnsb</t>
+          <t>https://procurement.opengov.com/portal/volusia</t>
         </is>
       </c>
       <c r="K484" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/cityofnsb</t>
+          <t>https://procurement.opengov.com/portal/volusia</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
@@ -25908,27 +25908,23 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Escambia</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Escambia County BOCC</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>PD 23-24.010-1</t>
-        </is>
-      </c>
+          <t>City of Pompano Beach</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr"/>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>Engineering Professional Services Continuing Contract - (2nd Advertisement)</t>
+          <t>VOIP Phone System</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -25938,19 +25934,19 @@
         </is>
       </c>
       <c r="H485" s="3" t="n">
-        <v>46440</v>
+        <v>46391</v>
       </c>
       <c r="I485" s="3" t="n">
-        <v>45345</v>
+        <v>46317</v>
       </c>
       <c r="J485" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/escambiacountyfl</t>
+          <t>https://procurement.opengov.com/portal/copbfl</t>
         </is>
       </c>
       <c r="K485" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/escambiacountyfl</t>
+          <t>https://procurement.opengov.com/portal/copbfl</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
@@ -25962,23 +25958,27 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Volusia</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Greater Orlando Aviation Authority</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr"/>
+          <t>City of New Smyrna Beach</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>04-26-ENG</t>
+        </is>
+      </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>Express Baggage Handling Services Permit Application</t>
+          <t>Construction of the Washington Street Roadway Improvements FPID NO. 447711-1-54-01</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>IT &amp; Technology</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -25988,19 +25988,19 @@
         </is>
       </c>
       <c r="H486" s="3" t="n">
-        <v>46690</v>
+        <v>46400</v>
       </c>
       <c r="I486" s="3" t="n">
-        <v>45618</v>
+        <v>46311</v>
       </c>
       <c r="J486" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/goaa</t>
+          <t>https://procurement.opengov.com/portal/cityofnsb</t>
         </is>
       </c>
       <c r="K486" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/goaa</t>
+          <t>https://procurement.opengov.com/portal/cityofnsb</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
@@ -26012,23 +26012,27 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Escambia</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Tampa International Airport</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr"/>
+          <t>Escambia County BOCC</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>PD 23-24.010-1</t>
+        </is>
+      </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>Staffing Services</t>
+          <t>Engineering Professional Services Continuing Contract - (2nd Advertisement)</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -26038,19 +26042,19 @@
         </is>
       </c>
       <c r="H487" s="3" t="n">
-        <v>46812</v>
+        <v>46440</v>
       </c>
       <c r="I487" s="3" t="n">
-        <v>44846</v>
+        <v>45345</v>
       </c>
       <c r="J487" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/tampaairport</t>
+          <t>https://procurement.opengov.com/portal/escambiacountyfl</t>
         </is>
       </c>
       <c r="K487" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/tampaairport</t>
+          <t>https://procurement.opengov.com/portal/escambiacountyfl</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
@@ -26062,27 +26066,23 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Escambia</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Escambia County BOCC</t>
-        </is>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>PD 24-25.070-1</t>
-        </is>
-      </c>
+          <t>Greater Orlando Aviation Authority</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr"/>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>Task Order Solicitation for Code Enforcement- Re-solicit - 2nd Advertisement</t>
+          <t>Express Baggage Handling Services Permit Application</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -26092,19 +26092,19 @@
         </is>
       </c>
       <c r="H488" s="3" t="n">
-        <v>46971</v>
+        <v>46690</v>
       </c>
       <c r="I488" s="3" t="n">
-        <v>46027</v>
+        <v>45618</v>
       </c>
       <c r="J488" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/escambiacountyfl</t>
+          <t>https://procurement.opengov.com/portal/goaa</t>
         </is>
       </c>
       <c r="K488" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/escambiacountyfl</t>
+          <t>https://procurement.opengov.com/portal/goaa</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
@@ -26116,27 +26116,23 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Escambia</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Escambia County BOCC</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>PD 25-26.002-1</t>
-        </is>
-      </c>
+          <t>Tampa International Airport</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr"/>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>Professional Architectural Services - 2nd Posting</t>
+          <t>Staffing Services</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
+          <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -26146,19 +26142,19 @@
         </is>
       </c>
       <c r="H489" s="3" t="n">
-        <v>47097</v>
+        <v>46812</v>
       </c>
       <c r="I489" s="3" t="n">
-        <v>46007</v>
+        <v>44846</v>
       </c>
       <c r="J489" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/escambiacountyfl</t>
+          <t>https://procurement.opengov.com/portal/tampaairport</t>
         </is>
       </c>
       <c r="K489" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/escambiacountyfl</t>
+          <t>https://procurement.opengov.com/portal/tampaairport</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
@@ -26170,23 +26166,27 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Pinellas</t>
+          <t>Escambia</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>City of St. Petersburg</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr"/>
+          <t>Escambia County BOCC</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>PD 24-25.070-1</t>
+        </is>
+      </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>Rehabilitation of Residential Single-Family Properties: Plumbers, Roofing, Building, Residential, and General Contractors</t>
+          <t>Task Order Solicitation for Code Enforcement- Re-solicit - 2nd Advertisement</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -26196,19 +26196,19 @@
         </is>
       </c>
       <c r="H490" s="3" t="n">
-        <v>47192</v>
+        <v>46971</v>
       </c>
       <c r="I490" s="3" t="n">
-        <v>46097</v>
+        <v>46027</v>
       </c>
       <c r="J490" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/stpete</t>
+          <t>https://procurement.opengov.com/portal/escambiacountyfl</t>
         </is>
       </c>
       <c r="K490" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/stpete</t>
+          <t>https://procurement.opengov.com/portal/escambiacountyfl</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
@@ -26220,27 +26220,27 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Escambia</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>City of Bartow</t>
+          <t>Escambia County BOCC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>CSB 25-17</t>
+          <t>PD 25-26.002-1</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>Water &amp; Wastewater Utilities Supplies, Parts &amp; Equipment</t>
+          <t>Professional Architectural Services - 2nd Posting</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -26250,19 +26250,19 @@
         </is>
       </c>
       <c r="H491" s="3" t="n">
-        <v>47268</v>
+        <v>47097</v>
       </c>
       <c r="I491" s="3" t="n">
-        <v>45793</v>
+        <v>46007</v>
       </c>
       <c r="J491" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/bartowfl</t>
+          <t>https://procurement.opengov.com/portal/escambiacountyfl</t>
         </is>
       </c>
       <c r="K491" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/bartowfl</t>
+          <t>https://procurement.opengov.com/portal/escambiacountyfl</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
@@ -26274,27 +26274,23 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Osceola</t>
+          <t>Pinellas</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>City of St. Cloud</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>2024-120</t>
-        </is>
-      </c>
+          <t>City of St. Petersburg</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr"/>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>Citywide Cell Towers</t>
+          <t>Rehabilitation of Residential Single-Family Properties: Plumbers, Roofing, Building, Residential, and General Contractors</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Concessions &amp; Programs</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -26304,19 +26300,19 @@
         </is>
       </c>
       <c r="H492" s="3" t="n">
-        <v>47290</v>
+        <v>47192</v>
       </c>
       <c r="I492" s="3" t="n">
-        <v>45459</v>
+        <v>46097</v>
       </c>
       <c r="J492" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/stcloud</t>
+          <t>https://procurement.opengov.com/portal/stpete</t>
         </is>
       </c>
       <c r="K492" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/stcloud</t>
+          <t>https://procurement.opengov.com/portal/stpete</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
@@ -26328,22 +26324,22 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Pinellas</t>
+          <t>Polk</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Pinellas County BOCC</t>
+          <t>City of Bartow</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>25-0786-ITQ</t>
+          <t>CSB 25-17</t>
         </is>
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>General Solicitation for Emergency/Disaster Response Goods &amp; Services</t>
+          <t>Water &amp; Wastewater Utilities Supplies, Parts &amp; Equipment</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -26351,30 +26347,26 @@
           <t>Goods &amp; Supplies</t>
         </is>
       </c>
-      <c r="F493" t="inlineStr">
-        <is>
-          <t>Quote</t>
-        </is>
-      </c>
+      <c r="F493" t="inlineStr"/>
       <c r="G493" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
       <c r="H493" s="3" t="n">
-        <v>47330</v>
+        <v>47268</v>
       </c>
       <c r="I493" s="3" t="n">
-        <v>45869</v>
+        <v>45793</v>
       </c>
       <c r="J493" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/pinellasfl</t>
+          <t>https://procurement.opengov.com/portal/bartowfl</t>
         </is>
       </c>
       <c r="K493" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/pinellasfl</t>
+          <t>https://procurement.opengov.com/portal/bartowfl</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
@@ -26386,53 +26378,49 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Pinellas</t>
+          <t>Osceola</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Pinellas County BOCC</t>
+          <t>City of St. Cloud</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>26-0853-RFQ-CCNA</t>
+          <t>2024-120</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>Pinellas County SBE Consultants per the Consultant Competitive Negotiations Act (CCNA)</t>
+          <t>Citywide Cell Towers</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
-        </is>
-      </c>
-      <c r="F494" t="inlineStr">
-        <is>
-          <t>RFQ (qualifications)</t>
-        </is>
-      </c>
+          <t>Concessions &amp; Programs</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr"/>
       <c r="G494" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
       <c r="H494" s="3" t="n">
-        <v>48102</v>
+        <v>47290</v>
       </c>
       <c r="I494" s="3" t="n">
-        <v>46276</v>
+        <v>45459</v>
       </c>
       <c r="J494" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/pinellasfl</t>
+          <t>https://procurement.opengov.com/portal/stcloud</t>
         </is>
       </c>
       <c r="K494" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/pinellasfl</t>
+          <t>https://procurement.opengov.com/portal/stcloud</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
@@ -26444,22 +26432,22 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Pinellas</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>City of Bartow</t>
+          <t>Pinellas County BOCC</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>2026-033</t>
+          <t>25-0786-ITQ</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>ITB-CS - Safety Products, Equipment &amp; Supplies</t>
+          <t>General Solicitation for Emergency/Disaster Response Goods &amp; Services</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -26469,7 +26457,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
@@ -26478,19 +26466,19 @@
         </is>
       </c>
       <c r="H495" s="3" t="n">
-        <v>48115</v>
+        <v>47330</v>
       </c>
       <c r="I495" s="3" t="n">
-        <v>46269</v>
+        <v>45869</v>
       </c>
       <c r="J495" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/bartowfl</t>
+          <t>https://procurement.opengov.com/portal/pinellasfl</t>
         </is>
       </c>
       <c r="K495" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/bartowfl</t>
+          <t>https://procurement.opengov.com/portal/pinellasfl</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
@@ -26502,49 +26490,53 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Pinellas</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>City of Bartow</t>
+          <t>Pinellas County BOCC</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>CSB - 27-01</t>
+          <t>26-0853-RFQ-CCNA</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>Hardware, Tools, and General Maintenance Supplies and Equipment</t>
+          <t>Pinellas County SBE Consultants per the Consultant Competitive Negotiations Act (CCNA)</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
-        </is>
-      </c>
-      <c r="F496" t="inlineStr"/>
+          <t>Consulting &amp; Professional Services</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>RFQ (qualifications)</t>
+        </is>
+      </c>
       <c r="G496" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
       <c r="H496" s="3" t="n">
-        <v>48141</v>
+        <v>48102</v>
       </c>
       <c r="I496" s="3" t="n">
-        <v>46318</v>
+        <v>46276</v>
       </c>
       <c r="J496" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/bartowfl</t>
+          <t>https://procurement.opengov.com/portal/pinellasfl</t>
         </is>
       </c>
       <c r="K496" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/bartowfl</t>
+          <t>https://procurement.opengov.com/portal/pinellasfl</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
@@ -26556,77 +26548,85 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Broward</t>
+          <t>Polk</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>City of Wilton Manors</t>
+          <t>City of Bartow</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-033</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>2026-05 Parking Management Services</t>
+          <t>ITB-CS - Safety Products, Equipment &amp; Supplies</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Concessions &amp; Programs</t>
-        </is>
-      </c>
-      <c r="F497" t="inlineStr"/>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>ITB</t>
+        </is>
+      </c>
       <c r="G497" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="H497" s="5" t="inlineStr"/>
-      <c r="I497" s="3" t="inlineStr"/>
+      <c r="H497" s="3" t="n">
+        <v>48115</v>
+      </c>
+      <c r="I497" s="3" t="n">
+        <v>46269</v>
+      </c>
       <c r="J497" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=153</t>
+          <t>https://procurement.opengov.com/portal/bartowfl</t>
         </is>
       </c>
       <c r="K497" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx</t>
+          <t>https://procurement.opengov.com/portal/bartowfl</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>Closes: Upon Contract</t>
+          <t>Added by one-time backfill.</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Broward</t>
+          <t>Polk</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>City of Wilton Manors</t>
+          <t>City of Bartow</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>CSB - 27-01</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>2026-10 Tidal Valve Program</t>
+          <t>Hardware, Tools, and General Maintenance Supplies and Equipment</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -26635,21 +26635,25 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="H498" s="5" t="inlineStr"/>
-      <c r="I498" s="3" t="inlineStr"/>
+      <c r="H498" s="3" t="n">
+        <v>48141</v>
+      </c>
+      <c r="I498" s="3" t="n">
+        <v>46318</v>
+      </c>
       <c r="J498" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=159</t>
+          <t>https://procurement.opengov.com/portal/bartowfl</t>
         </is>
       </c>
       <c r="K498" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx</t>
+          <t>https://procurement.opengov.com/portal/bartowfl</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>Closes: Upon Contract</t>
+          <t>Added by one-time backfill.</t>
         </is>
       </c>
     </row>
@@ -26666,17 +26670,17 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>2026-13</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>2026-13 Justin Flippen Park Electrical Upgrades</t>
+          <t>2026-05 Parking Management Services</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Concessions &amp; Programs</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -26689,7 +26693,7 @@
       <c r="I499" s="3" t="inlineStr"/>
       <c r="J499" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=160</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=153</t>
         </is>
       </c>
       <c r="K499" s="4" t="inlineStr">
@@ -26716,12 +26720,12 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>2026-14 - Re-Bid</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>2026-14 51st Year CDBG Mickel Park Electrical Upgrades - Re-Bid</t>
+          <t>2026-10 Tidal Valve Program</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -26739,7 +26743,7 @@
       <c r="I500" s="3" t="inlineStr"/>
       <c r="J500" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=165</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=159</t>
         </is>
       </c>
       <c r="K500" s="4" t="inlineStr">
@@ -26766,17 +26770,17 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>2026-15</t>
+          <t>2026-13</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>2026-15 Emergency and Special Event Catering</t>
+          <t>2026-13 Justin Flippen Park Electrical Upgrades</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Concessions &amp; Programs</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -26789,7 +26793,7 @@
       <c r="I501" s="3" t="inlineStr"/>
       <c r="J501" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=162</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=160</t>
         </is>
       </c>
       <c r="K501" s="4" t="inlineStr">
@@ -26816,12 +26820,12 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>2026-16</t>
+          <t>2026-14 - Re-Bid</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>2026-16 Lift Station No. 1 Replacement</t>
+          <t>2026-14 51st Year CDBG Mickel Park Electrical Upgrades - Re-Bid</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -26839,7 +26843,7 @@
       <c r="I502" s="3" t="inlineStr"/>
       <c r="J502" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=163</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=165</t>
         </is>
       </c>
       <c r="K502" s="4" t="inlineStr">
@@ -26866,17 +26870,17 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2026-15</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>2027-01 Lift Station No. 4 Replacement</t>
+          <t>2026-15 Emergency and Special Event Catering</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Concessions &amp; Programs</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -26889,7 +26893,7 @@
       <c r="I503" s="3" t="inlineStr"/>
       <c r="J503" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=164</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=162</t>
         </is>
       </c>
       <c r="K503" s="4" t="inlineStr">
@@ -26916,12 +26920,12 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-16</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>2027-02 Lift Station No. 7 Replacement</t>
+          <t>2026-16 Lift Station No. 1 Replacement</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -26939,7 +26943,7 @@
       <c r="I504" s="3" t="inlineStr"/>
       <c r="J504" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=166</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=163</t>
         </is>
       </c>
       <c r="K504" s="4" t="inlineStr">
@@ -26956,22 +26960,22 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Duval</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>JAXPORT</t>
+          <t>City of Wilton Manors</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>ITB_EQ-2039A</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>BLOUNT ISLAND MARINE TERMINAL HANJUNG CRANE #8841 REFURBISHMENT</t>
+          <t>2027-01 Lift Station No. 4 Replacement</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -26979,451 +26983,469 @@
           <t>Construction</t>
         </is>
       </c>
-      <c r="F505" t="inlineStr">
-        <is>
-          <t>ITB</t>
-        </is>
-      </c>
+      <c r="F505" t="inlineStr"/>
       <c r="G505" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H505" s="5" t="inlineStr"/>
       <c r="I505" s="3" t="inlineStr"/>
       <c r="J505" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14412/?sort%5B7%5D=asc</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=164</t>
         </is>
       </c>
       <c r="K505" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
-        </is>
-      </c>
-      <c r="L505" t="inlineStr"/>
+          <t>https://www.wiltonmanors.gov/bids.aspx</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>Closes: Upon Contract</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Duval</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>JAXPORT</t>
+          <t>City of Wilton Manors</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>RFQ_AE-178DR</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>CRANE ENGINEERING SERVICES (REBID)</t>
+          <t>2027-02 Lift Station No. 7 Replacement</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
-        </is>
-      </c>
-      <c r="F506" t="inlineStr">
-        <is>
-          <t>ITB</t>
-        </is>
-      </c>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr"/>
       <c r="G506" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H506" s="5" t="inlineStr"/>
       <c r="I506" s="3" t="inlineStr"/>
       <c r="J506" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14356/?sort%5B7%5D=asc</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=166</t>
         </is>
       </c>
       <c r="K506" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
-        </is>
-      </c>
-      <c r="L506" t="inlineStr"/>
+          <t>https://www.wiltonmanors.gov/bids.aspx</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>Closes: Upon Contract</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Duval</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>JAXPORT</t>
+          <t>Broward County BOCC</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>ITB_MC-2132</t>
+          <t>#248449</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>INTSALLATION OF NEW CRANE STOW PIN SOCKETS AT THE TALLEYRAND MARINE TERMINAL (TMT)</t>
+          <t>Broward County Judicial Court West Tower Repairs</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F507" t="inlineStr">
-        <is>
-          <t>ITB</t>
-        </is>
-      </c>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr"/>
       <c r="G507" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H507" s="5" t="inlineStr"/>
       <c r="I507" s="3" t="inlineStr"/>
       <c r="J507" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14410/?sort%5B7%5D=asc</t>
+          <t>https://broward.bonfirehub.com/opportunities/248449</t>
         </is>
       </c>
       <c r="K507" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
-        </is>
-      </c>
-      <c r="L507" t="inlineStr"/>
+          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Duval</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>JAXPORT</t>
+          <t>Broward County BOCC</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>PSS # EQ-2128</t>
+          <t>#239116</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>Purchase of three (3) Elevator Safety Devices</t>
+          <t>Environmental Planning and Consulting Services at FLL and HWO</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="F508" t="inlineStr">
-        <is>
-          <t>Sole source</t>
-        </is>
-      </c>
+          <t>Consulting &amp; Professional Services</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr"/>
       <c r="G508" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H508" s="5" t="inlineStr"/>
       <c r="I508" s="3" t="inlineStr"/>
       <c r="J508" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14104/?sort%5B7%5D=asc</t>
+          <t>https://broward.bonfirehub.com/opportunities/239116</t>
         </is>
       </c>
       <c r="K508" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
-        </is>
-      </c>
-      <c r="L508" t="inlineStr"/>
+          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Duval</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>JAXPORT</t>
+          <t>Broward County BOCC</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>PSS # MC-2017AJ</t>
+          <t>#254086</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>Repair and Replacement of Four (4) Canopies for Jacksonville Port Authority, Dames Point Cruise Terminal</t>
+          <t>Pre-Solicitation Notice - Draft Computer Aided Dispatch/Automatic Vehicle Location System</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>Sole source</t>
+          <t>Draft / Future</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H509" s="5" t="inlineStr"/>
       <c r="I509" s="3" t="inlineStr"/>
       <c r="J509" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14389/?sort%5B7%5D=asc</t>
+          <t>https://broward.bonfirehub.com/opportunities/254086</t>
         </is>
       </c>
       <c r="K509" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
-        </is>
-      </c>
-      <c r="L509" t="inlineStr"/>
+          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Duval</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>JAXPORT</t>
+          <t>Broward County BOCC</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>ITB C-2131</t>
+          <t>#243763</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>TALLEYRAND MARINE TERMINAL (TMT) PILE, CAP, AND BEAM REHAB</t>
+          <t>Public Notice: West Copans Rehabilitation and Redevelopment Project</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Property &amp; Real Estate</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>Notice</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H510" s="5" t="inlineStr"/>
       <c r="I510" s="3" t="inlineStr"/>
       <c r="J510" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14384/?sort%5B7%5D=asc</t>
+          <t>https://broward.bonfirehub.com/opportunities/243763</t>
         </is>
       </c>
       <c r="K510" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
-        </is>
-      </c>
-      <c r="L510" t="inlineStr"/>
+          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Duval</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>JAXPORT</t>
+          <t>Broward County BOCC</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>ITB_MC-2108N</t>
+          <t>#258935</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>TPO ROOF RETROFITS AT TMT AUTO FACILITY</t>
+          <t>Request for Information - Algo Communications – Airport Mass Notification System</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>RFI</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H511" s="5" t="inlineStr"/>
       <c r="I511" s="3" t="inlineStr"/>
       <c r="J511" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14333/?sort%5B7%5D=asc</t>
+          <t>https://broward.bonfirehub.com/opportunities/258935</t>
         </is>
       </c>
       <c r="K511" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
-        </is>
-      </c>
-      <c r="L511" t="inlineStr"/>
+          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Duval</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>JAXPORT</t>
+          <t>Broward County BOCC</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>PSS # EQ-2095A</t>
+          <t>#258937</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>The purchase of two (2) new-surplus CAT 270-3504 radiator assemblies</t>
+          <t>Request for Information - Genea Security Access Control System</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>Sole source</t>
+          <t>RFI</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H512" s="5" t="inlineStr"/>
       <c r="I512" s="3" t="inlineStr"/>
       <c r="J512" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14299/?sort%5B7%5D=asc</t>
+          <t>https://broward.bonfirehub.com/opportunities/258937</t>
         </is>
       </c>
       <c r="K512" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
-        </is>
-      </c>
-      <c r="L512" t="inlineStr"/>
+          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
+          <t>Broward County BOCC</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>A26PM01</t>
+          <t>#258942</t>
         </is>
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>A/E Services for Real Estate</t>
+          <t>Request for Information - OpenEye – CCTV Recording and Analytics</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>Draft / Future</t>
+          <t>RFI</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H513" s="5" t="inlineStr"/>
-      <c r="I513" s="3" t="n">
-        <v>46315</v>
-      </c>
+      <c r="I513" s="3" t="inlineStr"/>
       <c r="J513" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8983</t>
+          <t>https://broward.bonfirehub.com/opportunities/258942</t>
         </is>
       </c>
       <c r="K513" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>Draft for feedback. Send comments to Julie Whiteside (Julie.whiteside@miamidade.gov). Posted until 2026-11-10.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
-        </is>
-      </c>
-      <c r="C514" t="inlineStr"/>
+          <t>Broward County BOCC</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>#258939</t>
+        </is>
+      </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>Access Control Point Barrier Systems</t>
+          <t>Request for Information - Verkada – CCTV System</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -27433,153 +27455,151 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>Draft / Future</t>
+          <t>RFI</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H514" s="5" t="inlineStr"/>
-      <c r="I514" s="3" t="n">
-        <v>46302</v>
-      </c>
+      <c r="I514" s="3" t="inlineStr"/>
       <c r="J514" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8975</t>
+          <t>https://broward.bonfirehub.com/opportunities/258939</t>
         </is>
       </c>
       <c r="K514" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>Draft for feedback. Send comments to Amy Almanzar (Amy.almanzar@miamidade.gov). Posted until 2026-10-27.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
-        </is>
-      </c>
-      <c r="C515" t="inlineStr"/>
+          <t>Broward County BOCC</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>#253591</t>
+        </is>
+      </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>E26WS02 - REPOST - GEOTECHNICAL SRVS, STRUCTURAL ASSESSMENT, MATERIALS TEST</t>
+          <t>Transit Bus Stop ADA Improvements (FTA)</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
-        </is>
-      </c>
-      <c r="F515" t="inlineStr">
-        <is>
-          <t>Draft / Future</t>
-        </is>
-      </c>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr"/>
       <c r="G515" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H515" s="5" t="inlineStr"/>
-      <c r="I515" s="3" t="n">
-        <v>46315</v>
-      </c>
+      <c r="I515" s="3" t="inlineStr"/>
       <c r="J515" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8981</t>
+          <t>https://broward.bonfirehub.com/opportunities/253591</t>
         </is>
       </c>
       <c r="K515" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>Draft for feedback. Send comments to Ana M. DaSilva (ana.dasilva@miamidade.gov). Posted until 2026-11-09.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr"/>
+          <t>Broward County BOCC</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>#254409</t>
+        </is>
+      </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>Summer Food Service Program</t>
+          <t>Transit Shelters and Amenities (FTA)</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Concessions &amp; Programs</t>
-        </is>
-      </c>
-      <c r="F516" t="inlineStr">
-        <is>
-          <t>Draft / Future</t>
-        </is>
-      </c>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr"/>
       <c r="G516" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H516" s="5" t="inlineStr"/>
-      <c r="I516" s="3" t="n">
-        <v>46295</v>
-      </c>
+      <c r="I516" s="3" t="inlineStr"/>
       <c r="J516" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8973</t>
+          <t>https://broward.bonfirehub.com/opportunities/254409</t>
         </is>
       </c>
       <c r="K516" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>Draft for feedback. Send comments to Leslie Zambrana (leslie.zambrana@miamidade.gov). Posted until 2026-10-30.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
-        </is>
-      </c>
-      <c r="C517" t="inlineStr"/>
+          <t>Broward County BOCC</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>#236937</t>
+        </is>
+      </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>Third-Party Inspection Services for Elevators, Escalators, and Other Convey</t>
+          <t>Walk-Through Metal Detector Preventive Maintenance and Repair Services</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -27587,111 +27607,99 @@
           <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
-      <c r="F517" t="inlineStr">
-        <is>
-          <t>Draft / Future</t>
-        </is>
-      </c>
+      <c r="F517" t="inlineStr"/>
       <c r="G517" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H517" s="5" t="inlineStr"/>
-      <c r="I517" s="3" t="n">
-        <v>46315</v>
-      </c>
+      <c r="I517" s="3" t="inlineStr"/>
       <c r="J517" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8980</t>
+          <t>https://broward.bonfirehub.com/opportunities/236937</t>
         </is>
       </c>
       <c r="K517" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>Draft for feedback. Send comments to Richard Celestin (richard.celestin@miamidade.gov). Posted until 2026-10-27.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Duval</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
+          <t>JAXPORT</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>E26PM01</t>
+          <t>ITB_EQ-2039A</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>Water Remediation Pool</t>
+          <t>BLOUNT ISLAND MARINE TERMINAL HANJUNG CRANE #8841 REFURBISHMENT</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>Draft / Future</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H518" s="5" t="inlineStr"/>
-      <c r="I518" s="3" t="n">
-        <v>46315</v>
-      </c>
+      <c r="I518" s="3" t="inlineStr"/>
       <c r="J518" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8984</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14412/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K518" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
-        </is>
-      </c>
-      <c r="L518" t="inlineStr">
-        <is>
-          <t>Draft for feedback. Send comments to Julie Whiteside (Julie.whiteside@miamidade.gov). Posted until 2026-11-10.</t>
-        </is>
-      </c>
+          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Duval</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>JAXPORT</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>RFP 26-345</t>
+          <t>RFQ_AE-178DR</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>Advertising &amp; Marketing Services for Visit Central Florida</t>
+          <t>CRANE ENGINEERING SERVICES (REBID)</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -27701,24 +27709,24 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>RFP</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H519" s="5" t="inlineStr"/>
       <c r="I519" s="3" t="inlineStr"/>
       <c r="J519" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-345/</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14356/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K519" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
         </is>
       </c>
       <c r="L519" t="inlineStr"/>
@@ -27726,22 +27734,22 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Duval</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>JAXPORT</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>CS 25-230</t>
+          <t>ITB_MC-2132</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>Asphalt</t>
+          <t>INTSALLATION OF NEW CRANE STOW PIN SOCKETS AT THE TALLEYRAND MARINE TERMINAL (TMT)</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -27749,22 +27757,26 @@
           <t>Construction</t>
         </is>
       </c>
-      <c r="F520" t="inlineStr"/>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>ITB</t>
+        </is>
+      </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H520" s="5" t="inlineStr"/>
       <c r="I520" s="3" t="inlineStr"/>
       <c r="J520" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-25-230/</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14410/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K520" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
         </is>
       </c>
       <c r="L520" t="inlineStr"/>
@@ -27772,22 +27784,22 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Duval</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>JAXPORT</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>CS 24-330</t>
+          <t>PSS # EQ-2128</t>
         </is>
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>Body Shop Services</t>
+          <t>Purchase of three (3) Elevator Safety Devices</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -27795,22 +27807,26 @@
           <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
-      <c r="F521" t="inlineStr"/>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Sole source</t>
+        </is>
+      </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H521" s="5" t="inlineStr"/>
       <c r="I521" s="3" t="inlineStr"/>
       <c r="J521" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-24-330/</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14104/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K521" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
         </is>
       </c>
       <c r="L521" t="inlineStr"/>
@@ -27818,49 +27834,49 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Duval</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>JAXPORT</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>RFP 26-068</t>
+          <t>PSS # MC-2017AJ</t>
         </is>
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>CMAR - Polk County Utilities Northeast Regional Warehouse/Operations Building and Fleet Campus</t>
+          <t>Repair and Replacement of Four (4) Canopies for Jacksonville Port Authority, Dames Point Cruise Terminal</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>RFP</t>
+          <t>Sole source</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H522" s="5" t="inlineStr"/>
       <c r="I522" s="3" t="inlineStr"/>
       <c r="J522" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-068/</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14389/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K522" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
         </is>
       </c>
       <c r="L522" t="inlineStr"/>
@@ -27868,45 +27884,49 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Duval</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>JAXPORT</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Bid 26-395</t>
+          <t>ITB C-2131</t>
         </is>
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>Communication Amplifier Systems</t>
+          <t>TALLEYRAND MARINE TERMINAL (TMT) PILE, CAP, AND BEAM REHAB</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>IT &amp; Technology</t>
-        </is>
-      </c>
-      <c r="F523" t="inlineStr"/>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>ITB</t>
+        </is>
+      </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H523" s="5" t="inlineStr"/>
       <c r="I523" s="3" t="inlineStr"/>
       <c r="J523" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-395/</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14384/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K523" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
         </is>
       </c>
       <c r="L523" t="inlineStr"/>
@@ -27914,45 +27934,49 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Duval</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>JAXPORT</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>CS 24-507</t>
+          <t>ITB_MC-2108N</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>Cremation Services</t>
+          <t>TPO ROOF RETROFITS AT TMT AUTO FACILITY</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
-        </is>
-      </c>
-      <c r="F524" t="inlineStr"/>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>ITB</t>
+        </is>
+      </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H524" s="5" t="inlineStr"/>
       <c r="I524" s="3" t="inlineStr"/>
       <c r="J524" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-24-507/</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14333/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K524" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
         </is>
       </c>
       <c r="L524" t="inlineStr"/>
@@ -27960,49 +27984,49 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Duval</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>JAXPORT</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>RFP 26-320</t>
+          <t>PSS # EQ-2095A</t>
         </is>
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>Engineering Services for Water Infrastructure Repair &amp; Water Quality Improvement Solutions for the Lakeland to Bartow Lake Watershed</t>
+          <t>The purchase of two (2) new-surplus CAT 270-3504 radiator assemblies</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>RFP</t>
+          <t>Sole source</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H525" s="5" t="inlineStr"/>
       <c r="I525" s="3" t="inlineStr"/>
       <c r="J525" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-320/</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14299/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K525" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
         </is>
       </c>
       <c r="L525" t="inlineStr"/>
@@ -28010,22 +28034,22 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>CS 13-294</t>
+          <t>#253223</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>Environmental Lands Site Caretaker</t>
+          <t>Columbus Drive Bridge #105504 Painting and Repair</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -28043,47 +28067,47 @@
       <c r="I526" s="3" t="inlineStr"/>
       <c r="J526" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-13-294/</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/253223</t>
         </is>
       </c>
       <c r="K526" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L526" t="inlineStr"/>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>RFP 26-370</t>
+          <t>#259631</t>
         </is>
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>Grant Administration for Community Development Block Grant (CDBG) Disaster Recovery (DR) Infrastructure Repair Program</t>
+          <t>Community Feral Cat Spay and Neuter Program</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
-        </is>
-      </c>
-      <c r="F527" t="inlineStr">
-        <is>
-          <t>RFP</t>
-        </is>
-      </c>
+          <t>Concessions &amp; Programs</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr"/>
       <c r="G527" t="inlineStr">
         <is>
           <t>Open</t>
@@ -28093,40 +28117,44 @@
       <c r="I527" s="3" t="inlineStr"/>
       <c r="J527" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-370/</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/259631</t>
         </is>
       </c>
       <c r="K527" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L527" t="inlineStr"/>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>CS 20-667</t>
+          <t>#257039</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>Heavy Equipment and Tool Rentals</t>
+          <t>Computer Assisted Mass Appraisal (CAMA) System</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
@@ -28139,40 +28167,44 @@
       <c r="I528" s="3" t="inlineStr"/>
       <c r="J528" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-20-667/</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/257039</t>
         </is>
       </c>
       <c r="K528" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L528" t="inlineStr"/>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>CS 26-296</t>
+          <t>#244837</t>
         </is>
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
-          <t>MUTCD Regulatory &amp; Warning Signs</t>
+          <t>Countywide Fire Hydrant Replacement - WORCS-5</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -28185,40 +28217,44 @@
       <c r="I529" s="3" t="inlineStr"/>
       <c r="J529" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-26-296/</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/244837</t>
         </is>
       </c>
       <c r="K529" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L529" t="inlineStr"/>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Bid 26-367</t>
+          <t>#251575</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>Mowing &amp; Maintenance for Utilities – North Region</t>
+          <t>Intersection Improvements for East County Line Road at Grand Hampton Drive</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -28231,40 +28267,44 @@
       <c r="I530" s="3" t="inlineStr"/>
       <c r="J530" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-367/</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/251575</t>
         </is>
       </c>
       <c r="K530" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L530" t="inlineStr"/>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>CS 24-194</t>
+          <t>#252053</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
-          <t>Overgrowth and Large Lot Clearing</t>
+          <t>Kirby Street Pump Station #08 Rehabilitation</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -28277,40 +28317,44 @@
       <c r="I531" s="3" t="inlineStr"/>
       <c r="J531" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-24-194/</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/252053</t>
         </is>
       </c>
       <c r="K531" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L531" t="inlineStr"/>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>CS 09-007</t>
+          <t>#256978</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>Park Service Residents</t>
+          <t>Laboratory Courier Services</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -28323,35 +28367,39 @@
       <c r="I532" s="3" t="inlineStr"/>
       <c r="J532" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-09-007/</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/256978</t>
         </is>
       </c>
       <c r="K532" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L532" t="inlineStr"/>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Bid 26-349</t>
+          <t>#257045</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>Pond Mowing and Maintenance – Roads and Drainage</t>
+          <t>Lift Station Landscaping Maintenance Services (SBE Set-Aside)</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -28369,40 +28417,44 @@
       <c r="I533" s="3" t="inlineStr"/>
       <c r="J533" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-349/</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/257045</t>
         </is>
       </c>
       <c r="K533" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L533" t="inlineStr"/>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>CS 26-059</t>
+          <t>#244676</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>Protective Footwear for Employees</t>
+          <t>Low Pressure Sewer System Installations and Repairs (WORCS-2)</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -28415,40 +28467,44 @@
       <c r="I534" s="3" t="inlineStr"/>
       <c r="J534" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-26-059/</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/244676</t>
         </is>
       </c>
       <c r="K534" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L534" t="inlineStr"/>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>CS 17-633</t>
+          <t>#251584</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>Radiology Services</t>
+          <t>Misc. Professional Stormwater Services</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -28461,40 +28517,44 @@
       <c r="I535" s="3" t="inlineStr"/>
       <c r="J535" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-17-633/</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/251584</t>
         </is>
       </c>
       <c r="K535" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L535" t="inlineStr"/>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Bid 26-372</t>
+          <t>#248264</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>Saddle Creek New Office and Maintenance Buildings</t>
+          <t>Miscellaneous Construction Engineering and Inspection (CEI) Services - CDBG-DR</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -28507,40 +28567,44 @@
       <c r="I536" s="3" t="inlineStr"/>
       <c r="J536" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-372/</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/248264</t>
         </is>
       </c>
       <c r="K536" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L536" t="inlineStr"/>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>CS 25-463</t>
+          <t>#251576</t>
         </is>
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>Safety Products and Equipment</t>
+          <t>Miscellaneous Parking Lot Repaving Services Term Contract B</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -28553,40 +28617,44 @@
       <c r="I537" s="3" t="inlineStr"/>
       <c r="J537" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-25-463/</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/251576</t>
         </is>
       </c>
       <c r="K537" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L537" t="inlineStr"/>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>CS 25-475</t>
+          <t>#248352</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>Sherwin Williams Paint and Supplies</t>
+          <t>Miscellaneous Subsurface Investigation &amp; Testing</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -28599,40 +28667,44 @@
       <c r="I538" s="3" t="inlineStr"/>
       <c r="J538" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-25-475/</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/248352</t>
         </is>
       </c>
       <c r="K538" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L538" t="inlineStr"/>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>CS 21-380</t>
+          <t>#251655</t>
         </is>
       </c>
       <c r="D539" s="2" t="inlineStr">
         <is>
-          <t>Various Medical Related Supplies</t>
+          <t>R3M Miscellaneous Facilities Construction Term Contract 11</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -28645,18 +28717,2124 @@
       <c r="I539" s="3" t="inlineStr"/>
       <c r="J539" s="4" t="inlineStr">
         <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/251655</t>
+        </is>
+      </c>
+      <c r="K539" s="4" t="inlineStr">
+        <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Hillsborough County BOCC</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>#256945</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
+        <is>
+          <t>Rental of Traffic Control Devices</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr"/>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H540" s="5" t="inlineStr"/>
+      <c r="I540" s="3" t="inlineStr"/>
+      <c r="J540" s="4" t="inlineStr">
+        <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/256945</t>
+        </is>
+      </c>
+      <c r="K540" s="4" t="inlineStr">
+        <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Hillsborough County BOCC</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>#247158</t>
+        </is>
+      </c>
+      <c r="D541" s="2" t="inlineStr">
+        <is>
+          <t>Roadway Resurfacing Repair and Preservation Districts 3&amp;4 WORCS</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr"/>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H541" s="5" t="inlineStr"/>
+      <c r="I541" s="3" t="inlineStr"/>
+      <c r="J541" s="4" t="inlineStr">
+        <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/247158</t>
+        </is>
+      </c>
+      <c r="K541" s="4" t="inlineStr">
+        <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Hillsborough County BOCC</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>#254535</t>
+        </is>
+      </c>
+      <c r="D542" s="2" t="inlineStr">
+        <is>
+          <t>Tire Disposal Services</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr"/>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H542" s="5" t="inlineStr"/>
+      <c r="I542" s="3" t="inlineStr"/>
+      <c r="J542" s="4" t="inlineStr">
+        <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/254535</t>
+        </is>
+      </c>
+      <c r="K542" s="4" t="inlineStr">
+        <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Hillsborough County BOCC</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>#258220</t>
+        </is>
+      </c>
+      <c r="D543" s="2" t="inlineStr">
+        <is>
+          <t>Uniforms and Protective Clothing</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr"/>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H543" s="5" t="inlineStr"/>
+      <c r="I543" s="3" t="inlineStr"/>
+      <c r="J543" s="4" t="inlineStr">
+        <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/258220</t>
+        </is>
+      </c>
+      <c r="K543" s="4" t="inlineStr">
+        <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Hillsborough County BOCC</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>#252215</t>
+        </is>
+      </c>
+      <c r="D544" s="2" t="inlineStr">
+        <is>
+          <t>Valrico Reclaimed Water Facility Diesel Generator Project</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr"/>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H544" s="5" t="inlineStr"/>
+      <c r="I544" s="3" t="inlineStr"/>
+      <c r="J544" s="4" t="inlineStr">
+        <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/252215</t>
+        </is>
+      </c>
+      <c r="K544" s="4" t="inlineStr">
+        <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Hillsborough County BOCC</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>#257371</t>
+        </is>
+      </c>
+      <c r="D545" s="2" t="inlineStr">
+        <is>
+          <t>Various Fleet Vehicles and Equipment</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr"/>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H545" s="5" t="inlineStr"/>
+      <c r="I545" s="3" t="inlineStr"/>
+      <c r="J545" s="4" t="inlineStr">
+        <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/257371</t>
+        </is>
+      </c>
+      <c r="K545" s="4" t="inlineStr">
+        <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Hillsborough County BOCC</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>#254487</t>
+        </is>
+      </c>
+      <c r="D546" s="2" t="inlineStr">
+        <is>
+          <t>Waters Avenue Force Main Replacement CEI Services</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr"/>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H546" s="5" t="inlineStr"/>
+      <c r="I546" s="3" t="inlineStr"/>
+      <c r="J546" s="4" t="inlineStr">
+        <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/254487</t>
+        </is>
+      </c>
+      <c r="K546" s="4" t="inlineStr">
+        <is>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Miami-Dade</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>A26PM01</t>
+        </is>
+      </c>
+      <c r="D547" s="2" t="inlineStr">
+        <is>
+          <t>A/E Services for Real Estate</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Draft / Future</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H547" s="5" t="inlineStr"/>
+      <c r="I547" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="J547" s="4" t="inlineStr">
+        <is>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8983</t>
+        </is>
+      </c>
+      <c r="K547" s="4" t="inlineStr">
+        <is>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>Draft for feedback. Send comments to Julie Whiteside (Julie.whiteside@miamidade.gov). Posted until 2026-11-10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Miami-Dade</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr"/>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>Access Control Point Barrier Systems</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>IT &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Draft / Future</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H548" s="5" t="inlineStr"/>
+      <c r="I548" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="J548" s="4" t="inlineStr">
+        <is>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8975</t>
+        </is>
+      </c>
+      <c r="K548" s="4" t="inlineStr">
+        <is>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>Draft for feedback. Send comments to Amy Almanzar (Amy.almanzar@miamidade.gov). Posted until 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Miami-Dade</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr"/>
+      <c r="D549" s="2" t="inlineStr">
+        <is>
+          <t>E26WS02 - REPOST - GEOTECHNICAL SRVS, STRUCTURAL ASSESSMENT, MATERIALS TEST</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Draft / Future</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H549" s="5" t="inlineStr"/>
+      <c r="I549" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="J549" s="4" t="inlineStr">
+        <is>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8981</t>
+        </is>
+      </c>
+      <c r="K549" s="4" t="inlineStr">
+        <is>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>Draft for feedback. Send comments to Ana M. DaSilva (ana.dasilva@miamidade.gov). Posted until 2026-11-09.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Miami-Dade</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr"/>
+      <c r="D550" s="2" t="inlineStr">
+        <is>
+          <t>Summer Food Service Program</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Concessions &amp; Programs</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Draft / Future</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H550" s="5" t="inlineStr"/>
+      <c r="I550" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J550" s="4" t="inlineStr">
+        <is>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8973</t>
+        </is>
+      </c>
+      <c r="K550" s="4" t="inlineStr">
+        <is>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>Draft for feedback. Send comments to Leslie Zambrana (leslie.zambrana@miamidade.gov). Posted until 2026-10-30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Miami-Dade</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr"/>
+      <c r="D551" s="2" t="inlineStr">
+        <is>
+          <t>Third-Party Inspection Services for Elevators, Escalators, and Other Convey</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Draft / Future</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H551" s="5" t="inlineStr"/>
+      <c r="I551" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="J551" s="4" t="inlineStr">
+        <is>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8980</t>
+        </is>
+      </c>
+      <c r="K551" s="4" t="inlineStr">
+        <is>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>Draft for feedback. Send comments to Richard Celestin (richard.celestin@miamidade.gov). Posted until 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Miami-Dade</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>E26PM01</t>
+        </is>
+      </c>
+      <c r="D552" s="2" t="inlineStr">
+        <is>
+          <t>Water Remediation Pool</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Draft / Future</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H552" s="5" t="inlineStr"/>
+      <c r="I552" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="J552" s="4" t="inlineStr">
+        <is>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8984</t>
+        </is>
+      </c>
+      <c r="K552" s="4" t="inlineStr">
+        <is>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>Draft for feedback. Send comments to Julie Whiteside (Julie.whiteside@miamidade.gov). Posted until 2026-11-10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Monroe</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Monroe County BOCC</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>#257290</t>
+        </is>
+      </c>
+      <c r="D553" s="2" t="inlineStr">
+        <is>
+          <t>Construction, Engineering and Inspection Services for Key Deer Blvd (North of Watson Blvd) Roadway Rehabilitation Project</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr"/>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H553" s="5" t="inlineStr"/>
+      <c r="I553" s="3" t="inlineStr"/>
+      <c r="J553" s="4" t="inlineStr">
+        <is>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/257290</t>
+        </is>
+      </c>
+      <c r="K553" s="4" t="inlineStr">
+        <is>
+          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Monroe</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Monroe County BOCC</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>#259466</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="inlineStr">
+        <is>
+          <t>Ellis Building Interior Renovation</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr"/>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H554" s="5" t="inlineStr"/>
+      <c r="I554" s="3" t="inlineStr"/>
+      <c r="J554" s="4" t="inlineStr">
+        <is>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/259466</t>
+        </is>
+      </c>
+      <c r="K554" s="4" t="inlineStr">
+        <is>
+          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Monroe</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Monroe County BOCC</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>#256505</t>
+        </is>
+      </c>
+      <c r="D555" s="2" t="inlineStr">
+        <is>
+          <t>Latin America Sales Agency for Monroe County Tourist Development Council</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr"/>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H555" s="5" t="inlineStr"/>
+      <c r="I555" s="3" t="inlineStr"/>
+      <c r="J555" s="4" t="inlineStr">
+        <is>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/256505</t>
+        </is>
+      </c>
+      <c r="K555" s="4" t="inlineStr">
+        <is>
+          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Monroe</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Monroe County BOCC</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>#235838</t>
+        </is>
+      </c>
+      <c r="D556" s="2" t="inlineStr">
+        <is>
+          <t>Multifamily SHIP Application 2025 RFA</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>IT &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr"/>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H556" s="5" t="inlineStr"/>
+      <c r="I556" s="3" t="inlineStr"/>
+      <c r="J556" s="4" t="inlineStr">
+        <is>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/235838</t>
+        </is>
+      </c>
+      <c r="K556" s="4" t="inlineStr">
+        <is>
+          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Monroe</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Monroe County BOCC</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>#256340</t>
+        </is>
+      </c>
+      <c r="D557" s="2" t="inlineStr">
+        <is>
+          <t>Professional Architectural and Engineering Continuing Services</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr"/>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H557" s="5" t="inlineStr"/>
+      <c r="I557" s="3" t="inlineStr"/>
+      <c r="J557" s="4" t="inlineStr">
+        <is>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/256340</t>
+        </is>
+      </c>
+      <c r="K557" s="4" t="inlineStr">
+        <is>
+          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Monroe</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Monroe County BOCC</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>#255496</t>
+        </is>
+      </c>
+      <c r="D558" s="2" t="inlineStr">
+        <is>
+          <t>Professional Surveying Continuing Services</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr"/>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H558" s="5" t="inlineStr"/>
+      <c r="I558" s="3" t="inlineStr"/>
+      <c r="J558" s="4" t="inlineStr">
+        <is>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/255496</t>
+        </is>
+      </c>
+      <c r="K558" s="4" t="inlineStr">
+        <is>
+          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Pasco</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Pasco County BOCC</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>#259647</t>
+        </is>
+      </c>
+      <c r="D559" s="2" t="inlineStr">
+        <is>
+          <t>BEXLEY ELEMENTARY SIDEWALK PROJECT (BALLANTRAE BLVD FROM STRATON PL TO BUD BEXLEY PKWY)</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr"/>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H559" s="5" t="inlineStr"/>
+      <c r="I559" s="3" t="inlineStr"/>
+      <c r="J559" s="4" t="inlineStr">
+        <is>
+          <t>https://pascocountyfl.bonfirehub.com/opportunities/259647</t>
+        </is>
+      </c>
+      <c r="K559" s="4" t="inlineStr">
+        <is>
+          <t>https://pascocountyfl.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Pasco</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Pasco County BOCC</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>#255847</t>
+        </is>
+      </c>
+      <c r="D560" s="2" t="inlineStr">
+        <is>
+          <t>BYRD DR. AND GUNN HIGHWAY INTERSECTION IMPROVEMENTS</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr"/>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H560" s="5" t="inlineStr"/>
+      <c r="I560" s="3" t="inlineStr"/>
+      <c r="J560" s="4" t="inlineStr">
+        <is>
+          <t>https://pascocountyfl.bonfirehub.com/opportunities/255847</t>
+        </is>
+      </c>
+      <c r="K560" s="4" t="inlineStr">
+        <is>
+          <t>https://pascocountyfl.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Pasco</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Pasco County BOCC</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>#255633</t>
+        </is>
+      </c>
+      <c r="D561" s="2" t="inlineStr">
+        <is>
+          <t>EILAND BOULEVARD AND SILVERADO RANCH BOULEVARD/RYALS ROAD INTERSECTION SIGNALIZATION</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr"/>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H561" s="5" t="inlineStr"/>
+      <c r="I561" s="3" t="inlineStr"/>
+      <c r="J561" s="4" t="inlineStr">
+        <is>
+          <t>https://pascocountyfl.bonfirehub.com/opportunities/255633</t>
+        </is>
+      </c>
+      <c r="K561" s="4" t="inlineStr">
+        <is>
+          <t>https://pascocountyfl.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>RFP 26-345</t>
+        </is>
+      </c>
+      <c r="D562" s="2" t="inlineStr">
+        <is>
+          <t>Advertising &amp; Marketing Services for Visit Central Florida</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Consulting &amp; Professional Services</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>RFP</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H562" s="5" t="inlineStr"/>
+      <c r="I562" s="3" t="inlineStr"/>
+      <c r="J562" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-345/</t>
+        </is>
+      </c>
+      <c r="K562" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>CS 25-230</t>
+        </is>
+      </c>
+      <c r="D563" s="2" t="inlineStr">
+        <is>
+          <t>Asphalt</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr"/>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H563" s="5" t="inlineStr"/>
+      <c r="I563" s="3" t="inlineStr"/>
+      <c r="J563" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/cs-25-230/</t>
+        </is>
+      </c>
+      <c r="K563" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>CS 24-330</t>
+        </is>
+      </c>
+      <c r="D564" s="2" t="inlineStr">
+        <is>
+          <t>Body Shop Services</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr"/>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H564" s="5" t="inlineStr"/>
+      <c r="I564" s="3" t="inlineStr"/>
+      <c r="J564" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/cs-24-330/</t>
+        </is>
+      </c>
+      <c r="K564" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>RFP 26-068</t>
+        </is>
+      </c>
+      <c r="D565" s="2" t="inlineStr">
+        <is>
+          <t>CMAR - Polk County Utilities Northeast Regional Warehouse/Operations Building and Fleet Campus</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>RFP</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H565" s="5" t="inlineStr"/>
+      <c r="I565" s="3" t="inlineStr"/>
+      <c r="J565" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-068/</t>
+        </is>
+      </c>
+      <c r="K565" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Bid 26-395</t>
+        </is>
+      </c>
+      <c r="D566" s="2" t="inlineStr">
+        <is>
+          <t>Communication Amplifier Systems</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>IT &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr"/>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H566" s="5" t="inlineStr"/>
+      <c r="I566" s="3" t="inlineStr"/>
+      <c r="J566" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/bid-26-395/</t>
+        </is>
+      </c>
+      <c r="K566" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>CS 24-507</t>
+        </is>
+      </c>
+      <c r="D567" s="2" t="inlineStr">
+        <is>
+          <t>Cremation Services</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Consulting &amp; Professional Services</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr"/>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H567" s="5" t="inlineStr"/>
+      <c r="I567" s="3" t="inlineStr"/>
+      <c r="J567" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/cs-24-507/</t>
+        </is>
+      </c>
+      <c r="K567" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>RFP 26-320</t>
+        </is>
+      </c>
+      <c r="D568" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Services for Water Infrastructure Repair &amp; Water Quality Improvement Solutions for the Lakeland to Bartow Lake Watershed</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>RFP</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H568" s="5" t="inlineStr"/>
+      <c r="I568" s="3" t="inlineStr"/>
+      <c r="J568" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-320/</t>
+        </is>
+      </c>
+      <c r="K568" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>CS 13-294</t>
+        </is>
+      </c>
+      <c r="D569" s="2" t="inlineStr">
+        <is>
+          <t>Environmental Lands Site Caretaker</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr"/>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H569" s="5" t="inlineStr"/>
+      <c r="I569" s="3" t="inlineStr"/>
+      <c r="J569" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/cs-13-294/</t>
+        </is>
+      </c>
+      <c r="K569" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>RFP 26-370</t>
+        </is>
+      </c>
+      <c r="D570" s="2" t="inlineStr">
+        <is>
+          <t>Grant Administration for Community Development Block Grant (CDBG) Disaster Recovery (DR) Infrastructure Repair Program</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Consulting &amp; Professional Services</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>RFP</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H570" s="5" t="inlineStr"/>
+      <c r="I570" s="3" t="inlineStr"/>
+      <c r="J570" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-370/</t>
+        </is>
+      </c>
+      <c r="K570" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>CS 20-667</t>
+        </is>
+      </c>
+      <c r="D571" s="2" t="inlineStr">
+        <is>
+          <t>Heavy Equipment and Tool Rentals</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr"/>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H571" s="5" t="inlineStr"/>
+      <c r="I571" s="3" t="inlineStr"/>
+      <c r="J571" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/cs-20-667/</t>
+        </is>
+      </c>
+      <c r="K571" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>CS 26-296</t>
+        </is>
+      </c>
+      <c r="D572" s="2" t="inlineStr">
+        <is>
+          <t>MUTCD Regulatory &amp; Warning Signs</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr"/>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H572" s="5" t="inlineStr"/>
+      <c r="I572" s="3" t="inlineStr"/>
+      <c r="J572" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/cs-26-296/</t>
+        </is>
+      </c>
+      <c r="K572" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Bid 26-367</t>
+        </is>
+      </c>
+      <c r="D573" s="2" t="inlineStr">
+        <is>
+          <t>Mowing &amp; Maintenance for Utilities – North Region</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr"/>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H573" s="5" t="inlineStr"/>
+      <c r="I573" s="3" t="inlineStr"/>
+      <c r="J573" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/bid-26-367/</t>
+        </is>
+      </c>
+      <c r="K573" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>CS 24-194</t>
+        </is>
+      </c>
+      <c r="D574" s="2" t="inlineStr">
+        <is>
+          <t>Overgrowth and Large Lot Clearing</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr"/>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H574" s="5" t="inlineStr"/>
+      <c r="I574" s="3" t="inlineStr"/>
+      <c r="J574" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/cs-24-194/</t>
+        </is>
+      </c>
+      <c r="K574" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>CS 09-007</t>
+        </is>
+      </c>
+      <c r="D575" s="2" t="inlineStr">
+        <is>
+          <t>Park Service Residents</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr"/>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H575" s="5" t="inlineStr"/>
+      <c r="I575" s="3" t="inlineStr"/>
+      <c r="J575" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/cs-09-007/</t>
+        </is>
+      </c>
+      <c r="K575" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Bid 26-349</t>
+        </is>
+      </c>
+      <c r="D576" s="2" t="inlineStr">
+        <is>
+          <t>Pond Mowing and Maintenance – Roads and Drainage</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr"/>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H576" s="5" t="inlineStr"/>
+      <c r="I576" s="3" t="inlineStr"/>
+      <c r="J576" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/bid-26-349/</t>
+        </is>
+      </c>
+      <c r="K576" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>CS 26-059</t>
+        </is>
+      </c>
+      <c r="D577" s="2" t="inlineStr">
+        <is>
+          <t>Protective Footwear for Employees</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr"/>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H577" s="5" t="inlineStr"/>
+      <c r="I577" s="3" t="inlineStr"/>
+      <c r="J577" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/cs-26-059/</t>
+        </is>
+      </c>
+      <c r="K577" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>CS 17-633</t>
+        </is>
+      </c>
+      <c r="D578" s="2" t="inlineStr">
+        <is>
+          <t>Radiology Services</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Consulting &amp; Professional Services</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr"/>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H578" s="5" t="inlineStr"/>
+      <c r="I578" s="3" t="inlineStr"/>
+      <c r="J578" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/cs-17-633/</t>
+        </is>
+      </c>
+      <c r="K578" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Bid 26-372</t>
+        </is>
+      </c>
+      <c r="D579" s="2" t="inlineStr">
+        <is>
+          <t>Saddle Creek New Office and Maintenance Buildings</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr"/>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H579" s="5" t="inlineStr"/>
+      <c r="I579" s="3" t="inlineStr"/>
+      <c r="J579" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/bid-26-372/</t>
+        </is>
+      </c>
+      <c r="K579" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>CS 25-463</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>Safety Products and Equipment</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr"/>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H580" s="5" t="inlineStr"/>
+      <c r="I580" s="3" t="inlineStr"/>
+      <c r="J580" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/cs-25-463/</t>
+        </is>
+      </c>
+      <c r="K580" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>CS 25-475</t>
+        </is>
+      </c>
+      <c r="D581" s="2" t="inlineStr">
+        <is>
+          <t>Sherwin Williams Paint and Supplies</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr"/>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H581" s="5" t="inlineStr"/>
+      <c r="I581" s="3" t="inlineStr"/>
+      <c r="J581" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/cs-25-475/</t>
+        </is>
+      </c>
+      <c r="K581" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>CS 21-380</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>Various Medical Related Supplies</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr"/>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H582" s="5" t="inlineStr"/>
+      <c r="I582" s="3" t="inlineStr"/>
+      <c r="J582" s="4" t="inlineStr">
+        <is>
           <t>https://www.polkfl.gov/bid-form/cs-21-380/</t>
         </is>
       </c>
-      <c r="K539" s="4" t="inlineStr">
+      <c r="K582" s="4" t="inlineStr">
         <is>
           <t>https://www.polkfl.gov/business/procurement/</t>
         </is>
       </c>
-      <c r="L539" t="inlineStr"/>
+      <c r="L582" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L539"/>
+  <autoFilter ref="A1:L582"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId2"/>
@@ -29464,8 +31642,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K412" r:id="rId804"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J413" r:id="rId805"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K413" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K414" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J415" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J414" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K414" r:id="rId808"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K415" r:id="rId809"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J416" r:id="rId810"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K416" r:id="rId811"/>
@@ -29515,8 +31693,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K438" r:id="rId855"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J439" r:id="rId856"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K439" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K440" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J441" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J440" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K440" r:id="rId859"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K441" r:id="rId860"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J442" r:id="rId861"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K442" r:id="rId862"/>
@@ -29528,8 +31706,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K445" r:id="rId868"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J446" r:id="rId869"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K446" r:id="rId870"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K447" r:id="rId871"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J448" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J447" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K447" r:id="rId872"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K448" r:id="rId873"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J449" r:id="rId874"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K449" r:id="rId875"/>
@@ -29583,8 +31761,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K473" r:id="rId923"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J474" r:id="rId924"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K474" r:id="rId925"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K475" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J476" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J475" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K475" r:id="rId927"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K476" r:id="rId928"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J477" r:id="rId929"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K477" r:id="rId930"/>
@@ -29594,10 +31772,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K479" r:id="rId934"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J480" r:id="rId935"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K480" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K481" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J482" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K482" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J483" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J481" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K481" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J482" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K482" r:id="rId940"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K483" r:id="rId941"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J484" r:id="rId942"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K484" r:id="rId943"/>
@@ -29711,6 +31889,92 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K538" r:id="rId1051"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J539" r:id="rId1052"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K539" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J540" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K540" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J541" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K541" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J542" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K542" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J543" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K543" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J544" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K544" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J545" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K545" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J546" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K546" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J547" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K547" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J548" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K548" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J549" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K549" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J550" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K550" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J551" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K551" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J552" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K552" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J553" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K553" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J554" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K554" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J555" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K555" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J556" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K556" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J557" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K557" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J558" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K558" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J559" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K559" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J560" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K560" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J561" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K561" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J562" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K562" r:id="rId1099"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J563" r:id="rId1100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K563" r:id="rId1101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J564" r:id="rId1102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K564" r:id="rId1103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J565" r:id="rId1104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K565" r:id="rId1105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J566" r:id="rId1106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K566" r:id="rId1107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J567" r:id="rId1108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K567" r:id="rId1109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J568" r:id="rId1110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K568" r:id="rId1111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J569" r:id="rId1112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K569" r:id="rId1113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J570" r:id="rId1114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K570" r:id="rId1115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J571" r:id="rId1116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K571" r:id="rId1117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J572" r:id="rId1118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K572" r:id="rId1119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J573" r:id="rId1120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K573" r:id="rId1121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J574" r:id="rId1122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K574" r:id="rId1123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J575" r:id="rId1124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K575" r:id="rId1125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J576" r:id="rId1126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K576" r:id="rId1127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J577" r:id="rId1128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K577" r:id="rId1129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J578" r:id="rId1130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K578" r:id="rId1131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J579" r:id="rId1132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K579" r:id="rId1133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J580" r:id="rId1134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K580" r:id="rId1135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J581" r:id="rId1136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K581" r:id="rId1137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J582" r:id="rId1138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K582" r:id="rId1139"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29735,7 +31999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 2026-10-25 12:24 AM (Eastern time)</t>
+          <t>Updated 2026-10-25 10:26 AM (Eastern time)</t>
         </is>
       </c>
     </row>

--- a/site/data/florida-open-bids.xlsx
+++ b/site/data/florida-open-bids.xlsx
@@ -30005,7 +30005,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 2026-10-25 12:14 PM (Eastern time)</t>
+          <t>Updated 2026-10-25 01:22 PM (Eastern time)</t>
         </is>
       </c>
     </row>

--- a/site/data/florida-open-bids.xlsx
+++ b/site/data/florida-open-bids.xlsx
@@ -31175,7 +31175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 2026-10-25 02:39 PM (Eastern time)</t>
+          <t>Updated 2026-10-26 11:06 AM (Eastern time)</t>
         </is>
       </c>
     </row>

--- a/site/data/florida-open-bids.xlsx
+++ b/site/data/florida-open-bids.xlsx
@@ -31175,7 +31175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 2026-10-26 11:06 AM (Eastern time)</t>
+          <t>Updated 2026-10-26 11:08 AM (Eastern time)</t>
         </is>
       </c>
     </row>

--- a/site/data/florida-open-bids.xlsx
+++ b/site/data/florida-open-bids.xlsx
@@ -31175,7 +31175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 2026-10-26 11:08 AM (Eastern time)</t>
+          <t>Updated 2026-10-26 11:30 AM (Eastern time)</t>
         </is>
       </c>
     </row>

--- a/site/data/florida-open-bids.xlsx
+++ b/site/data/florida-open-bids.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Open solicitations'!$A$1:$L$571</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Open solicitations'!$A$1:$L$580</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L571"/>
+  <dimension ref="A1:L580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -25385,29 +25385,25 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Broward County BOCC</t>
+          <t>City of Hollywood</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Draft TRN2131593P1</t>
+          <t>#319675</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>Pre-Solicitation Notice - Draft Computer Aided Dispatch/Automatic Vehicle Location System</t>
+          <t>Meter Transmission Unit / VertexOne Consumer Portal</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>IT &amp; Technology</t>
-        </is>
-      </c>
-      <c r="F477" t="inlineStr">
-        <is>
-          <t>Draft / Future</t>
-        </is>
-      </c>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr"/>
       <c r="G477" t="inlineStr">
         <is>
           <t>Open</t>
@@ -25417,12 +25413,12 @@
       <c r="I477" s="3" t="inlineStr"/>
       <c r="J477" s="4" t="inlineStr">
         <is>
-          <t>https://broward.bonfirehub.com/opportunities/254086</t>
+          <t>https://procurement.opengov.com/portal/hollywoodfl/projects/319675</t>
         </is>
       </c>
       <c r="K477" s="4" t="inlineStr">
         <is>
-          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://procurement.opengov.com/portal/hollywoodfl</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
@@ -25444,22 +25440,22 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Public Notice</t>
+          <t>Draft TRN2131593P1</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>Public Notice: West Copans Rehabilitation and Redevelopment Project</t>
+          <t>Pre-Solicitation Notice - Draft Computer Aided Dispatch/Automatic Vehicle Location System</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Property &amp; Real Estate</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>Notice</t>
+          <t>Draft / Future</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
@@ -25471,7 +25467,7 @@
       <c r="I478" s="3" t="inlineStr"/>
       <c r="J478" s="4" t="inlineStr">
         <is>
-          <t>https://broward.bonfirehub.com/opportunities/243763</t>
+          <t>https://broward.bonfirehub.com/opportunities/254086</t>
         </is>
       </c>
       <c r="K478" s="4" t="inlineStr">
@@ -25498,22 +25494,22 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>TCH2133145F1</t>
+          <t>Public Notice</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>Request for Information - Algo Communications – Airport Mass Notification System</t>
+          <t>Public Notice: West Copans Rehabilitation and Redevelopment Project</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>IT &amp; Technology</t>
+          <t>Property &amp; Real Estate</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>RFI</t>
+          <t>Notice</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
@@ -25525,7 +25521,7 @@
       <c r="I479" s="3" t="inlineStr"/>
       <c r="J479" s="4" t="inlineStr">
         <is>
-          <t>https://broward.bonfirehub.com/opportunities/258935</t>
+          <t>https://broward.bonfirehub.com/opportunities/243763</t>
         </is>
       </c>
       <c r="K479" s="4" t="inlineStr">
@@ -25552,12 +25548,12 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>TCH2133147F1</t>
+          <t>TCH2133145F1</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>Request for Information - Genea Security Access Control System</t>
+          <t>Request for Information - Algo Communications – Airport Mass Notification System</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -25579,7 +25575,7 @@
       <c r="I480" s="3" t="inlineStr"/>
       <c r="J480" s="4" t="inlineStr">
         <is>
-          <t>https://broward.bonfirehub.com/opportunities/258937</t>
+          <t>https://broward.bonfirehub.com/opportunities/258935</t>
         </is>
       </c>
       <c r="K480" s="4" t="inlineStr">
@@ -25606,12 +25602,12 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>TCH2133148F1</t>
+          <t>TCH2133147F1</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>Request for Information - OpenEye – CCTV Recording and Analytics</t>
+          <t>Request for Information - Genea Security Access Control System</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -25633,7 +25629,7 @@
       <c r="I481" s="3" t="inlineStr"/>
       <c r="J481" s="4" t="inlineStr">
         <is>
-          <t>https://broward.bonfirehub.com/opportunities/258942</t>
+          <t>https://broward.bonfirehub.com/opportunities/258937</t>
         </is>
       </c>
       <c r="K481" s="4" t="inlineStr">
@@ -25660,12 +25656,12 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>TCH2133146F1</t>
+          <t>TCH2133148F1</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>Request for Information - Verkada – CCTV System</t>
+          <t>Request for Information - OpenEye – CCTV Recording and Analytics</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -25687,7 +25683,7 @@
       <c r="I482" s="3" t="inlineStr"/>
       <c r="J482" s="4" t="inlineStr">
         <is>
-          <t>https://broward.bonfirehub.com/opportunities/258939</t>
+          <t>https://broward.bonfirehub.com/opportunities/258942</t>
         </is>
       </c>
       <c r="K482" s="4" t="inlineStr">
@@ -25714,20 +25710,24 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>TRN2132943B1</t>
+          <t>TCH2133146F1</t>
         </is>
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>Transit Bus Stop ADA Improvements (FTA)</t>
+          <t>Request for Information - Verkada – CCTV System</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F483" t="inlineStr"/>
+          <t>IT &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>RFI</t>
+        </is>
+      </c>
       <c r="G483" t="inlineStr">
         <is>
           <t>Open</t>
@@ -25737,7 +25737,7 @@
       <c r="I483" s="3" t="inlineStr"/>
       <c r="J483" s="4" t="inlineStr">
         <is>
-          <t>https://broward.bonfirehub.com/opportunities/253591</t>
+          <t>https://broward.bonfirehub.com/opportunities/258939</t>
         </is>
       </c>
       <c r="K483" s="4" t="inlineStr">
@@ -25764,12 +25764,12 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>TRN2133001B1</t>
+          <t>TRN2132943B1</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>Transit Shelters and Amenities (FTA)</t>
+          <t>Transit Bus Stop ADA Improvements (FTA)</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -25787,7 +25787,7 @@
       <c r="I484" s="3" t="inlineStr"/>
       <c r="J484" s="4" t="inlineStr">
         <is>
-          <t>https://broward.bonfirehub.com/opportunities/254409</t>
+          <t>https://broward.bonfirehub.com/opportunities/253591</t>
         </is>
       </c>
       <c r="K484" s="4" t="inlineStr">
@@ -25814,17 +25814,17 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>BLD2132313B1</t>
+          <t>TRN2133001B1</t>
         </is>
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>Walk-Through Metal Detector Preventive Maintenance and Repair Services</t>
+          <t>Transit Shelters and Amenities (FTA)</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -25837,7 +25837,7 @@
       <c r="I485" s="3" t="inlineStr"/>
       <c r="J485" s="4" t="inlineStr">
         <is>
-          <t>https://broward.bonfirehub.com/opportunities/236937</t>
+          <t>https://broward.bonfirehub.com/opportunities/254409</t>
         </is>
       </c>
       <c r="K485" s="4" t="inlineStr">
@@ -25854,152 +25854,152 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Duval</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>JAXPORT</t>
+          <t>Broward County BOCC</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>ITB_EQ-2039A</t>
+          <t>BLD2132313B1</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>BLOUNT ISLAND MARINE TERMINAL HANJUNG CRANE #8841 REFURBISHMENT</t>
+          <t>Walk-Through Metal Detector Preventive Maintenance and Repair Services</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F486" t="inlineStr">
-        <is>
-          <t>ITB</t>
-        </is>
-      </c>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr"/>
       <c r="G486" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H486" s="5" t="inlineStr"/>
       <c r="I486" s="3" t="inlineStr"/>
       <c r="J486" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14412/?sort%5B7%5D=asc</t>
+          <t>https://broward.bonfirehub.com/opportunities/236937</t>
         </is>
       </c>
       <c r="K486" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
-        </is>
-      </c>
-      <c r="L486" t="inlineStr"/>
+          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Duval</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>JAXPORT</t>
+          <t>City of Hollywood</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>RFQ_AE-178DR</t>
+          <t>#313307</t>
         </is>
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>CRANE ENGINEERING SERVICES (REBID)</t>
+          <t>Water Treatment Plant MS/RO Chemical Area Recoating; Project No. 25-4262A</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
-        </is>
-      </c>
-      <c r="F487" t="inlineStr">
-        <is>
-          <t>ITB</t>
-        </is>
-      </c>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr"/>
       <c r="G487" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H487" s="5" t="inlineStr"/>
       <c r="I487" s="3" t="inlineStr"/>
       <c r="J487" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14356/?sort%5B7%5D=asc</t>
+          <t>https://procurement.opengov.com/portal/hollywoodfl/projects/313307</t>
         </is>
       </c>
       <c r="K487" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
-        </is>
-      </c>
-      <c r="L487" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/hollywoodfl</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Duval</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>JAXPORT</t>
+          <t>City of Hollywood</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>ITB_MC-2132</t>
+          <t>#313241</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>INTSALLATION OF NEW CRANE STOW PIN SOCKETS AT THE TALLEYRAND MARINE TERMINAL (TMT)</t>
+          <t>Water Treatment Plant Maintenance Package 'B'; Project No. 25-4262</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F488" t="inlineStr">
-        <is>
-          <t>ITB</t>
-        </is>
-      </c>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr"/>
       <c r="G488" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H488" s="5" t="inlineStr"/>
       <c r="I488" s="3" t="inlineStr"/>
       <c r="J488" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14410/?sort%5B7%5D=asc</t>
+          <t>https://procurement.opengov.com/portal/hollywoodfl/projects/313241</t>
         </is>
       </c>
       <c r="K488" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
-        </is>
-      </c>
-      <c r="L488" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/hollywoodfl</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -26014,22 +26014,22 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>PSS # EQ-2128</t>
+          <t>ITB_EQ-2039A</t>
         </is>
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>Purchase of three (3) Elevator Safety Devices</t>
+          <t>BLOUNT ISLAND MARINE TERMINAL HANJUNG CRANE #8841 REFURBISHMENT</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>Sole source</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
@@ -26041,7 +26041,7 @@
       <c r="I489" s="3" t="inlineStr"/>
       <c r="J489" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14104/?sort%5B7%5D=asc</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14412/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K489" s="4" t="inlineStr">
@@ -26064,22 +26064,22 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>PSS # MC-2017AJ</t>
+          <t>RFQ_AE-178DR</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>Repair and Replacement of Four (4) Canopies for Jacksonville Port Authority, Dames Point Cruise Terminal</t>
+          <t>CRANE ENGINEERING SERVICES (REBID)</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>Sole source</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
@@ -26091,7 +26091,7 @@
       <c r="I490" s="3" t="inlineStr"/>
       <c r="J490" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14389/?sort%5B7%5D=asc</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14356/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K490" s="4" t="inlineStr">
@@ -26114,12 +26114,12 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>ITB C-2131</t>
+          <t>ITB_MC-2132</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>TALLEYRAND MARINE TERMINAL (TMT) PILE, CAP, AND BEAM REHAB</t>
+          <t>INTSALLATION OF NEW CRANE STOW PIN SOCKETS AT THE TALLEYRAND MARINE TERMINAL (TMT)</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -26141,7 +26141,7 @@
       <c r="I491" s="3" t="inlineStr"/>
       <c r="J491" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14384/?sort%5B7%5D=asc</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14410/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K491" s="4" t="inlineStr">
@@ -26164,22 +26164,22 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>ITB_MC-2108N</t>
+          <t>PSS # EQ-2128</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>TPO ROOF RETROFITS AT TMT AUTO FACILITY</t>
+          <t>Purchase of three (3) Elevator Safety Devices</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>Sole source</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
@@ -26191,7 +26191,7 @@
       <c r="I492" s="3" t="inlineStr"/>
       <c r="J492" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14333/?sort%5B7%5D=asc</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14104/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K492" s="4" t="inlineStr">
@@ -26214,17 +26214,17 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>PSS # EQ-2095A</t>
+          <t>PSS # MC-2017AJ</t>
         </is>
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>The purchase of two (2) new-surplus CAT 270-3504 radiator assemblies</t>
+          <t>Repair and Replacement of Four (4) Canopies for Jacksonville Port Authority, Dames Point Cruise Terminal</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
@@ -26241,7 +26241,7 @@
       <c r="I493" s="3" t="inlineStr"/>
       <c r="J493" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14299/?sort%5B7%5D=asc</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14389/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K493" s="4" t="inlineStr">
@@ -26254,152 +26254,152 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Duval</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Hillsborough County BOCC</t>
+          <t>JAXPORT</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>IFB-26-00413</t>
+          <t>ITB C-2131</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>Columbus Drive Bridge #105504 Painting and Repair</t>
+          <t>TALLEYRAND MARINE TERMINAL (TMT) PILE, CAP, AND BEAM REHAB</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="F494" t="inlineStr"/>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>ITB</t>
+        </is>
+      </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H494" s="5" t="inlineStr"/>
       <c r="I494" s="3" t="inlineStr"/>
       <c r="J494" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/253223</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14384/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K494" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
-        </is>
-      </c>
-      <c r="L494" t="inlineStr">
-        <is>
-          <t>From the agency's email alert.</t>
-        </is>
-      </c>
+          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Duval</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Hillsborough County BOCC</t>
+          <t>JAXPORT</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>ITB-27-00018</t>
+          <t>ITB_MC-2108N</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>Community Feral Cat Spay and Neuter Program</t>
+          <t>TPO ROOF RETROFITS AT TMT AUTO FACILITY</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Concessions &amp; Programs</t>
-        </is>
-      </c>
-      <c r="F495" t="inlineStr"/>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>ITB</t>
+        </is>
+      </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H495" s="5" t="inlineStr"/>
       <c r="I495" s="3" t="inlineStr"/>
       <c r="J495" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/259631</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14333/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K495" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
-        </is>
-      </c>
-      <c r="L495" t="inlineStr">
-        <is>
-          <t>From the agency's email alert.</t>
-        </is>
-      </c>
+          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Duval</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Hillsborough County BOCC</t>
+          <t>JAXPORT</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>RFI-27-00004</t>
+          <t>PSS # EQ-2095A</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>Computer Assisted Mass Appraisal (CAMA) System</t>
+          <t>The purchase of two (2) new-surplus CAT 270-3504 radiator assemblies</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>IT &amp; Technology</t>
-        </is>
-      </c>
-      <c r="F496" t="inlineStr"/>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Sole source</t>
+        </is>
+      </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H496" s="5" t="inlineStr"/>
       <c r="I496" s="3" t="inlineStr"/>
       <c r="J496" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/257039</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14299/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K496" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
-        </is>
-      </c>
-      <c r="L496" t="inlineStr">
-        <is>
-          <t>From the agency's email alert.</t>
-        </is>
-      </c>
+          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -26414,17 +26414,17 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>IFB-26-00348</t>
+          <t>IFB-26-00413</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>Countywide Fire Hydrant Replacement - WORCS-5</t>
+          <t>Columbus Drive Bridge #105504 Painting and Repair</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F497" t="inlineStr"/>
@@ -26437,7 +26437,7 @@
       <c r="I497" s="3" t="inlineStr"/>
       <c r="J497" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/244837</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/253223</t>
         </is>
       </c>
       <c r="K497" s="4" t="inlineStr">
@@ -26464,17 +26464,17 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>IFB-26-00398</t>
+          <t>ITB-27-00018</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>Intersection Improvements for East County Line Road at Grand Hampton Drive</t>
+          <t>Community Feral Cat Spay and Neuter Program</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Concessions &amp; Programs</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -26487,7 +26487,7 @@
       <c r="I498" s="3" t="inlineStr"/>
       <c r="J498" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/251575</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/259631</t>
         </is>
       </c>
       <c r="K498" s="4" t="inlineStr">
@@ -26514,17 +26514,17 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>IFB-26-00404</t>
+          <t>RFI-27-00004</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>Kirby Street Pump Station #08 Rehabilitation</t>
+          <t>Computer Assisted Mass Appraisal (CAMA) System</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -26537,7 +26537,7 @@
       <c r="I499" s="3" t="inlineStr"/>
       <c r="J499" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/252053</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/257039</t>
         </is>
       </c>
       <c r="K499" s="4" t="inlineStr">
@@ -26564,17 +26564,17 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>ITB-27-00003</t>
+          <t>IFB-26-00348</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>Laboratory Courier Services</t>
+          <t>Countywide Fire Hydrant Replacement - WORCS-5</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -26587,7 +26587,7 @@
       <c r="I500" s="3" t="inlineStr"/>
       <c r="J500" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/256978</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/244837</t>
         </is>
       </c>
       <c r="K500" s="4" t="inlineStr">
@@ -26609,25 +26609,29 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Hillsborough County BOCC</t>
+          <t>City of Tampa</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>ITB-27-00005</t>
+          <t>#320261</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>Lift Station Landscaping Maintenance Services (SBE Set-Aside)</t>
+          <t>Intent to Single Source for Hach Equipment, Parts, and Service</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="F501" t="inlineStr"/>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Sole source</t>
+        </is>
+      </c>
       <c r="G501" t="inlineStr">
         <is>
           <t>Open</t>
@@ -26637,12 +26641,12 @@
       <c r="I501" s="3" t="inlineStr"/>
       <c r="J501" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/257045</t>
+          <t>https://procurement.opengov.com/portal/cityoftampa/projects/320261</t>
         </is>
       </c>
       <c r="K501" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://procurement.opengov.com/portal/cityoftampa</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
@@ -26664,12 +26668,12 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>IFB-26-00346</t>
+          <t>IFB-26-00398</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>Low Pressure Sewer System Installations and Repairs (WORCS-2)</t>
+          <t>Intersection Improvements for East County Line Road at Grand Hampton Drive</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -26687,7 +26691,7 @@
       <c r="I502" s="3" t="inlineStr"/>
       <c r="J502" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/244676</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/251575</t>
         </is>
       </c>
       <c r="K502" s="4" t="inlineStr">
@@ -26714,17 +26718,17 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>RPS-26-00400</t>
+          <t>IFB-26-00404</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>Misc. Professional Stormwater Services</t>
+          <t>Kirby Street Pump Station #08 Rehabilitation</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -26737,7 +26741,7 @@
       <c r="I503" s="3" t="inlineStr"/>
       <c r="J503" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/251584</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/252053</t>
         </is>
       </c>
       <c r="K503" s="4" t="inlineStr">
@@ -26764,17 +26768,17 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>RPS-26-00366</t>
+          <t>ITB-27-00003</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>Miscellaneous Construction Engineering and Inspection (CEI) Services - CDBG-DR</t>
+          <t>Laboratory Courier Services</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -26787,7 +26791,7 @@
       <c r="I504" s="3" t="inlineStr"/>
       <c r="J504" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/248264</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/256978</t>
         </is>
       </c>
       <c r="K504" s="4" t="inlineStr">
@@ -26814,17 +26818,17 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>IFB-26-00399</t>
+          <t>ITB-27-00005</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>Miscellaneous Parking Lot Repaving Services Term Contract B</t>
+          <t>Lift Station Landscaping Maintenance Services (SBE Set-Aside)</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -26837,7 +26841,7 @@
       <c r="I505" s="3" t="inlineStr"/>
       <c r="J505" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/251576</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/257045</t>
         </is>
       </c>
       <c r="K505" s="4" t="inlineStr">
@@ -26864,17 +26868,17 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>RPS-26-00367</t>
+          <t>IFB-26-00346</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>Miscellaneous Subsurface Investigation &amp; Testing</t>
+          <t>Low Pressure Sewer System Installations and Repairs (WORCS-2)</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -26887,7 +26891,7 @@
       <c r="I506" s="3" t="inlineStr"/>
       <c r="J506" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/248352</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/244676</t>
         </is>
       </c>
       <c r="K506" s="4" t="inlineStr">
@@ -26914,17 +26918,17 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>IFB-26-00401</t>
+          <t>RPS-26-00400</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>R3M Miscellaneous Facilities Construction Term Contract 11</t>
+          <t>Misc. Professional Stormwater Services</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -26937,7 +26941,7 @@
       <c r="I507" s="3" t="inlineStr"/>
       <c r="J507" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/251655</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/251584</t>
         </is>
       </c>
       <c r="K507" s="4" t="inlineStr">
@@ -26964,17 +26968,17 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>ITB-27-00002</t>
+          <t>RPS-26-00366</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>Rental of Traffic Control Devices</t>
+          <t>Miscellaneous Construction Engineering and Inspection (CEI) Services - CDBG-DR</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -26987,7 +26991,7 @@
       <c r="I508" s="3" t="inlineStr"/>
       <c r="J508" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/256945</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/248264</t>
         </is>
       </c>
       <c r="K508" s="4" t="inlineStr">
@@ -27014,12 +27018,12 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>IFB-26-00363</t>
+          <t>IFB-26-00399</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>Roadway Resurfacing Repair and Preservation Districts 3&amp;4 WORCS</t>
+          <t>Miscellaneous Parking Lot Repaving Services Term Contract B</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -27037,7 +27041,7 @@
       <c r="I509" s="3" t="inlineStr"/>
       <c r="J509" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/247158</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/251576</t>
         </is>
       </c>
       <c r="K509" s="4" t="inlineStr">
@@ -27064,17 +27068,17 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>ITB-26-00424</t>
+          <t>RPS-26-00367</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>Tire Disposal Services</t>
+          <t>Miscellaneous Subsurface Investigation &amp; Testing</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -27087,7 +27091,7 @@
       <c r="I510" s="3" t="inlineStr"/>
       <c r="J510" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/254535</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/248352</t>
         </is>
       </c>
       <c r="K510" s="4" t="inlineStr">
@@ -27114,17 +27118,17 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>ITQ-27-00013</t>
+          <t>IFB-26-00401</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>Uniforms and Protective Clothing</t>
+          <t>R3M Miscellaneous Facilities Construction Term Contract 11</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -27137,7 +27141,7 @@
       <c r="I511" s="3" t="inlineStr"/>
       <c r="J511" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/258220</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/251655</t>
         </is>
       </c>
       <c r="K511" s="4" t="inlineStr">
@@ -27164,17 +27168,17 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>IFB-26-00406</t>
+          <t>ITB-27-00002</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>Valrico Reclaimed Water Facility Diesel Generator Project</t>
+          <t>Rental of Traffic Control Devices</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -27187,7 +27191,7 @@
       <c r="I512" s="3" t="inlineStr"/>
       <c r="J512" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/252215</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/256945</t>
         </is>
       </c>
       <c r="K512" s="4" t="inlineStr">
@@ -27214,17 +27218,17 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>ITB-27-00008</t>
+          <t>IFB-26-00363</t>
         </is>
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>Various Fleet Vehicles and Equipment</t>
+          <t>Roadway Resurfacing Repair and Preservation Districts 3&amp;4 WORCS</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -27237,7 +27241,7 @@
       <c r="I513" s="3" t="inlineStr"/>
       <c r="J513" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/257371</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/247158</t>
         </is>
       </c>
       <c r="K513" s="4" t="inlineStr">
@@ -27264,17 +27268,17 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>RPS-26-00423</t>
+          <t>ITB-26-00424</t>
         </is>
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>Waters Avenue Force Main Replacement CEI Services</t>
+          <t>Tire Disposal Services</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -27287,7 +27291,7 @@
       <c r="I514" s="3" t="inlineStr"/>
       <c r="J514" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/254487</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/254535</t>
         </is>
       </c>
       <c r="K514" s="4" t="inlineStr">
@@ -27304,342 +27308,322 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>A26PM01</t>
+          <t>ITQ-27-00013</t>
         </is>
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>A/E Services for Real Estate</t>
+          <t>Uniforms and Protective Clothing</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
-        </is>
-      </c>
-      <c r="F515" t="inlineStr">
-        <is>
-          <t>Draft / Future</t>
-        </is>
-      </c>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr"/>
       <c r="G515" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H515" s="5" t="inlineStr"/>
-      <c r="I515" s="3" t="n">
-        <v>46315</v>
-      </c>
+      <c r="I515" s="3" t="inlineStr"/>
       <c r="J515" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8983</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/258220</t>
         </is>
       </c>
       <c r="K515" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>Draft for feedback. Send comments to Julie Whiteside (Julie.whiteside@miamidade.gov). Posted until 2026-11-10.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr"/>
+          <t>Hillsborough County BOCC</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>IFB-26-00406</t>
+        </is>
+      </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>Access Control Point Barrier Systems</t>
+          <t>Valrico Reclaimed Water Facility Diesel Generator Project</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>IT &amp; Technology</t>
-        </is>
-      </c>
-      <c r="F516" t="inlineStr">
-        <is>
-          <t>Draft / Future</t>
-        </is>
-      </c>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr"/>
       <c r="G516" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H516" s="5" t="inlineStr"/>
-      <c r="I516" s="3" t="n">
-        <v>46302</v>
-      </c>
+      <c r="I516" s="3" t="inlineStr"/>
       <c r="J516" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8975</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/252215</t>
         </is>
       </c>
       <c r="K516" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>Draft for feedback. Send comments to Amy Almanzar (Amy.almanzar@miamidade.gov). Posted until 2026-10-27.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
-        </is>
-      </c>
-      <c r="C517" t="inlineStr"/>
+          <t>Hillsborough County BOCC</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>ITB-27-00008</t>
+        </is>
+      </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>E26WS02 - REPOST - GEOTECHNICAL SRVS, STRUCTURAL ASSESSMENT, MATERIALS TEST</t>
+          <t>Various Fleet Vehicles and Equipment</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
-        </is>
-      </c>
-      <c r="F517" t="inlineStr">
-        <is>
-          <t>Draft / Future</t>
-        </is>
-      </c>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr"/>
       <c r="G517" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H517" s="5" t="inlineStr"/>
-      <c r="I517" s="3" t="n">
-        <v>46315</v>
-      </c>
+      <c r="I517" s="3" t="inlineStr"/>
       <c r="J517" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8981</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/257371</t>
         </is>
       </c>
       <c r="K517" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>Draft for feedback. Send comments to Ana M. DaSilva (ana.dasilva@miamidade.gov). Posted until 2026-11-09.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
-        </is>
-      </c>
-      <c r="C518" t="inlineStr"/>
+          <t>Hillsborough County BOCC</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>RPS-26-00423</t>
+        </is>
+      </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>Summer Food Service Program</t>
+          <t>Waters Avenue Force Main Replacement CEI Services</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Concessions &amp; Programs</t>
-        </is>
-      </c>
-      <c r="F518" t="inlineStr">
-        <is>
-          <t>Draft / Future</t>
-        </is>
-      </c>
+          <t>Engineering &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr"/>
       <c r="G518" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H518" s="5" t="inlineStr"/>
-      <c r="I518" s="3" t="n">
-        <v>46295</v>
-      </c>
+      <c r="I518" s="3" t="inlineStr"/>
       <c r="J518" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8973</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/254487</t>
         </is>
       </c>
       <c r="K518" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>Draft for feedback. Send comments to Leslie Zambrana (leslie.zambrana@miamidade.gov). Posted until 2026-10-30.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
-        </is>
-      </c>
-      <c r="C519" t="inlineStr"/>
+          <t>City of Fort Myers</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>#320240</t>
+        </is>
+      </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>Third-Party Inspection Services for Elevators, Escalators, and Other Convey</t>
+          <t>Composite Access Products LP (CAP)</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="F519" t="inlineStr">
-        <is>
-          <t>Draft / Future</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr"/>
       <c r="G519" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H519" s="5" t="inlineStr"/>
-      <c r="I519" s="3" t="n">
-        <v>46315</v>
-      </c>
+      <c r="I519" s="3" t="inlineStr"/>
       <c r="J519" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8980</t>
+          <t>https://procurement.opengov.com/portal/cityftmyers/projects/320240</t>
         </is>
       </c>
       <c r="K519" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+          <t>https://procurement.opengov.com/portal/cityftmyers</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>Draft for feedback. Send comments to Richard Celestin (richard.celestin@miamidade.gov). Posted until 2026-10-27.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
+          <t>City of Cape Coral</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>E26PM01</t>
+          <t>#300122</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>Water Remediation Pool</t>
+          <t>Construction Manager at Risk (CMAR) for Projects less than $4 Million</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="F520" t="inlineStr">
-        <is>
-          <t>Draft / Future</t>
-        </is>
-      </c>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr"/>
       <c r="G520" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H520" s="5" t="inlineStr"/>
-      <c r="I520" s="3" t="n">
-        <v>46315</v>
-      </c>
+      <c r="I520" s="3" t="inlineStr"/>
       <c r="J520" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8984</t>
+          <t>https://procurement.opengov.com/portal/capecoralfl/projects/300122</t>
         </is>
       </c>
       <c r="K520" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+          <t>https://procurement.opengov.com/portal/capecoralfl</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>Draft for feedback. Send comments to Julie Whiteside (Julie.whiteside@miamidade.gov). Posted until 2026-11-10.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Monroe</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Monroe County BOCC</t>
+          <t>Miami-Dade County</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>#257290</t>
+          <t>A26PM01</t>
         </is>
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>Construction, Engineering and Inspection Services for Key Deer Blvd (North of Watson Blvd) Roadway Rehabilitation Project</t>
+          <t>A/E Services for Real Estate</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -27647,304 +27631,324 @@
           <t>Engineering &amp; Architecture</t>
         </is>
       </c>
-      <c r="F521" t="inlineStr"/>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Draft / Future</t>
+        </is>
+      </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="H521" s="5" t="inlineStr"/>
-      <c r="I521" s="3" t="inlineStr"/>
+      <c r="I521" s="3" t="n">
+        <v>46315</v>
+      </c>
       <c r="J521" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/opportunities/257290</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8983</t>
         </is>
       </c>
       <c r="K521" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>From the agency's email alert.</t>
+          <t>Draft for feedback. Send comments to Julie Whiteside (Julie.whiteside@miamidade.gov). Posted until 2026-11-10.</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Monroe</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Monroe County BOCC</t>
-        </is>
-      </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>#259466</t>
-        </is>
-      </c>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr"/>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>Ellis Building Interior Renovation</t>
+          <t>Access Control Point Barrier Systems</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F522" t="inlineStr"/>
+          <t>IT &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Draft / Future</t>
+        </is>
+      </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="H522" s="5" t="inlineStr"/>
-      <c r="I522" s="3" t="inlineStr"/>
+      <c r="I522" s="3" t="n">
+        <v>46302</v>
+      </c>
       <c r="J522" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/opportunities/259466</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8975</t>
         </is>
       </c>
       <c r="K522" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>From the agency's email alert.</t>
+          <t>Draft for feedback. Send comments to Amy Almanzar (Amy.almanzar@miamidade.gov). Posted until 2026-10-27.</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Monroe</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Monroe County BOCC</t>
-        </is>
-      </c>
-      <c r="C523" t="inlineStr">
-        <is>
-          <t>#256505</t>
-        </is>
-      </c>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr"/>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>Latin America Sales Agency for Monroe County Tourist Development Council</t>
+          <t>E26WS02 - REPOST - GEOTECHNICAL SRVS, STRUCTURAL ASSESSMENT, MATERIALS TEST</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F523" t="inlineStr"/>
+          <t>Engineering &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Draft / Future</t>
+        </is>
+      </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="H523" s="5" t="inlineStr"/>
-      <c r="I523" s="3" t="inlineStr"/>
+      <c r="I523" s="3" t="n">
+        <v>46315</v>
+      </c>
       <c r="J523" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/opportunities/256505</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8981</t>
         </is>
       </c>
       <c r="K523" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t>From the agency's email alert.</t>
+          <t>Draft for feedback. Send comments to Ana M. DaSilva (ana.dasilva@miamidade.gov). Posted until 2026-11-09.</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Monroe</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Monroe County BOCC</t>
-        </is>
-      </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>#235838</t>
-        </is>
-      </c>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr"/>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>Multifamily SHIP Application 2025 RFA</t>
+          <t>Summer Food Service Program</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>IT &amp; Technology</t>
-        </is>
-      </c>
-      <c r="F524" t="inlineStr"/>
+          <t>Concessions &amp; Programs</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Draft / Future</t>
+        </is>
+      </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="H524" s="5" t="inlineStr"/>
-      <c r="I524" s="3" t="inlineStr"/>
+      <c r="I524" s="3" t="n">
+        <v>46295</v>
+      </c>
       <c r="J524" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/opportunities/235838</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8973</t>
         </is>
       </c>
       <c r="K524" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>From the agency's email alert.</t>
+          <t>Draft for feedback. Send comments to Leslie Zambrana (leslie.zambrana@miamidade.gov). Posted until 2026-10-30.</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Monroe</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Monroe County BOCC</t>
-        </is>
-      </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>#256340</t>
-        </is>
-      </c>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr"/>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>Professional Architectural and Engineering Continuing Services</t>
+          <t>Third-Party Inspection Services for Elevators, Escalators, and Other Convey</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
-        </is>
-      </c>
-      <c r="F525" t="inlineStr"/>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Draft / Future</t>
+        </is>
+      </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="H525" s="5" t="inlineStr"/>
-      <c r="I525" s="3" t="inlineStr"/>
+      <c r="I525" s="3" t="n">
+        <v>46315</v>
+      </c>
       <c r="J525" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/opportunities/256340</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8980</t>
         </is>
       </c>
       <c r="K525" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>From the agency's email alert.</t>
+          <t>Draft for feedback. Send comments to Richard Celestin (richard.celestin@miamidade.gov). Posted until 2026-10-27.</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Monroe</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Monroe County BOCC</t>
+          <t>Miami-Dade County</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>#255496</t>
+          <t>E26PM01</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>Professional Surveying Continuing Services</t>
+          <t>Water Remediation Pool</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
-        </is>
-      </c>
-      <c r="F526" t="inlineStr"/>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Draft / Future</t>
+        </is>
+      </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="H526" s="5" t="inlineStr"/>
-      <c r="I526" s="3" t="inlineStr"/>
+      <c r="I526" s="3" t="n">
+        <v>46315</v>
+      </c>
       <c r="J526" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/opportunities/255496</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8984</t>
         </is>
       </c>
       <c r="K526" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>From the agency's email alert.</t>
+          <t>Draft for feedback. Send comments to Julie Whiteside (Julie.whiteside@miamidade.gov). Posted until 2026-11-10.</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Pasco</t>
+          <t>Monroe</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Pasco County BOCC</t>
+          <t>Monroe County BOCC</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>IFB-KM-27-016</t>
+          <t>#257290</t>
         </is>
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>BEXLEY ELEMENTARY SIDEWALK PROJECT (BALLANTRAE BLVD FROM STRATON PL TO BUD BEXLEY PKWY)</t>
+          <t>Construction, Engineering and Inspection Services for Key Deer Blvd (North of Watson Blvd) Roadway Rehabilitation Project</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
@@ -27957,12 +27961,12 @@
       <c r="I527" s="3" t="inlineStr"/>
       <c r="J527" s="4" t="inlineStr">
         <is>
-          <t>https://pascocountyfl.bonfirehub.com/opportunities/259647</t>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/257290</t>
         </is>
       </c>
       <c r="K527" s="4" t="inlineStr">
         <is>
-          <t>https://pascocountyfl.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
@@ -27974,22 +27978,22 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Pasco</t>
+          <t>Monroe</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Pasco County BOCC</t>
+          <t>Monroe County BOCC</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>IFB-BW-27-009</t>
+          <t>#259466</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>BYRD DR. AND GUNN HIGHWAY INTERSECTION IMPROVEMENTS</t>
+          <t>Ellis Building Interior Renovation</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -28007,12 +28011,12 @@
       <c r="I528" s="3" t="inlineStr"/>
       <c r="J528" s="4" t="inlineStr">
         <is>
-          <t>https://pascocountyfl.bonfirehub.com/opportunities/255847</t>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/259466</t>
         </is>
       </c>
       <c r="K528" s="4" t="inlineStr">
         <is>
-          <t>https://pascocountyfl.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
@@ -28024,27 +28028,27 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Pasco</t>
+          <t>Monroe</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Pasco County BOCC</t>
+          <t>Monroe County BOCC</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>IFB-KM-27-010</t>
+          <t>#256505</t>
         </is>
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
-          <t>EILAND BOULEVARD AND SILVERADO RANCH BOULEVARD/RYALS ROAD INTERSECTION SIGNALIZATION</t>
+          <t>Latin America Sales Agency for Monroe County Tourist Development Council</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -28057,12 +28061,12 @@
       <c r="I529" s="3" t="inlineStr"/>
       <c r="J529" s="4" t="inlineStr">
         <is>
-          <t>https://pascocountyfl.bonfirehub.com/opportunities/255633</t>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/256505</t>
         </is>
       </c>
       <c r="K529" s="4" t="inlineStr">
         <is>
-          <t>https://pascocountyfl.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
@@ -28074,34 +28078,30 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Monroe</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Monroe County BOCC</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>RFP 26-345</t>
+          <t>#235838</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>Advertising &amp; Marketing Services for Visit Central Florida</t>
+          <t>Multifamily SHIP Application 2025 RFA</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
-        </is>
-      </c>
-      <c r="F530" t="inlineStr">
-        <is>
-          <t>RFP</t>
-        </is>
-      </c>
+          <t>IT &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr"/>
       <c r="G530" t="inlineStr">
         <is>
           <t>Open</t>
@@ -28111,40 +28111,44 @@
       <c r="I530" s="3" t="inlineStr"/>
       <c r="J530" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-345/</t>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/235838</t>
         </is>
       </c>
       <c r="K530" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L530" t="inlineStr"/>
+          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Monroe</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Monroe County BOCC</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>CS 25-396</t>
+          <t>#256340</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
-          <t>Apparel Embroidery Services</t>
+          <t>Professional Architectural and Engineering Continuing Services</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -28157,40 +28161,44 @@
       <c r="I531" s="3" t="inlineStr"/>
       <c r="J531" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-25-396/</t>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/256340</t>
         </is>
       </c>
       <c r="K531" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L531" t="inlineStr"/>
+          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Monroe</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Monroe County BOCC</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>CS 25-230</t>
+          <t>#255496</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>Asphalt</t>
+          <t>Professional Surveying Continuing Services</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -28203,40 +28211,44 @@
       <c r="I532" s="3" t="inlineStr"/>
       <c r="J532" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-25-230/</t>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/255496</t>
         </is>
       </c>
       <c r="K532" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L532" t="inlineStr"/>
+          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Okaloosa</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Okaloosa County BOCC</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>CS 24-330</t>
+          <t>#315955</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>Body Shop Services</t>
+          <t>Covered Walkway Phase 2</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -28249,35 +28261,39 @@
       <c r="I533" s="3" t="inlineStr"/>
       <c r="J533" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-24-330/</t>
+          <t>https://procurement.opengov.com/portal/myokaloosa/projects/315955</t>
         </is>
       </c>
       <c r="K533" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L533" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/myokaloosa</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Okaloosa</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Okaloosa County BOCC</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>RFP 26-068</t>
+          <t>#312231</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>CMAR - Polk County Utilities Northeast Regional Warehouse/Operations Building and Fleet Campus</t>
+          <t>Okaloosa County Jail - Delta Pod - Complete Shingle Re-Roof</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -28285,11 +28301,7 @@
           <t>Construction</t>
         </is>
       </c>
-      <c r="F534" t="inlineStr">
-        <is>
-          <t>RFP</t>
-        </is>
-      </c>
+      <c r="F534" t="inlineStr"/>
       <c r="G534" t="inlineStr">
         <is>
           <t>Open</t>
@@ -28299,40 +28311,44 @@
       <c r="I534" s="3" t="inlineStr"/>
       <c r="J534" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-068/</t>
+          <t>https://procurement.opengov.com/portal/myokaloosa/projects/312231</t>
         </is>
       </c>
       <c r="K534" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L534" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/myokaloosa</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Pasco</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Pasco County BOCC</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>CS 25-456</t>
+          <t>IFB-KM-27-016</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Herbicides for Aquatic Weeds and Environmental Lands</t>
+          <t>BEXLEY ELEMENTARY SIDEWALK PROJECT (BALLANTRAE BLVD FROM STRATON PL TO BUD BEXLEY PKWY)</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -28345,40 +28361,44 @@
       <c r="I535" s="3" t="inlineStr"/>
       <c r="J535" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-25-456/</t>
+          <t>https://pascocountyfl.bonfirehub.com/opportunities/259647</t>
         </is>
       </c>
       <c r="K535" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L535" t="inlineStr"/>
+          <t>https://pascocountyfl.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Pasco</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Pasco County BOCC</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>CS 22-365</t>
+          <t>IFB-BW-27-009</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>Code Enforcement Towing</t>
+          <t>BYRD DR. AND GUNN HIGHWAY INTERSECTION IMPROVEMENTS</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -28391,40 +28411,44 @@
       <c r="I536" s="3" t="inlineStr"/>
       <c r="J536" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-22-365/</t>
+          <t>https://pascocountyfl.bonfirehub.com/opportunities/255847</t>
         </is>
       </c>
       <c r="K536" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L536" t="inlineStr"/>
+          <t>https://pascocountyfl.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Pasco</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Pasco County BOCC</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Bid 26-395</t>
+          <t>IFB-KM-27-010</t>
         </is>
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>Communication Amplifier Systems</t>
+          <t>EILAND BOULEVARD AND SILVERADO RANCH BOULEVARD/RYALS ROAD INTERSECTION SIGNALIZATION</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>IT &amp; Technology</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -28437,40 +28461,44 @@
       <c r="I537" s="3" t="inlineStr"/>
       <c r="J537" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-395/</t>
+          <t>https://pascocountyfl.bonfirehub.com/opportunities/255633</t>
         </is>
       </c>
       <c r="K537" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L537" t="inlineStr"/>
+          <t>https://pascocountyfl.bonfirehub.com/portal/?tab=openOpportunities</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Pinellas</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Pinellas County Schools</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>CS 24-507</t>
+          <t>#319367</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>Cremation Services</t>
+          <t>First Aid Suplies</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -28483,15 +28511,19 @@
       <c r="I538" s="3" t="inlineStr"/>
       <c r="J538" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-24-507/</t>
+          <t>https://procurement.opengov.com/portal/pcsb/projects/319367</t>
         </is>
       </c>
       <c r="K538" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L538" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/pcsb</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -28506,20 +28538,24 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>ISS 26-065</t>
+          <t>RFP 26-345</t>
         </is>
       </c>
       <c r="D539" s="2" t="inlineStr">
         <is>
-          <t>Digital Information Kiosks &amp; System</t>
+          <t>Advertising &amp; Marketing Services for Visit Central Florida</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>IT &amp; Technology</t>
-        </is>
-      </c>
-      <c r="F539" t="inlineStr"/>
+          <t>Consulting &amp; Professional Services</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>RFP</t>
+        </is>
+      </c>
       <c r="G539" t="inlineStr">
         <is>
           <t>Open</t>
@@ -28529,7 +28565,7 @@
       <c r="I539" s="3" t="inlineStr"/>
       <c r="J539" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/iss-26-065/</t>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-345/</t>
         </is>
       </c>
       <c r="K539" s="4" t="inlineStr">
@@ -28552,24 +28588,20 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>RFP 26-320</t>
+          <t>CS 25-396</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
-          <t>Engineering Services for Water Infrastructure Repair &amp; Water Quality Improvement Solutions for the Lakeland to Bartow Lake Watershed</t>
+          <t>Apparel Embroidery Services</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
-        </is>
-      </c>
-      <c r="F540" t="inlineStr">
-        <is>
-          <t>RFP</t>
-        </is>
-      </c>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr"/>
       <c r="G540" t="inlineStr">
         <is>
           <t>Open</t>
@@ -28579,7 +28611,7 @@
       <c r="I540" s="3" t="inlineStr"/>
       <c r="J540" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-320/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-25-396/</t>
         </is>
       </c>
       <c r="K540" s="4" t="inlineStr">
@@ -28602,17 +28634,17 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>CS 13-294</t>
+          <t>CS 25-230</t>
         </is>
       </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
-          <t>Environmental Lands Site Caretaker</t>
+          <t>Asphalt</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
@@ -28625,7 +28657,7 @@
       <c r="I541" s="3" t="inlineStr"/>
       <c r="J541" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-13-294/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-25-230/</t>
         </is>
       </c>
       <c r="K541" s="4" t="inlineStr">
@@ -28648,24 +28680,20 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>RFP 26-370</t>
+          <t>CS 24-330</t>
         </is>
       </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
-          <t>Grant Administration for Community Development Block Grant (CDBG) Disaster Recovery (DR) Infrastructure Repair Program</t>
+          <t>Body Shop Services</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
-        </is>
-      </c>
-      <c r="F542" t="inlineStr">
-        <is>
-          <t>RFP</t>
-        </is>
-      </c>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr"/>
       <c r="G542" t="inlineStr">
         <is>
           <t>Open</t>
@@ -28675,7 +28703,7 @@
       <c r="I542" s="3" t="inlineStr"/>
       <c r="J542" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-370/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-24-330/</t>
         </is>
       </c>
       <c r="K542" s="4" t="inlineStr">
@@ -28698,20 +28726,24 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Bid 26-229</t>
+          <t>RFP 26-068</t>
         </is>
       </c>
       <c r="D543" s="2" t="inlineStr">
         <is>
-          <t>Ground Maintenance – Countywide – Zones 1 through 8</t>
+          <t>CMAR - Polk County Utilities Northeast Regional Warehouse/Operations Building and Fleet Campus</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="F543" t="inlineStr"/>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>RFP</t>
+        </is>
+      </c>
       <c r="G543" t="inlineStr">
         <is>
           <t>Open</t>
@@ -28721,7 +28753,7 @@
       <c r="I543" s="3" t="inlineStr"/>
       <c r="J543" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-229/</t>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-068/</t>
         </is>
       </c>
       <c r="K543" s="4" t="inlineStr">
@@ -28744,12 +28776,12 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>CS 20-667</t>
+          <t>CS 25-456</t>
         </is>
       </c>
       <c r="D544" s="2" t="inlineStr">
         <is>
-          <t>Heavy Equipment and Tool Rentals</t>
+          <t>Chemicals &amp; Herbicides for Aquatic Weeds and Environmental Lands</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -28767,7 +28799,7 @@
       <c r="I544" s="3" t="inlineStr"/>
       <c r="J544" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-20-667/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-25-456/</t>
         </is>
       </c>
       <c r="K544" s="4" t="inlineStr">
@@ -28790,17 +28822,17 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>CS 20-1111</t>
+          <t>CS 22-365</t>
         </is>
       </c>
       <c r="D545" s="2" t="inlineStr">
         <is>
-          <t>Janitorial Supplies</t>
+          <t>Code Enforcement Towing</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -28813,7 +28845,7 @@
       <c r="I545" s="3" t="inlineStr"/>
       <c r="J545" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-20-1111/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-22-365/</t>
         </is>
       </c>
       <c r="K545" s="4" t="inlineStr">
@@ -28836,17 +28868,17 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>CS 20-633</t>
+          <t>Bid 26-395</t>
         </is>
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
-          <t>Litter Pickup</t>
+          <t>Communication Amplifier Systems</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -28859,7 +28891,7 @@
       <c r="I546" s="3" t="inlineStr"/>
       <c r="J546" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-20-633/</t>
+          <t>https://www.polkfl.gov/bid-form/bid-26-395/</t>
         </is>
       </c>
       <c r="K546" s="4" t="inlineStr">
@@ -28882,17 +28914,17 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>CQ 26-214</t>
+          <t>CS 24-507</t>
         </is>
       </c>
       <c r="D547" s="2" t="inlineStr">
         <is>
-          <t>Loyce Harpe Basketball Court and Sidewalks</t>
+          <t>Cremation Services</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -28905,7 +28937,7 @@
       <c r="I547" s="3" t="inlineStr"/>
       <c r="J547" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cq-26-214/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-24-507/</t>
         </is>
       </c>
       <c r="K547" s="4" t="inlineStr">
@@ -28928,17 +28960,17 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>CS 26-296</t>
+          <t>ISS 26-065</t>
         </is>
       </c>
       <c r="D548" s="2" t="inlineStr">
         <is>
-          <t>MUTCD Regulatory &amp; Warning Signs</t>
+          <t>Digital Information Kiosks &amp; System</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -28951,7 +28983,7 @@
       <c r="I548" s="3" t="inlineStr"/>
       <c r="J548" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-26-296/</t>
+          <t>https://www.polkfl.gov/bid-form/iss-26-065/</t>
         </is>
       </c>
       <c r="K548" s="4" t="inlineStr">
@@ -28974,17 +29006,17 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>RFP 26-352</t>
+          <t>RFP 26-320</t>
         </is>
       </c>
       <c r="D549" s="2" t="inlineStr">
         <is>
-          <t>Masterpiece Cattle Lease</t>
+          <t>Engineering Services for Water Infrastructure Repair &amp; Water Quality Improvement Solutions for the Lakeland to Bartow Lake Watershed</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F549" t="inlineStr">
@@ -29001,7 +29033,7 @@
       <c r="I549" s="3" t="inlineStr"/>
       <c r="J549" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-352/</t>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-320/</t>
         </is>
       </c>
       <c r="K549" s="4" t="inlineStr">
@@ -29024,12 +29056,12 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Bid 26-367</t>
+          <t>CS 13-294</t>
         </is>
       </c>
       <c r="D550" s="2" t="inlineStr">
         <is>
-          <t>Mowing &amp; Maintenance for Utilities – North Region</t>
+          <t>Environmental Lands Site Caretaker</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -29047,7 +29079,7 @@
       <c r="I550" s="3" t="inlineStr"/>
       <c r="J550" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-367/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-13-294/</t>
         </is>
       </c>
       <c r="K550" s="4" t="inlineStr">
@@ -29070,20 +29102,24 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Bid 26-350</t>
+          <t>RFP 26-370</t>
         </is>
       </c>
       <c r="D551" s="2" t="inlineStr">
         <is>
-          <t>Mowing and Maintenance for Solid Waste</t>
+          <t>Grant Administration for Community Development Block Grant (CDBG) Disaster Recovery (DR) Infrastructure Repair Program</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="F551" t="inlineStr"/>
+          <t>Consulting &amp; Professional Services</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>RFP</t>
+        </is>
+      </c>
       <c r="G551" t="inlineStr">
         <is>
           <t>Open</t>
@@ -29093,7 +29129,7 @@
       <c r="I551" s="3" t="inlineStr"/>
       <c r="J551" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-350/</t>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-370/</t>
         </is>
       </c>
       <c r="K551" s="4" t="inlineStr">
@@ -29116,17 +29152,17 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Bid 26-295</t>
+          <t>Bid 26-229</t>
         </is>
       </c>
       <c r="D552" s="2" t="inlineStr">
         <is>
-          <t>Onsite Clinic Services</t>
+          <t>Ground Maintenance – Countywide – Zones 1 through 8</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -29139,7 +29175,7 @@
       <c r="I552" s="3" t="inlineStr"/>
       <c r="J552" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-295/</t>
+          <t>https://www.polkfl.gov/bid-form/bid-26-229/</t>
         </is>
       </c>
       <c r="K552" s="4" t="inlineStr">
@@ -29162,17 +29198,17 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>CS 24-194</t>
+          <t>CS 20-667</t>
         </is>
       </c>
       <c r="D553" s="2" t="inlineStr">
         <is>
-          <t>Overgrowth and Large Lot Clearing</t>
+          <t>Heavy Equipment and Tool Rentals</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -29185,7 +29221,7 @@
       <c r="I553" s="3" t="inlineStr"/>
       <c r="J553" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-24-194/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-20-667/</t>
         </is>
       </c>
       <c r="K553" s="4" t="inlineStr">
@@ -29208,12 +29244,12 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>CS 24-195</t>
+          <t>CS 20-1111</t>
         </is>
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
-          <t>Overgrowth and Small Lot Clearing</t>
+          <t>Janitorial Supplies</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -29231,7 +29267,7 @@
       <c r="I554" s="3" t="inlineStr"/>
       <c r="J554" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-24-195/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-20-1111/</t>
         </is>
       </c>
       <c r="K554" s="4" t="inlineStr">
@@ -29254,17 +29290,17 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>CQ 26-343</t>
+          <t>CS 20-633</t>
         </is>
       </c>
       <c r="D555" s="2" t="inlineStr">
         <is>
-          <t>PCU Administration Building – Conference Room Remodel.</t>
+          <t>Litter Pickup</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F555" t="inlineStr"/>
@@ -29277,7 +29313,7 @@
       <c r="I555" s="3" t="inlineStr"/>
       <c r="J555" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cq-26-343/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-20-633/</t>
         </is>
       </c>
       <c r="K555" s="4" t="inlineStr">
@@ -29300,17 +29336,17 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>CS 09-007</t>
+          <t>CQ 26-214</t>
         </is>
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
-          <t>Park Service Residents</t>
+          <t>Loyce Harpe Basketball Court and Sidewalks</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -29323,7 +29359,7 @@
       <c r="I556" s="3" t="inlineStr"/>
       <c r="J556" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-09-007/</t>
+          <t>https://www.polkfl.gov/bid-form/cq-26-214/</t>
         </is>
       </c>
       <c r="K556" s="4" t="inlineStr">
@@ -29346,12 +29382,12 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>CS 18-824</t>
+          <t>CS 26-296</t>
         </is>
       </c>
       <c r="D557" s="2" t="inlineStr">
         <is>
-          <t>Pharmaceuticals for Fire Rescue</t>
+          <t>MUTCD Regulatory &amp; Warning Signs</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
@@ -29369,7 +29405,7 @@
       <c r="I557" s="3" t="inlineStr"/>
       <c r="J557" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-18-824/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-26-296/</t>
         </is>
       </c>
       <c r="K557" s="4" t="inlineStr">
@@ -29392,20 +29428,24 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>CS 25-303</t>
+          <t>RFP 26-352</t>
         </is>
       </c>
       <c r="D558" s="2" t="inlineStr">
         <is>
-          <t>Plumbing Equipment, Fixtures, and Supplies</t>
+          <t>Masterpiece Cattle Lease</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
-        </is>
-      </c>
-      <c r="F558" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>RFP</t>
+        </is>
+      </c>
       <c r="G558" t="inlineStr">
         <is>
           <t>Open</t>
@@ -29415,7 +29455,7 @@
       <c r="I558" s="3" t="inlineStr"/>
       <c r="J558" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-25-303/</t>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-352/</t>
         </is>
       </c>
       <c r="K558" s="4" t="inlineStr">
@@ -29438,12 +29478,12 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Bid 26-349</t>
+          <t>Bid 26-367</t>
         </is>
       </c>
       <c r="D559" s="2" t="inlineStr">
         <is>
-          <t>Pond Mowing and Maintenance – Roads and Drainage</t>
+          <t>Mowing &amp; Maintenance for Utilities – North Region</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -29461,7 +29501,7 @@
       <c r="I559" s="3" t="inlineStr"/>
       <c r="J559" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-349/</t>
+          <t>https://www.polkfl.gov/bid-form/bid-26-367/</t>
         </is>
       </c>
       <c r="K559" s="4" t="inlineStr">
@@ -29484,24 +29524,20 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>RFP 26-387</t>
+          <t>Bid 26-350</t>
         </is>
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>Professional Survey &amp; Mapping Services (CCNA)</t>
+          <t>Mowing and Maintenance for Solid Waste</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
-        </is>
-      </c>
-      <c r="F560" t="inlineStr">
-        <is>
-          <t>RFQ (qualifications)</t>
-        </is>
-      </c>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr"/>
       <c r="G560" t="inlineStr">
         <is>
           <t>Open</t>
@@ -29511,7 +29547,7 @@
       <c r="I560" s="3" t="inlineStr"/>
       <c r="J560" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-387/</t>
+          <t>https://www.polkfl.gov/bid-form/bid-26-350/</t>
         </is>
       </c>
       <c r="K560" s="4" t="inlineStr">
@@ -29534,17 +29570,17 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>CS 26-059</t>
+          <t>Bid 26-295</t>
         </is>
       </c>
       <c r="D561" s="2" t="inlineStr">
         <is>
-          <t>Protective Footwear for Employees</t>
+          <t>Onsite Clinic Services</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -29557,7 +29593,7 @@
       <c r="I561" s="3" t="inlineStr"/>
       <c r="J561" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-26-059/</t>
+          <t>https://www.polkfl.gov/bid-form/bid-26-295/</t>
         </is>
       </c>
       <c r="K561" s="4" t="inlineStr">
@@ -29580,17 +29616,17 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>CS 17-633</t>
+          <t>CS 24-194</t>
         </is>
       </c>
       <c r="D562" s="2" t="inlineStr">
         <is>
-          <t>Radiology Services</t>
+          <t>Overgrowth and Large Lot Clearing</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -29603,7 +29639,7 @@
       <c r="I562" s="3" t="inlineStr"/>
       <c r="J562" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-17-633/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-24-194/</t>
         </is>
       </c>
       <c r="K562" s="4" t="inlineStr">
@@ -29626,12 +29662,12 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Bid 26-372</t>
+          <t>CS 24-195</t>
         </is>
       </c>
       <c r="D563" s="2" t="inlineStr">
         <is>
-          <t>Saddle Creek New Office and Maintenance Buildings</t>
+          <t>Overgrowth and Small Lot Clearing</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -29649,7 +29685,7 @@
       <c r="I563" s="3" t="inlineStr"/>
       <c r="J563" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-372/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-24-195/</t>
         </is>
       </c>
       <c r="K563" s="4" t="inlineStr">
@@ -29672,17 +29708,17 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>CS 25-463</t>
+          <t>CQ 26-343</t>
         </is>
       </c>
       <c r="D564" s="2" t="inlineStr">
         <is>
-          <t>Safety Products and Equipment</t>
+          <t>PCU Administration Building – Conference Room Remodel.</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
@@ -29695,7 +29731,7 @@
       <c r="I564" s="3" t="inlineStr"/>
       <c r="J564" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-25-463/</t>
+          <t>https://www.polkfl.gov/bid-form/cq-26-343/</t>
         </is>
       </c>
       <c r="K564" s="4" t="inlineStr">
@@ -29718,12 +29754,12 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>CS 19-642</t>
+          <t>CS 09-007</t>
         </is>
       </c>
       <c r="D565" s="2" t="inlineStr">
         <is>
-          <t>Securing of Structures</t>
+          <t>Park Service Residents</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -29741,7 +29777,7 @@
       <c r="I565" s="3" t="inlineStr"/>
       <c r="J565" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-19-642/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-09-007/</t>
         </is>
       </c>
       <c r="K565" s="4" t="inlineStr">
@@ -29764,12 +29800,12 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>CS 25-475</t>
+          <t>CS 18-824</t>
         </is>
       </c>
       <c r="D566" s="2" t="inlineStr">
         <is>
-          <t>Sherwin Williams Paint and Supplies</t>
+          <t>Pharmaceuticals for Fire Rescue</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
@@ -29787,7 +29823,7 @@
       <c r="I566" s="3" t="inlineStr"/>
       <c r="J566" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-25-475/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-18-824/</t>
         </is>
       </c>
       <c r="K566" s="4" t="inlineStr">
@@ -29810,17 +29846,17 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>CS 26-238</t>
+          <t>CS 25-303</t>
         </is>
       </c>
       <c r="D567" s="2" t="inlineStr">
         <is>
-          <t>Sign Removal from Rights-of-Way</t>
+          <t>Plumbing Equipment, Fixtures, and Supplies</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -29833,7 +29869,7 @@
       <c r="I567" s="3" t="inlineStr"/>
       <c r="J567" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-26-238/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-25-303/</t>
         </is>
       </c>
       <c r="K567" s="4" t="inlineStr">
@@ -29856,24 +29892,20 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>RFP 26-384</t>
+          <t>Bid 26-349</t>
         </is>
       </c>
       <c r="D568" s="2" t="inlineStr">
         <is>
-          <t>TPA for Off-Site Inmate Medical and Pharmacy Services</t>
+          <t>Pond Mowing and Maintenance – Roads and Drainage</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F568" t="inlineStr">
-        <is>
-          <t>RFP</t>
-        </is>
-      </c>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr"/>
       <c r="G568" t="inlineStr">
         <is>
           <t>Open</t>
@@ -29883,7 +29915,7 @@
       <c r="I568" s="3" t="inlineStr"/>
       <c r="J568" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-384/</t>
+          <t>https://www.polkfl.gov/bid-form/bid-26-349/</t>
         </is>
       </c>
       <c r="K568" s="4" t="inlineStr">
@@ -29906,20 +29938,24 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>CS 24-022</t>
+          <t>RFP 26-387</t>
         </is>
       </c>
       <c r="D569" s="2" t="inlineStr">
         <is>
-          <t>Towing Services for Polk County</t>
+          <t>Professional Survey &amp; Mapping Services (CCNA)</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="F569" t="inlineStr"/>
+          <t>Engineering &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>RFQ (qualifications)</t>
+        </is>
+      </c>
       <c r="G569" t="inlineStr">
         <is>
           <t>Open</t>
@@ -29929,7 +29965,7 @@
       <c r="I569" s="3" t="inlineStr"/>
       <c r="J569" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-24-022/</t>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-387/</t>
         </is>
       </c>
       <c r="K569" s="4" t="inlineStr">
@@ -29952,17 +29988,17 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Bid 26-412</t>
+          <t>CS 26-059</t>
         </is>
       </c>
       <c r="D570" s="2" t="inlineStr">
         <is>
-          <t>Vacuum Truck Cleaning Services for Underground Stormwater Baffle Boxes</t>
+          <t>Protective Footwear for Employees</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -29975,7 +30011,7 @@
       <c r="I570" s="3" t="inlineStr"/>
       <c r="J570" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-412/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-26-059/</t>
         </is>
       </c>
       <c r="K570" s="4" t="inlineStr">
@@ -29998,17 +30034,17 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>CS 21-380</t>
+          <t>CS 17-633</t>
         </is>
       </c>
       <c r="D571" s="2" t="inlineStr">
         <is>
-          <t>Various Medical Related Supplies</t>
+          <t>Radiology Services</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -30021,18 +30057,436 @@
       <c r="I571" s="3" t="inlineStr"/>
       <c r="J571" s="4" t="inlineStr">
         <is>
+          <t>https://www.polkfl.gov/bid-form/cs-17-633/</t>
+        </is>
+      </c>
+      <c r="K571" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Bid 26-372</t>
+        </is>
+      </c>
+      <c r="D572" s="2" t="inlineStr">
+        <is>
+          <t>Saddle Creek New Office and Maintenance Buildings</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr"/>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H572" s="5" t="inlineStr"/>
+      <c r="I572" s="3" t="inlineStr"/>
+      <c r="J572" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/bid-26-372/</t>
+        </is>
+      </c>
+      <c r="K572" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>CS 25-463</t>
+        </is>
+      </c>
+      <c r="D573" s="2" t="inlineStr">
+        <is>
+          <t>Safety Products and Equipment</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr"/>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H573" s="5" t="inlineStr"/>
+      <c r="I573" s="3" t="inlineStr"/>
+      <c r="J573" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/cs-25-463/</t>
+        </is>
+      </c>
+      <c r="K573" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>CS 19-642</t>
+        </is>
+      </c>
+      <c r="D574" s="2" t="inlineStr">
+        <is>
+          <t>Securing of Structures</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr"/>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H574" s="5" t="inlineStr"/>
+      <c r="I574" s="3" t="inlineStr"/>
+      <c r="J574" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/cs-19-642/</t>
+        </is>
+      </c>
+      <c r="K574" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>CS 25-475</t>
+        </is>
+      </c>
+      <c r="D575" s="2" t="inlineStr">
+        <is>
+          <t>Sherwin Williams Paint and Supplies</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr"/>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H575" s="5" t="inlineStr"/>
+      <c r="I575" s="3" t="inlineStr"/>
+      <c r="J575" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/cs-25-475/</t>
+        </is>
+      </c>
+      <c r="K575" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>CS 26-238</t>
+        </is>
+      </c>
+      <c r="D576" s="2" t="inlineStr">
+        <is>
+          <t>Sign Removal from Rights-of-Way</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr"/>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H576" s="5" t="inlineStr"/>
+      <c r="I576" s="3" t="inlineStr"/>
+      <c r="J576" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/cs-26-238/</t>
+        </is>
+      </c>
+      <c r="K576" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>RFP 26-384</t>
+        </is>
+      </c>
+      <c r="D577" s="2" t="inlineStr">
+        <is>
+          <t>TPA for Off-Site Inmate Medical and Pharmacy Services</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>RFP</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H577" s="5" t="inlineStr"/>
+      <c r="I577" s="3" t="inlineStr"/>
+      <c r="J577" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-384/</t>
+        </is>
+      </c>
+      <c r="K577" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>CS 24-022</t>
+        </is>
+      </c>
+      <c r="D578" s="2" t="inlineStr">
+        <is>
+          <t>Towing Services for Polk County</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr"/>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H578" s="5" t="inlineStr"/>
+      <c r="I578" s="3" t="inlineStr"/>
+      <c r="J578" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/cs-24-022/</t>
+        </is>
+      </c>
+      <c r="K578" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Bid 26-412</t>
+        </is>
+      </c>
+      <c r="D579" s="2" t="inlineStr">
+        <is>
+          <t>Vacuum Truck Cleaning Services for Underground Stormwater Baffle Boxes</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr"/>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H579" s="5" t="inlineStr"/>
+      <c r="I579" s="3" t="inlineStr"/>
+      <c r="J579" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/bid-form/bid-26-412/</t>
+        </is>
+      </c>
+      <c r="K579" s="4" t="inlineStr">
+        <is>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Polk</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Polk County BOCC</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>CS 21-380</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>Various Medical Related Supplies</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr"/>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H580" s="5" t="inlineStr"/>
+      <c r="I580" s="3" t="inlineStr"/>
+      <c r="J580" s="4" t="inlineStr">
+        <is>
           <t>https://www.polkfl.gov/bid-form/cs-21-380/</t>
         </is>
       </c>
-      <c r="K571" s="4" t="inlineStr">
+      <c r="K580" s="4" t="inlineStr">
         <is>
           <t>https://www.polkfl.gov/business/procurement/</t>
         </is>
       </c>
-      <c r="L571" t="inlineStr"/>
+      <c r="L580" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L571"/>
+  <autoFilter ref="A1:L580"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId2"/>
@@ -31151,6 +31605,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K570" r:id="rId1115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J571" r:id="rId1116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K571" r:id="rId1117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J572" r:id="rId1118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K572" r:id="rId1119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J573" r:id="rId1120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K573" r:id="rId1121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J574" r:id="rId1122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K574" r:id="rId1123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J575" r:id="rId1124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K575" r:id="rId1125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J576" r:id="rId1126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K576" r:id="rId1127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J577" r:id="rId1128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K577" r:id="rId1129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J578" r:id="rId1130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K578" r:id="rId1131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J579" r:id="rId1132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K579" r:id="rId1133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J580" r:id="rId1134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K580" r:id="rId1135"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31175,7 +31647,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 2026-10-26 11:30 AM (Eastern time)</t>
+          <t>Updated 2026-10-26 11:49 AM (Eastern time)</t>
         </is>
       </c>
     </row>

--- a/site/data/florida-open-bids.xlsx
+++ b/site/data/florida-open-bids.xlsx
@@ -7416,34 +7416,26 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Lutheran Services Florida</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>RFP-2026-010</t>
-        </is>
-      </c>
+          <t>City of Fort Myers</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>RFP-2026-010 Child Care Providers Palm Beach County</t>
+          <t>Dean Park Residential Elevation Project</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>RFP</t>
-        </is>
-      </c>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
           <t>Open</t>
@@ -7453,19 +7445,23 @@
         <v>46325</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
-          <t>https://www.bidnetdirect.com/florida/solicitations/open-bids/RFP-2026-010-Child-Care-Providers-Palm-Beach-County/0000438920?purchasingGroupId=8408751&amp;origin=2</t>
+          <t>https://procurement.opengov.com/portal/cityftmyers</t>
         </is>
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>https://www.bidnetdirect.com/florida/lutheranservicesflorida/solicitations/open-bids?selectedContent=BUYER</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/cityftmyers</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Added by one-time backfill.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7481,7 +7477,7 @@
       <c r="C135" t="inlineStr"/>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Dean Park Residential Elevation Project</t>
+          <t>Downtown Stormwater Drainage Improvements - First Street Flood Risk Reduction Professional Services</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7499,7 +7495,7 @@
         <v>46325</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
@@ -7520,23 +7516,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>City of Fort Myers</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
+          <t>City of Miami Beach</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2027-013-WG</t>
+        </is>
+      </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Downtown Stormwater Drainage Improvements - First Street Flood Risk Reduction Professional Services</t>
+          <t>AGGREGATE, TOPSOIL, AND SAND</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -7549,23 +7549,19 @@
         <v>46325</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/cityftmyers</t>
+          <t>https://www.bidnetdirect.com/florida/solicitations/open-bids/AGGREGATE-TOPSOIL-AND-SAND/0000438877?purchasingGroupId=8408751&amp;origin=2</t>
         </is>
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/cityftmyers</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>Added by one-time backfill.</t>
-        </is>
-      </c>
+          <t>https://www.bidnetdirect.com/florida/cityofmiamibeach/solicitations/open-bids?selectedContent=BUYER</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7575,22 +7571,22 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>City of Miami Beach</t>
+          <t>City of Miami</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2027-013-WG</t>
+          <t>2030386</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>AGGREGATE, TOPSOIL, AND SAND</t>
+          <t>Storm Drainage System Cleaning</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -7603,16 +7599,16 @@
         <v>46325</v>
       </c>
       <c r="I137" s="3" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>https://www.bidnetdirect.com/florida/solicitations/open-bids/AGGREGATE-TOPSOIL-AND-SAND/0000438877?purchasingGroupId=8408751&amp;origin=2</t>
+          <t>https://www.bidnetdirect.com/florida/solicitations/open-bids/Storm-Drainage-System-Cleaning/0000407674?purchasingGroupId=8408751&amp;origin=2</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>https://www.bidnetdirect.com/florida/cityofmiamibeach/solicitations/open-bids?selectedContent=BUYER</t>
+          <t>https://www.bidnetdirect.com/florida/cityofmiami/solicitations/open-bids?selectedContent=BUYER</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -7620,27 +7616,23 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>City of Miami</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>2030386</t>
-        </is>
-      </c>
+          <t>Greater Orlando Aviation Authority</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Storm Drainage System Cleaning</t>
+          <t>Airsides 1 &amp; 3 Pond Dredging (BP-00516)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -7653,35 +7645,39 @@
         <v>46325</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>46295</v>
+        <v>46278</v>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
-          <t>https://www.bidnetdirect.com/florida/solicitations/open-bids/Storm-Drainage-System-Cleaning/0000407674?purchasingGroupId=8408751&amp;origin=2</t>
+          <t>https://procurement.opengov.com/portal/goaa</t>
         </is>
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>https://www.bidnetdirect.com/florida/cityofmiami/solicitations/open-bids?selectedContent=BUYER</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/goaa</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Added by one-time backfill.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Palm Beach</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Greater Orlando Aviation Authority</t>
+          <t>City of Palm Beach Gardens</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Airsides 1 &amp; 3 Pond Dredging (BP-00516)</t>
+          <t>Open Air Pavilion for Gardens North County District Park</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -7699,16 +7695,16 @@
         <v>46325</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>46278</v>
+        <v>46306</v>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/goaa</t>
+          <t>https://procurement.opengov.com/portal/pbgfl</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/goaa</t>
+          <t>https://procurement.opengov.com/portal/pbgfl</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -7725,21 +7721,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>City of Palm Beach Gardens</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
+          <t>Lutheran Services Florida</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>RFP-2026-010</t>
+        </is>
+      </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Open Air Pavilion for Gardens North County District Park</t>
+          <t>RFP-2026-010 Child Care Providers Palm Beach County</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>RFP</t>
+        </is>
+      </c>
       <c r="G140" t="inlineStr">
         <is>
           <t>Open</t>
@@ -7749,23 +7753,19 @@
         <v>46325</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>46306</v>
+        <v>46296</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/pbgfl</t>
+          <t>https://www.bidnetdirect.com/florida/solicitations/open-bids/RFP-2026-010-Child-Care-Providers-Palm-Beach-County/0000438920?purchasingGroupId=8408751&amp;origin=2</t>
         </is>
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/pbgfl</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>Added by one-time backfill.</t>
-        </is>
-      </c>
+          <t>https://www.bidnetdirect.com/florida/lutheranservicesflorida/solicitations/open-bids?selectedContent=BUYER</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -34147,7 +34147,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 2026-10-26 02:06 PM (Eastern time)</t>
+          <t>Updated 2026-10-26 03:01 PM (Eastern time)</t>
         </is>
       </c>
     </row>

--- a/site/data/florida-open-bids.xlsx
+++ b/site/data/florida-open-bids.xlsx
@@ -34147,7 +34147,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 2026-10-26 03:01 PM (Eastern time)</t>
+          <t>Updated 2026-10-26 03:13 PM (Eastern time)</t>
         </is>
       </c>
     </row>

--- a/site/data/florida-open-bids.xlsx
+++ b/site/data/florida-open-bids.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Open solicitations'!$A$1:$L$629</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Open solicitations'!$A$1:$L$633</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L629"/>
+  <dimension ref="A1:L633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11535,17 +11535,17 @@
       <c r="I212" s="3" t="inlineStr"/>
       <c r="J212" s="4" t="inlineStr">
         <is>
+          <t>https://stpetebeach.bonfirehub.com/opportunities/256236</t>
+        </is>
+      </c>
+      <c r="K212" s="4" t="inlineStr">
+        <is>
           <t>https://stpetebeach.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
-      <c r="K212" s="4" t="inlineStr">
-        <is>
-          <t>https://stpetebeach.bonfirehub.com/portal/?tab=openOpportunities</t>
-        </is>
-      </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>Added by one-time backfill.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
@@ -21175,17 +21175,17 @@
       <c r="I396" s="3" t="inlineStr"/>
       <c r="J396" s="4" t="inlineStr">
         <is>
-          <t>https://sfrta.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://tri-rail.bonfirehub.com/opportunities/248355</t>
         </is>
       </c>
       <c r="K396" s="4" t="inlineStr">
         <is>
-          <t>https://sfrta.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://tri-rail.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>Added by one-time backfill.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
@@ -22739,17 +22739,17 @@
       <c r="I426" s="3" t="inlineStr"/>
       <c r="J426" s="4" t="inlineStr">
         <is>
+          <t>https://swa.bonfirehub.com/opportunities/252493</t>
+        </is>
+      </c>
+      <c r="K426" s="4" t="inlineStr">
+        <is>
           <t>https://swa.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
-      <c r="K426" s="4" t="inlineStr">
-        <is>
-          <t>https://swa.bonfirehub.com/portal/?tab=openOpportunities</t>
-        </is>
-      </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>Added by one-time backfill.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
@@ -28436,27 +28436,27 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Broward</t>
+          <t>Brevard</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>City of Wilton Manors</t>
+          <t>City of Palm Bay</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>NIGP 2026</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>2026-05 Parking Management Services</t>
+          <t>Central Florida Chapter of NIGP 2026 Reverse Trade Show</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Concessions &amp; Programs</t>
+          <t>Notices &amp; Events</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -28469,44 +28469,44 @@
       <c r="I536" s="3" t="inlineStr"/>
       <c r="J536" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=153</t>
+          <t>https://palmbayflorida.bonfirehub.com/opportunities/230782</t>
         </is>
       </c>
       <c r="K536" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx</t>
+          <t>https://palmbayflorida.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>Closes: Upon Contract</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Broward</t>
+          <t>Brevard</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>City of Wilton Manors</t>
+          <t>City of Palm Bay</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>#258632</t>
         </is>
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>2026-10 Tidal Valve Program</t>
+          <t>Palm Bay Aquatic Center</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -28519,44 +28519,44 @@
       <c r="I537" s="3" t="inlineStr"/>
       <c r="J537" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=159</t>
+          <t>https://palmbayflorida.bonfirehub.com/opportunities/258632</t>
         </is>
       </c>
       <c r="K537" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx</t>
+          <t>https://palmbayflorida.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>Closes: Upon Contract</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Broward</t>
+          <t>Brevard</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>City of Wilton Manors</t>
+          <t>City of Palm Bay</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>2026-13</t>
+          <t>#255878</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>2026-13 Justin Flippen Park Electrical Upgrades</t>
+          <t>Pond Improvements Cadillac Drive &amp; RJ Conlan - Re-Bid</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -28569,17 +28569,17 @@
       <c r="I538" s="3" t="inlineStr"/>
       <c r="J538" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=160</t>
+          <t>https://palmbayflorida.bonfirehub.com/opportunities/255878</t>
         </is>
       </c>
       <c r="K538" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx</t>
+          <t>https://palmbayflorida.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t>Closes: Upon Contract</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
@@ -28596,17 +28596,17 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>2026-14 - Re-Bid</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="D539" s="2" t="inlineStr">
         <is>
-          <t>2026-14 51st Year CDBG Mickel Park Electrical Upgrades - Re-Bid</t>
+          <t>2026-05 Parking Management Services</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Concessions &amp; Programs</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -28619,7 +28619,7 @@
       <c r="I539" s="3" t="inlineStr"/>
       <c r="J539" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=165</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=153</t>
         </is>
       </c>
       <c r="K539" s="4" t="inlineStr">
@@ -28646,17 +28646,17 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>2026-15</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
-          <t>2026-15 Emergency and Special Event Catering</t>
+          <t>2026-10 Tidal Valve Program</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>Concessions &amp; Programs</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -28669,7 +28669,7 @@
       <c r="I540" s="3" t="inlineStr"/>
       <c r="J540" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=162</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=159</t>
         </is>
       </c>
       <c r="K540" s="4" t="inlineStr">
@@ -28696,12 +28696,12 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>2026-16</t>
+          <t>2026-13</t>
         </is>
       </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
-          <t>2026-16 Lift Station No. 1 Replacement</t>
+          <t>2026-13 Justin Flippen Park Electrical Upgrades</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
@@ -28719,7 +28719,7 @@
       <c r="I541" s="3" t="inlineStr"/>
       <c r="J541" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=163</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=160</t>
         </is>
       </c>
       <c r="K541" s="4" t="inlineStr">
@@ -28746,12 +28746,12 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2026-14 - Re-Bid</t>
         </is>
       </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
-          <t>2027-01 Lift Station No. 4 Replacement</t>
+          <t>2026-14 51st Year CDBG Mickel Park Electrical Upgrades - Re-Bid</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -28769,7 +28769,7 @@
       <c r="I542" s="3" t="inlineStr"/>
       <c r="J542" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=164</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=165</t>
         </is>
       </c>
       <c r="K542" s="4" t="inlineStr">
@@ -28796,17 +28796,17 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-15</t>
         </is>
       </c>
       <c r="D543" s="2" t="inlineStr">
         <is>
-          <t>2027-02 Lift Station No. 7 Replacement</t>
+          <t>2026-15 Emergency and Special Event Catering</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Concessions &amp; Programs</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
@@ -28819,7 +28819,7 @@
       <c r="I543" s="3" t="inlineStr"/>
       <c r="J543" s="4" t="inlineStr">
         <is>
-          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=166</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=162</t>
         </is>
       </c>
       <c r="K543" s="4" t="inlineStr">
@@ -28841,22 +28841,22 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>City of Dania Beach</t>
+          <t>City of Wilton Manors</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>#304804</t>
+          <t>2026-16</t>
         </is>
       </c>
       <c r="D544" s="2" t="inlineStr">
         <is>
-          <t>Dania Beach Blvd Landscape Improvements Grant Section #1 (West) &amp; Grant Section #2 (East)</t>
+          <t>2026-16 Lift Station No. 1 Replacement</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -28869,17 +28869,17 @@
       <c r="I544" s="3" t="inlineStr"/>
       <c r="J544" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/daniabeachfl/projects/304804</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=163</t>
         </is>
       </c>
       <c r="K544" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/daniabeachfl</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx</t>
         </is>
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t>From the agency's email alert.</t>
+          <t>Closes: Upon Contract</t>
         </is>
       </c>
     </row>
@@ -28891,22 +28891,22 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>City of Hollywood</t>
+          <t>City of Wilton Manors</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>#319675</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="D545" s="2" t="inlineStr">
         <is>
-          <t>Meter Transmission Unit / VertexOne Consumer Portal</t>
+          <t>2027-01 Lift Station No. 4 Replacement</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -28919,17 +28919,17 @@
       <c r="I545" s="3" t="inlineStr"/>
       <c r="J545" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/hollywoodfl/projects/319675</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=164</t>
         </is>
       </c>
       <c r="K545" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/hollywoodfl</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t>From the agency's email alert.</t>
+          <t>Closes: Upon Contract</t>
         </is>
       </c>
     </row>
@@ -28941,29 +28941,25 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Broward County BOCC</t>
+          <t>City of Wilton Manors</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>#254086</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
-          <t>Pre-Solicitation Notice - Draft Computer Aided Dispatch/Automatic Vehicle Location System</t>
+          <t>2027-02 Lift Station No. 7 Replacement</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>IT &amp; Technology</t>
-        </is>
-      </c>
-      <c r="F546" t="inlineStr">
-        <is>
-          <t>Draft / Future</t>
-        </is>
-      </c>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr"/>
       <c r="G546" t="inlineStr">
         <is>
           <t>Open</t>
@@ -28973,17 +28969,17 @@
       <c r="I546" s="3" t="inlineStr"/>
       <c r="J546" s="4" t="inlineStr">
         <is>
-          <t>https://broward.bonfirehub.com/opportunities/254086</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx?bidID=166</t>
         </is>
       </c>
       <c r="K546" s="4" t="inlineStr">
         <is>
-          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://www.wiltonmanors.gov/bids.aspx</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t>From the agency's email alert.</t>
+          <t>Closes: Upon Contract</t>
         </is>
       </c>
     </row>
@@ -28995,22 +28991,22 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>City of Hollywood</t>
+          <t>City of Dania Beach</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>#313307</t>
+          <t>#304804</t>
         </is>
       </c>
       <c r="D547" s="2" t="inlineStr">
         <is>
-          <t>Water Treatment Plant MS/RO Chemical Area Recoating; Project No. 25-4262A</t>
+          <t>Dania Beach Blvd Landscape Improvements Grant Section #1 (West) &amp; Grant Section #2 (East)</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -29023,12 +29019,12 @@
       <c r="I547" s="3" t="inlineStr"/>
       <c r="J547" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/hollywoodfl/projects/313307</t>
+          <t>https://procurement.opengov.com/portal/daniabeachfl/projects/304804</t>
         </is>
       </c>
       <c r="K547" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/hollywoodfl</t>
+          <t>https://procurement.opengov.com/portal/daniabeachfl</t>
         </is>
       </c>
       <c r="L547" t="inlineStr">
@@ -29050,12 +29046,12 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>#313241</t>
+          <t>#319675</t>
         </is>
       </c>
       <c r="D548" s="2" t="inlineStr">
         <is>
-          <t>Water Treatment Plant Maintenance Package 'B'; Project No. 25-4262</t>
+          <t>Meter Transmission Unit / VertexOne Consumer Portal</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -29073,7 +29069,7 @@
       <c r="I548" s="3" t="inlineStr"/>
       <c r="J548" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/hollywoodfl/projects/313241</t>
+          <t>https://procurement.opengov.com/portal/hollywoodfl/projects/319675</t>
         </is>
       </c>
       <c r="K548" s="4" t="inlineStr">
@@ -29090,30 +29086,34 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Clay</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>City of Green Cove Springs</t>
+          <t>Broward County BOCC</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>#320490</t>
+          <t>#254086</t>
         </is>
       </c>
       <c r="D549" s="2" t="inlineStr">
         <is>
-          <t>DEP SRF Harbor Road WRF Expansion, Phase 3 - Reclaimed Water Ground Storage Tank</t>
+          <t>Pre-Solicitation Notice - Draft Computer Aided Dispatch/Automatic Vehicle Location System</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F549" t="inlineStr"/>
+          <t>IT &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Draft / Future</t>
+        </is>
+      </c>
       <c r="G549" t="inlineStr">
         <is>
           <t>Open</t>
@@ -29123,12 +29123,12 @@
       <c r="I549" s="3" t="inlineStr"/>
       <c r="J549" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/greencovesprings/projects/320490</t>
+          <t>https://broward.bonfirehub.com/opportunities/254086</t>
         </is>
       </c>
       <c r="K549" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/greencovesprings</t>
+          <t>https://broward.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
@@ -29140,122 +29140,122 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Duval</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>JAXPORT</t>
+          <t>City of Hollywood</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>ITB_EQ-2039A</t>
+          <t>#313307</t>
         </is>
       </c>
       <c r="D550" s="2" t="inlineStr">
         <is>
-          <t>BLOUNT ISLAND MARINE TERMINAL HANJUNG CRANE #8841 REFURBISHMENT</t>
+          <t>Water Treatment Plant MS/RO Chemical Area Recoating; Project No. 25-4262A</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F550" t="inlineStr">
-        <is>
-          <t>ITB</t>
-        </is>
-      </c>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr"/>
       <c r="G550" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H550" s="5" t="inlineStr"/>
       <c r="I550" s="3" t="inlineStr"/>
       <c r="J550" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14412/?sort%5B7%5D=asc</t>
+          <t>https://procurement.opengov.com/portal/hollywoodfl/projects/313307</t>
         </is>
       </c>
       <c r="K550" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
-        </is>
-      </c>
-      <c r="L550" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/hollywoodfl</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Duval</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>JAXPORT</t>
+          <t>City of Hollywood</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>RFQ_AE-178DR</t>
+          <t>#313241</t>
         </is>
       </c>
       <c r="D551" s="2" t="inlineStr">
         <is>
-          <t>CRANE ENGINEERING SERVICES (REBID)</t>
+          <t>Water Treatment Plant Maintenance Package 'B'; Project No. 25-4262</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
-        </is>
-      </c>
-      <c r="F551" t="inlineStr">
-        <is>
-          <t>ITB</t>
-        </is>
-      </c>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr"/>
       <c r="G551" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H551" s="5" t="inlineStr"/>
       <c r="I551" s="3" t="inlineStr"/>
       <c r="J551" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14356/?sort%5B7%5D=asc</t>
+          <t>https://procurement.opengov.com/portal/hollywoodfl/projects/313241</t>
         </is>
       </c>
       <c r="K551" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
-        </is>
-      </c>
-      <c r="L551" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/hollywoodfl</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Duval</t>
+          <t>Clay</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>JAXPORT</t>
+          <t>City of Green Cove Springs</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>ITB_MC-2132</t>
+          <t>#320490</t>
         </is>
       </c>
       <c r="D552" s="2" t="inlineStr">
         <is>
-          <t>INTSALLATION OF NEW CRANE STOW PIN SOCKETS AT THE TALLEYRAND MARINE TERMINAL (TMT)</t>
+          <t>DEP SRF Harbor Road WRF Expansion, Phase 3 - Reclaimed Water Ground Storage Tank</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -29263,29 +29263,29 @@
           <t>Construction</t>
         </is>
       </c>
-      <c r="F552" t="inlineStr">
-        <is>
-          <t>ITB</t>
-        </is>
-      </c>
+      <c r="F552" t="inlineStr"/>
       <c r="G552" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H552" s="5" t="inlineStr"/>
       <c r="I552" s="3" t="inlineStr"/>
       <c r="J552" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14410/?sort%5B7%5D=asc</t>
+          <t>https://procurement.opengov.com/portal/greencovesprings/projects/320490</t>
         </is>
       </c>
       <c r="K552" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
-        </is>
-      </c>
-      <c r="L552" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/greencovesprings</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -29300,22 +29300,22 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>PSS # EQ-2128</t>
+          <t>ITB_EQ-2039A</t>
         </is>
       </c>
       <c r="D553" s="2" t="inlineStr">
         <is>
-          <t>Purchase of three (3) Elevator Safety Devices</t>
+          <t>BLOUNT ISLAND MARINE TERMINAL HANJUNG CRANE #8841 REFURBISHMENT</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>Sole source</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
@@ -29327,7 +29327,7 @@
       <c r="I553" s="3" t="inlineStr"/>
       <c r="J553" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14104/?sort%5B7%5D=asc</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14412/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K553" s="4" t="inlineStr">
@@ -29350,22 +29350,22 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>PSS # MC-2017AJ</t>
+          <t>RFQ_AE-178DR</t>
         </is>
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
-          <t>Repair and Replacement of Four (4) Canopies for Jacksonville Port Authority, Dames Point Cruise Terminal</t>
+          <t>CRANE ENGINEERING SERVICES (REBID)</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>Sole source</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
@@ -29377,7 +29377,7 @@
       <c r="I554" s="3" t="inlineStr"/>
       <c r="J554" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14389/?sort%5B7%5D=asc</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14356/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K554" s="4" t="inlineStr">
@@ -29400,12 +29400,12 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>ITB C-2131</t>
+          <t>ITB_MC-2132</t>
         </is>
       </c>
       <c r="D555" s="2" t="inlineStr">
         <is>
-          <t>TALLEYRAND MARINE TERMINAL (TMT) PILE, CAP, AND BEAM REHAB</t>
+          <t>INTSALLATION OF NEW CRANE STOW PIN SOCKETS AT THE TALLEYRAND MARINE TERMINAL (TMT)</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
@@ -29427,7 +29427,7 @@
       <c r="I555" s="3" t="inlineStr"/>
       <c r="J555" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14384/?sort%5B7%5D=asc</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14410/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K555" s="4" t="inlineStr">
@@ -29450,22 +29450,22 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>ITB_MC-2108N</t>
+          <t>PSS # EQ-2128</t>
         </is>
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
-          <t>TPO ROOF RETROFITS AT TMT AUTO FACILITY</t>
+          <t>Purchase of three (3) Elevator Safety Devices</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>Sole source</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
@@ -29477,7 +29477,7 @@
       <c r="I556" s="3" t="inlineStr"/>
       <c r="J556" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14333/?sort%5B7%5D=asc</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14104/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K556" s="4" t="inlineStr">
@@ -29500,17 +29500,17 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>PSS # EQ-2095A</t>
+          <t>PSS # MC-2017AJ</t>
         </is>
       </c>
       <c r="D557" s="2" t="inlineStr">
         <is>
-          <t>The purchase of two (2) new-surplus CAT 270-3504 radiator assemblies</t>
+          <t>Repair and Replacement of Four (4) Canopies for Jacksonville Port Authority, Dames Point Cruise Terminal</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
@@ -29527,7 +29527,7 @@
       <c r="I557" s="3" t="inlineStr"/>
       <c r="J557" s="4" t="inlineStr">
         <is>
-          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14299/?sort%5B7%5D=asc</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14389/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K557" s="4" t="inlineStr">
@@ -29540,184 +29540,184 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Duval</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>City of Tampa</t>
+          <t>JAXPORT</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>#320261</t>
+          <t>ITB C-2131</t>
         </is>
       </c>
       <c r="D558" s="2" t="inlineStr">
         <is>
-          <t>Intent to Single Source for Hach Equipment, Parts, and Service</t>
+          <t>TALLEYRAND MARINE TERMINAL (TMT) PILE, CAP, AND BEAM REHAB</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>Sole source</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H558" s="5" t="inlineStr"/>
       <c r="I558" s="3" t="inlineStr"/>
       <c r="J558" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/cityoftampa/projects/320261</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14384/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K558" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/cityoftampa</t>
-        </is>
-      </c>
-      <c r="L558" t="inlineStr">
-        <is>
-          <t>From the agency's email alert.</t>
-        </is>
-      </c>
+          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Duval</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Hillsborough County BOCC</t>
+          <t>JAXPORT</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>#251584</t>
+          <t>ITB_MC-2108N</t>
         </is>
       </c>
       <c r="D559" s="2" t="inlineStr">
         <is>
-          <t>Misc. Professional Stormwater Services</t>
+          <t>TPO ROOF RETROFITS AT TMT AUTO FACILITY</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
-        </is>
-      </c>
-      <c r="F559" t="inlineStr"/>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>ITB</t>
+        </is>
+      </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H559" s="5" t="inlineStr"/>
       <c r="I559" s="3" t="inlineStr"/>
       <c r="J559" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/251584</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14333/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K559" s="4" t="inlineStr">
         <is>
-          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
-        </is>
-      </c>
-      <c r="L559" t="inlineStr">
-        <is>
-          <t>From the agency's email alert.</t>
-        </is>
-      </c>
+          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Duval</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>City of Fort Myers</t>
+          <t>JAXPORT</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>#320240</t>
+          <t>PSS # EQ-2095A</t>
         </is>
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>Composite Access Products LP (CAP)</t>
+          <t>The purchase of two (2) new-surplus CAT 270-3504 radiator assemblies</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F560" t="inlineStr"/>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Sole source</t>
+        </is>
+      </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H560" s="5" t="inlineStr"/>
       <c r="I560" s="3" t="inlineStr"/>
       <c r="J560" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/cityftmyers/projects/320240</t>
+          <t>https://www.jaxport.com/procurement/active-solicitations/entry/14299/?sort%5B7%5D=asc</t>
         </is>
       </c>
       <c r="K560" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/cityftmyers</t>
-        </is>
-      </c>
-      <c r="L560" t="inlineStr">
-        <is>
-          <t>From the agency's email alert.</t>
-        </is>
-      </c>
+          <t>https://www.jaxport.com/procurement/active-solicitations/?sort[7]=asc</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>City of Cape Coral</t>
+          <t>City of Tampa</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>#300122</t>
+          <t>#320261</t>
         </is>
       </c>
       <c r="D561" s="2" t="inlineStr">
         <is>
-          <t>Construction Manager at Risk (CMAR) for Projects less than $4 Million</t>
+          <t>Intent to Single Source for Hach Equipment, Parts, and Service</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F561" t="inlineStr"/>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Sole source</t>
+        </is>
+      </c>
       <c r="G561" t="inlineStr">
         <is>
           <t>Open</t>
@@ -29727,12 +29727,12 @@
       <c r="I561" s="3" t="inlineStr"/>
       <c r="J561" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/capecoralfl/projects/300122</t>
+          <t>https://procurement.opengov.com/portal/cityoftampa/projects/320261</t>
         </is>
       </c>
       <c r="K561" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/capecoralfl</t>
+          <t>https://procurement.opengov.com/portal/cityoftampa</t>
         </is>
       </c>
       <c r="L561" t="inlineStr">
@@ -29744,22 +29744,22 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
+          <t>Hillsborough County BOCC</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>A26PM01</t>
+          <t>#251584</t>
         </is>
       </c>
       <c r="D562" s="2" t="inlineStr">
         <is>
-          <t>A/E Services for Real Estate</t>
+          <t>Misc. Professional Stormwater Services</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -29767,189 +29767,177 @@
           <t>Engineering &amp; Architecture</t>
         </is>
       </c>
-      <c r="F562" t="inlineStr">
-        <is>
-          <t>Draft / Future</t>
-        </is>
-      </c>
+      <c r="F562" t="inlineStr"/>
       <c r="G562" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H562" s="5" t="inlineStr"/>
-      <c r="I562" s="3" t="n">
-        <v>46315</v>
-      </c>
+      <c r="I562" s="3" t="inlineStr"/>
       <c r="J562" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8983</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/opportunities/251584</t>
         </is>
       </c>
       <c r="K562" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+          <t>https://hillsboroughcounty.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t>Draft for feedback. Send comments to Julie Whiteside (Julie.whiteside@miamidade.gov). Posted until 2026-11-10.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
-        </is>
-      </c>
-      <c r="C563" t="inlineStr"/>
+          <t>City of Fort Myers</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>#320240</t>
+        </is>
+      </c>
       <c r="D563" s="2" t="inlineStr">
         <is>
-          <t>Access Control Point Barrier Systems</t>
+          <t>Composite Access Products LP (CAP)</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>IT &amp; Technology</t>
-        </is>
-      </c>
-      <c r="F563" t="inlineStr">
-        <is>
-          <t>Draft / Future</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr"/>
       <c r="G563" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H563" s="5" t="inlineStr"/>
-      <c r="I563" s="3" t="n">
-        <v>46302</v>
-      </c>
+      <c r="I563" s="3" t="inlineStr"/>
       <c r="J563" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8975</t>
+          <t>https://procurement.opengov.com/portal/cityftmyers/projects/320240</t>
         </is>
       </c>
       <c r="K563" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+          <t>https://procurement.opengov.com/portal/cityftmyers</t>
         </is>
       </c>
       <c r="L563" t="inlineStr">
         <is>
-          <t>Draft for feedback. Send comments to Amy Almanzar (Amy.almanzar@miamidade.gov). Posted until 2026-10-27.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
-        </is>
-      </c>
-      <c r="C564" t="inlineStr"/>
+          <t>City of Cape Coral</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>#300122</t>
+        </is>
+      </c>
       <c r="D564" s="2" t="inlineStr">
         <is>
-          <t>E26WS02 - REPOST - GEOTECHNICAL SRVS, STRUCTURAL ASSESSMENT, MATERIALS TEST</t>
+          <t>Construction Manager at Risk (CMAR) for Projects less than $4 Million</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
-        </is>
-      </c>
-      <c r="F564" t="inlineStr">
-        <is>
-          <t>Draft / Future</t>
-        </is>
-      </c>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr"/>
       <c r="G564" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H564" s="5" t="inlineStr"/>
-      <c r="I564" s="3" t="n">
-        <v>46315</v>
-      </c>
+      <c r="I564" s="3" t="inlineStr"/>
       <c r="J564" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8981</t>
+          <t>https://procurement.opengov.com/portal/capecoralfl/projects/300122</t>
         </is>
       </c>
       <c r="K564" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+          <t>https://procurement.opengov.com/portal/capecoralfl</t>
         </is>
       </c>
       <c r="L564" t="inlineStr">
         <is>
-          <t>Draft for feedback. Send comments to Ana M. DaSilva (ana.dasilva@miamidade.gov). Posted until 2026-11-09.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Miami-Dade County</t>
-        </is>
-      </c>
-      <c r="C565" t="inlineStr"/>
+          <t>City of Tallahassee</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>#251608</t>
+        </is>
+      </c>
       <c r="D565" s="2" t="inlineStr">
         <is>
-          <t>Summer Food Service Program</t>
+          <t>Northwest Connector Corridor- Tharpe Street Civil Engineering Design Services</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>Concessions &amp; Programs</t>
-        </is>
-      </c>
-      <c r="F565" t="inlineStr">
-        <is>
-          <t>Draft / Future</t>
-        </is>
-      </c>
+          <t>Engineering &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr"/>
       <c r="G565" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H565" s="5" t="inlineStr"/>
-      <c r="I565" s="3" t="n">
-        <v>46295</v>
-      </c>
+      <c r="I565" s="3" t="inlineStr"/>
       <c r="J565" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8973</t>
+          <t>https://talgov.bonfirehub.com/opportunities/251608</t>
         </is>
       </c>
       <c r="K565" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
+          <t>https://talgov.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L565" t="inlineStr">
         <is>
-          <t>Draft for feedback. Send comments to Leslie Zambrana (leslie.zambrana@miamidade.gov). Posted until 2026-10-30.</t>
+          <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
@@ -29964,15 +29952,19 @@
           <t>Miami-Dade County</t>
         </is>
       </c>
-      <c r="C566" t="inlineStr"/>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>A26PM01</t>
+        </is>
+      </c>
       <c r="D566" s="2" t="inlineStr">
         <is>
-          <t>Third-Party Inspection Services for Elevators, Escalators, and Other Convey</t>
+          <t>A/E Services for Real Estate</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
@@ -29991,7 +29983,7 @@
       </c>
       <c r="J566" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8980</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8983</t>
         </is>
       </c>
       <c r="K566" s="4" t="inlineStr">
@@ -30001,7 +29993,7 @@
       </c>
       <c r="L566" t="inlineStr">
         <is>
-          <t>Draft for feedback. Send comments to Richard Celestin (richard.celestin@miamidade.gov). Posted until 2026-10-27.</t>
+          <t>Draft for feedback. Send comments to Julie Whiteside (Julie.whiteside@miamidade.gov). Posted until 2026-11-10.</t>
         </is>
       </c>
     </row>
@@ -30016,19 +30008,15 @@
           <t>Miami-Dade County</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr">
-        <is>
-          <t>E26PM01</t>
-        </is>
-      </c>
+      <c r="C567" t="inlineStr"/>
       <c r="D567" s="2" t="inlineStr">
         <is>
-          <t>Water Remediation Pool</t>
+          <t>Access Control Point Barrier Systems</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
@@ -30043,11 +30031,11 @@
       </c>
       <c r="H567" s="5" t="inlineStr"/>
       <c r="I567" s="3" t="n">
-        <v>46315</v>
+        <v>46302</v>
       </c>
       <c r="J567" s="4" t="inlineStr">
         <is>
-          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8984</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8975</t>
         </is>
       </c>
       <c r="K567" s="4" t="inlineStr">
@@ -30057,29 +30045,25 @@
       </c>
       <c r="L567" t="inlineStr">
         <is>
-          <t>Draft for feedback. Send comments to Julie Whiteside (Julie.whiteside@miamidade.gov). Posted until 2026-11-10.</t>
+          <t>Draft for feedback. Send comments to Amy Almanzar (Amy.almanzar@miamidade.gov). Posted until 2026-10-27.</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Monroe</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Monroe County BOCC</t>
-        </is>
-      </c>
-      <c r="C568" t="inlineStr">
-        <is>
-          <t>#257290</t>
-        </is>
-      </c>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr"/>
       <c r="D568" s="2" t="inlineStr">
         <is>
-          <t>Construction, Engineering and Inspection Services for Key Deer Blvd (North of Watson Blvd) Roadway Rehabilitation Project</t>
+          <t>E26WS02 - REPOST - GEOTECHNICAL SRVS, STRUCTURAL ASSESSMENT, MATERIALS TEST</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
@@ -30087,177 +30071,193 @@
           <t>Engineering &amp; Architecture</t>
         </is>
       </c>
-      <c r="F568" t="inlineStr"/>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Draft / Future</t>
+        </is>
+      </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="H568" s="5" t="inlineStr"/>
-      <c r="I568" s="3" t="inlineStr"/>
+      <c r="I568" s="3" t="n">
+        <v>46315</v>
+      </c>
       <c r="J568" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/opportunities/257290</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8981</t>
         </is>
       </c>
       <c r="K568" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
         </is>
       </c>
       <c r="L568" t="inlineStr">
         <is>
-          <t>From the agency's email alert.</t>
+          <t>Draft for feedback. Send comments to Ana M. DaSilva (ana.dasilva@miamidade.gov). Posted until 2026-11-09.</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Monroe</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Monroe County BOCC</t>
-        </is>
-      </c>
-      <c r="C569" t="inlineStr">
-        <is>
-          <t>#259466</t>
-        </is>
-      </c>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr"/>
       <c r="D569" s="2" t="inlineStr">
         <is>
-          <t>Ellis Building Interior Renovation</t>
+          <t>Summer Food Service Program</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>Construction</t>
-        </is>
-      </c>
-      <c r="F569" t="inlineStr"/>
+          <t>Concessions &amp; Programs</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Draft / Future</t>
+        </is>
+      </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="H569" s="5" t="inlineStr"/>
-      <c r="I569" s="3" t="inlineStr"/>
+      <c r="I569" s="3" t="n">
+        <v>46295</v>
+      </c>
       <c r="J569" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/opportunities/259466</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8973</t>
         </is>
       </c>
       <c r="K569" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
         </is>
       </c>
       <c r="L569" t="inlineStr">
         <is>
-          <t>From the agency's email alert.</t>
+          <t>Draft for feedback. Send comments to Leslie Zambrana (leslie.zambrana@miamidade.gov). Posted until 2026-10-30.</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Monroe</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Monroe County BOCC</t>
-        </is>
-      </c>
-      <c r="C570" t="inlineStr">
-        <is>
-          <t>#256505</t>
-        </is>
-      </c>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr"/>
       <c r="D570" s="2" t="inlineStr">
         <is>
-          <t>Latin America Sales Agency for Monroe County Tourist Development Council</t>
+          <t>Third-Party Inspection Services for Elevators, Escalators, and Other Convey</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F570" t="inlineStr"/>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Draft / Future</t>
+        </is>
+      </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="H570" s="5" t="inlineStr"/>
-      <c r="I570" s="3" t="inlineStr"/>
+      <c r="I570" s="3" t="n">
+        <v>46315</v>
+      </c>
       <c r="J570" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/opportunities/256505</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8980</t>
         </is>
       </c>
       <c r="K570" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t>From the agency's email alert.</t>
+          <t>Draft for feedback. Send comments to Richard Celestin (richard.celestin@miamidade.gov). Posted until 2026-10-27.</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Monroe</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Monroe County BOCC</t>
+          <t>Miami-Dade County</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>#235838</t>
+          <t>E26PM01</t>
         </is>
       </c>
       <c r="D571" s="2" t="inlineStr">
         <is>
-          <t>Multifamily SHIP Application 2025 RFA</t>
+          <t>Water Remediation Pool</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>IT &amp; Technology</t>
-        </is>
-      </c>
-      <c r="F571" t="inlineStr"/>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Draft / Future</t>
+        </is>
+      </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="H571" s="5" t="inlineStr"/>
-      <c r="I571" s="3" t="inlineStr"/>
+      <c r="I571" s="3" t="n">
+        <v>46315</v>
+      </c>
       <c r="J571" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/opportunities/235838</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitationDetails?webPostingCounter=8984</t>
         </is>
       </c>
       <c r="K571" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
+          <t>https://www.miamidade.gov/apps/isd/StratProc/Home/FutureSolicitations</t>
         </is>
       </c>
       <c r="L571" t="inlineStr">
         <is>
-          <t>From the agency's email alert.</t>
+          <t>Draft for feedback. Send comments to Julie Whiteside (Julie.whiteside@miamidade.gov). Posted until 2026-11-10.</t>
         </is>
       </c>
     </row>
@@ -30274,12 +30274,12 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>#256340</t>
+          <t>#257290</t>
         </is>
       </c>
       <c r="D572" s="2" t="inlineStr">
         <is>
-          <t>Professional Architectural and Engineering Continuing Services</t>
+          <t>Construction, Engineering and Inspection Services for Key Deer Blvd (North of Watson Blvd) Roadway Rehabilitation Project</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -30297,7 +30297,7 @@
       <c r="I572" s="3" t="inlineStr"/>
       <c r="J572" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/opportunities/256340</t>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/257290</t>
         </is>
       </c>
       <c r="K572" s="4" t="inlineStr">
@@ -30324,17 +30324,17 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>#255496</t>
+          <t>#259466</t>
         </is>
       </c>
       <c r="D573" s="2" t="inlineStr">
         <is>
-          <t>Professional Surveying Continuing Services</t>
+          <t>Ellis Building Interior Renovation</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F573" t="inlineStr"/>
@@ -30347,7 +30347,7 @@
       <c r="I573" s="3" t="inlineStr"/>
       <c r="J573" s="4" t="inlineStr">
         <is>
-          <t>https://monroecounty-fl.bonfirehub.com/opportunities/255496</t>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/259466</t>
         </is>
       </c>
       <c r="K573" s="4" t="inlineStr">
@@ -30364,27 +30364,27 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Okaloosa</t>
+          <t>Monroe</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Okaloosa County BOCC</t>
+          <t>Monroe County BOCC</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>#315955</t>
+          <t>#256505</t>
         </is>
       </c>
       <c r="D574" s="2" t="inlineStr">
         <is>
-          <t>Covered Walkway Phase 2</t>
+          <t>Latin America Sales Agency for Monroe County Tourist Development Council</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -30397,12 +30397,12 @@
       <c r="I574" s="3" t="inlineStr"/>
       <c r="J574" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/myokaloosa/projects/315955</t>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/256505</t>
         </is>
       </c>
       <c r="K574" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/myokaloosa</t>
+          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L574" t="inlineStr">
@@ -30414,27 +30414,27 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Okaloosa</t>
+          <t>Monroe</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Okaloosa County BOCC</t>
+          <t>Monroe County BOCC</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>#312231</t>
+          <t>#235838</t>
         </is>
       </c>
       <c r="D575" s="2" t="inlineStr">
         <is>
-          <t>Okaloosa County Jail - Delta Pod - Complete Shingle Re-Roof</t>
+          <t>Multifamily SHIP Application 2025 RFA</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -30447,12 +30447,12 @@
       <c r="I575" s="3" t="inlineStr"/>
       <c r="J575" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/myokaloosa/projects/312231</t>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/235838</t>
         </is>
       </c>
       <c r="K575" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/myokaloosa</t>
+          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L575" t="inlineStr">
@@ -30464,27 +30464,27 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Monroe</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>City of Orlando</t>
+          <t>Monroe County BOCC</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>#317746</t>
+          <t>#256340</t>
         </is>
       </c>
       <c r="D576" s="2" t="inlineStr">
         <is>
-          <t>Lift Station No. 85 Replacement</t>
+          <t>Professional Architectural and Engineering Continuing Services</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -30497,12 +30497,12 @@
       <c r="I576" s="3" t="inlineStr"/>
       <c r="J576" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/orlando/projects/317746</t>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/256340</t>
         </is>
       </c>
       <c r="K576" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/orlando</t>
+          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L576" t="inlineStr">
@@ -30514,27 +30514,27 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Monroe</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Greater Orlando Aviation Authority</t>
+          <t>Monroe County BOCC</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>#292755</t>
+          <t>#255496</t>
         </is>
       </c>
       <c r="D577" s="2" t="inlineStr">
         <is>
-          <t>Project Management Information System (PMIS)</t>
+          <t>Professional Surveying Continuing Services</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Engineering &amp; Architecture</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -30547,12 +30547,12 @@
       <c r="I577" s="3" t="inlineStr"/>
       <c r="J577" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/goaa/projects/292755</t>
+          <t>https://monroecounty-fl.bonfirehub.com/opportunities/255496</t>
         </is>
       </c>
       <c r="K577" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/goaa</t>
+          <t>https://monroecounty-fl.bonfirehub.com/portal/?tab=openOpportunities</t>
         </is>
       </c>
       <c r="L577" t="inlineStr">
@@ -30564,27 +30564,27 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Pinellas</t>
+          <t>Okaloosa</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Pinellas County Schools</t>
+          <t>Okaloosa County BOCC</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>#319367</t>
+          <t>#315955</t>
         </is>
       </c>
       <c r="D578" s="2" t="inlineStr">
         <is>
-          <t>First Aid Suplies</t>
+          <t>Covered Walkway Phase 2</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -30597,12 +30597,12 @@
       <c r="I578" s="3" t="inlineStr"/>
       <c r="J578" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/pcsb/projects/319367</t>
+          <t>https://procurement.opengov.com/portal/myokaloosa/projects/315955</t>
         </is>
       </c>
       <c r="K578" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/pcsb</t>
+          <t>https://procurement.opengov.com/portal/myokaloosa</t>
         </is>
       </c>
       <c r="L578" t="inlineStr">
@@ -30614,27 +30614,27 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Pinellas</t>
+          <t>Okaloosa</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>City of Clearwater</t>
+          <t>Okaloosa County BOCC</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>#320122</t>
+          <t>#312231</t>
         </is>
       </c>
       <c r="D579" s="2" t="inlineStr">
         <is>
-          <t>Fleet Maintenance Facility Spray Foam Insulation Replacement</t>
+          <t>Okaloosa County Jail - Delta Pod - Complete Shingle Re-Roof</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -30647,12 +30647,12 @@
       <c r="I579" s="3" t="inlineStr"/>
       <c r="J579" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/myclearwater/projects/320122</t>
+          <t>https://procurement.opengov.com/portal/myokaloosa/projects/312231</t>
         </is>
       </c>
       <c r="K579" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/myclearwater</t>
+          <t>https://procurement.opengov.com/portal/myokaloosa</t>
         </is>
       </c>
       <c r="L579" t="inlineStr">
@@ -30664,22 +30664,22 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Pinellas</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Pinellas County Schools</t>
+          <t>City of Orlando</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>#314736</t>
+          <t>#317746</t>
         </is>
       </c>
       <c r="D580" s="2" t="inlineStr">
         <is>
-          <t>Pool Demolition</t>
+          <t>Lift Station No. 85 Replacement</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
@@ -30697,12 +30697,12 @@
       <c r="I580" s="3" t="inlineStr"/>
       <c r="J580" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/pcsb/projects/314736</t>
+          <t>https://procurement.opengov.com/portal/orlando/projects/317746</t>
         </is>
       </c>
       <c r="K580" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/pcsb</t>
+          <t>https://procurement.opengov.com/portal/orlando</t>
         </is>
       </c>
       <c r="L580" t="inlineStr">
@@ -30714,27 +30714,27 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Pinellas</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>City of St. Petersburg</t>
+          <t>Greater Orlando Aviation Authority</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>#314465</t>
+          <t>#292755</t>
         </is>
       </c>
       <c r="D581" s="2" t="inlineStr">
         <is>
-          <t>Skate Park Obstacle, Demolition/Replacement</t>
+          <t>Project Management Information System (PMIS)</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -30747,12 +30747,12 @@
       <c r="I581" s="3" t="inlineStr"/>
       <c r="J581" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/stpete/projects/314465</t>
+          <t>https://procurement.opengov.com/portal/goaa/projects/292755</t>
         </is>
       </c>
       <c r="K581" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/stpete</t>
+          <t>https://procurement.opengov.com/portal/goaa</t>
         </is>
       </c>
       <c r="L581" t="inlineStr">
@@ -30764,34 +30764,30 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Pinellas</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Pinellas County Schools</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>RFP 26-345</t>
+          <t>#319367</t>
         </is>
       </c>
       <c r="D582" s="2" t="inlineStr">
         <is>
-          <t>Advertising &amp; Marketing Services for Visit Central Florida</t>
+          <t>First Aid Suplies</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
-        </is>
-      </c>
-      <c r="F582" t="inlineStr">
-        <is>
-          <t>RFP</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr"/>
       <c r="G582" t="inlineStr">
         <is>
           <t>Open</t>
@@ -30801,35 +30797,39 @@
       <c r="I582" s="3" t="inlineStr"/>
       <c r="J582" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-345/</t>
+          <t>https://procurement.opengov.com/portal/pcsb/projects/319367</t>
         </is>
       </c>
       <c r="K582" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L582" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/pcsb</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Pinellas</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>City of Clearwater</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>CS 25-396</t>
+          <t>#320122</t>
         </is>
       </c>
       <c r="D583" s="2" t="inlineStr">
         <is>
-          <t>Apparel Embroidery Services</t>
+          <t>Fleet Maintenance Facility Spray Foam Insulation Replacement</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -30847,35 +30847,39 @@
       <c r="I583" s="3" t="inlineStr"/>
       <c r="J583" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-25-396/</t>
+          <t>https://procurement.opengov.com/portal/myclearwater/projects/320122</t>
         </is>
       </c>
       <c r="K583" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L583" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/myclearwater</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Pinellas</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>Pinellas County Schools</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>CS 25-230</t>
+          <t>#314736</t>
         </is>
       </c>
       <c r="D584" s="2" t="inlineStr">
         <is>
-          <t>Asphalt</t>
+          <t>Pool Demolition</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -30893,40 +30897,44 @@
       <c r="I584" s="3" t="inlineStr"/>
       <c r="J584" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-25-230/</t>
+          <t>https://procurement.opengov.com/portal/pcsb/projects/314736</t>
         </is>
       </c>
       <c r="K584" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L584" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/pcsb</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>Polk</t>
+          <t>Pinellas</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>City of St. Petersburg</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>CS 24-330</t>
+          <t>#314465</t>
         </is>
       </c>
       <c r="D585" s="2" t="inlineStr">
         <is>
-          <t>Body Shop Services</t>
+          <t>Skate Park Obstacle, Demolition/Replacement</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -30939,15 +30947,19 @@
       <c r="I585" s="3" t="inlineStr"/>
       <c r="J585" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-24-330/</t>
+          <t>https://procurement.opengov.com/portal/stpete/projects/314465</t>
         </is>
       </c>
       <c r="K585" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L585" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/stpete</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -30962,17 +30974,17 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>RFP 26-068</t>
+          <t>RFP 26-345</t>
         </is>
       </c>
       <c r="D586" s="2" t="inlineStr">
         <is>
-          <t>CMAR - Polk County Utilities Northeast Regional Warehouse/Operations Building and Fleet Campus</t>
+          <t>Advertising &amp; Marketing Services for Visit Central Florida</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
       <c r="F586" t="inlineStr">
@@ -30989,7 +31001,7 @@
       <c r="I586" s="3" t="inlineStr"/>
       <c r="J586" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-068/</t>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-345/</t>
         </is>
       </c>
       <c r="K586" s="4" t="inlineStr">
@@ -31012,12 +31024,12 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>CS 25-456</t>
+          <t>CS 25-396</t>
         </is>
       </c>
       <c r="D587" s="2" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Herbicides for Aquatic Weeds and Environmental Lands</t>
+          <t>Apparel Embroidery Services</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -31035,7 +31047,7 @@
       <c r="I587" s="3" t="inlineStr"/>
       <c r="J587" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-25-456/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-25-396/</t>
         </is>
       </c>
       <c r="K587" s="4" t="inlineStr">
@@ -31058,17 +31070,17 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>CS 22-365</t>
+          <t>CS 25-230</t>
         </is>
       </c>
       <c r="D588" s="2" t="inlineStr">
         <is>
-          <t>Code Enforcement Towing</t>
+          <t>Asphalt</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -31081,7 +31093,7 @@
       <c r="I588" s="3" t="inlineStr"/>
       <c r="J588" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-22-365/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-25-230/</t>
         </is>
       </c>
       <c r="K588" s="4" t="inlineStr">
@@ -31104,17 +31116,17 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Bid 26-395</t>
+          <t>CS 24-330</t>
         </is>
       </c>
       <c r="D589" s="2" t="inlineStr">
         <is>
-          <t>Communication Amplifier Systems</t>
+          <t>Body Shop Services</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>IT &amp; Technology</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -31127,7 +31139,7 @@
       <c r="I589" s="3" t="inlineStr"/>
       <c r="J589" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-395/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-24-330/</t>
         </is>
       </c>
       <c r="K589" s="4" t="inlineStr">
@@ -31150,20 +31162,24 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>CS 24-507</t>
+          <t>RFP 26-068</t>
         </is>
       </c>
       <c r="D590" s="2" t="inlineStr">
         <is>
-          <t>Cremation Services</t>
+          <t>CMAR - Polk County Utilities Northeast Regional Warehouse/Operations Building and Fleet Campus</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
-        </is>
-      </c>
-      <c r="F590" t="inlineStr"/>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>RFP</t>
+        </is>
+      </c>
       <c r="G590" t="inlineStr">
         <is>
           <t>Open</t>
@@ -31173,7 +31189,7 @@
       <c r="I590" s="3" t="inlineStr"/>
       <c r="J590" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-24-507/</t>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-068/</t>
         </is>
       </c>
       <c r="K590" s="4" t="inlineStr">
@@ -31196,17 +31212,17 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>ISS 26-065</t>
+          <t>CS 25-456</t>
         </is>
       </c>
       <c r="D591" s="2" t="inlineStr">
         <is>
-          <t>Digital Information Kiosks &amp; System</t>
+          <t>Chemicals &amp; Herbicides for Aquatic Weeds and Environmental Lands</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>IT &amp; Technology</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -31219,7 +31235,7 @@
       <c r="I591" s="3" t="inlineStr"/>
       <c r="J591" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/iss-26-065/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-25-456/</t>
         </is>
       </c>
       <c r="K591" s="4" t="inlineStr">
@@ -31242,24 +31258,20 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>RFP 26-320</t>
+          <t>CS 22-365</t>
         </is>
       </c>
       <c r="D592" s="2" t="inlineStr">
         <is>
-          <t>Engineering Services for Water Infrastructure Repair &amp; Water Quality Improvement Solutions for the Lakeland to Bartow Lake Watershed</t>
+          <t>Code Enforcement Towing</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
-        </is>
-      </c>
-      <c r="F592" t="inlineStr">
-        <is>
-          <t>RFP</t>
-        </is>
-      </c>
+          <t>Consulting &amp; Professional Services</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr"/>
       <c r="G592" t="inlineStr">
         <is>
           <t>Open</t>
@@ -31269,7 +31281,7 @@
       <c r="I592" s="3" t="inlineStr"/>
       <c r="J592" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-320/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-22-365/</t>
         </is>
       </c>
       <c r="K592" s="4" t="inlineStr">
@@ -31292,17 +31304,17 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>CS 13-294</t>
+          <t>Bid 26-395</t>
         </is>
       </c>
       <c r="D593" s="2" t="inlineStr">
         <is>
-          <t>Environmental Lands Site Caretaker</t>
+          <t>Communication Amplifier Systems</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F593" t="inlineStr"/>
@@ -31315,7 +31327,7 @@
       <c r="I593" s="3" t="inlineStr"/>
       <c r="J593" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-13-294/</t>
+          <t>https://www.polkfl.gov/bid-form/bid-26-395/</t>
         </is>
       </c>
       <c r="K593" s="4" t="inlineStr">
@@ -31338,12 +31350,12 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>RFP 26-370</t>
+          <t>CS 24-507</t>
         </is>
       </c>
       <c r="D594" s="2" t="inlineStr">
         <is>
-          <t>Grant Administration for Community Development Block Grant (CDBG) Disaster Recovery (DR) Infrastructure Repair Program</t>
+          <t>Cremation Services</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -31351,11 +31363,7 @@
           <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
-      <c r="F594" t="inlineStr">
-        <is>
-          <t>RFP</t>
-        </is>
-      </c>
+      <c r="F594" t="inlineStr"/>
       <c r="G594" t="inlineStr">
         <is>
           <t>Open</t>
@@ -31365,7 +31373,7 @@
       <c r="I594" s="3" t="inlineStr"/>
       <c r="J594" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-370/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-24-507/</t>
         </is>
       </c>
       <c r="K594" s="4" t="inlineStr">
@@ -31388,17 +31396,17 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Bid 26-229</t>
+          <t>ISS 26-065</t>
         </is>
       </c>
       <c r="D595" s="2" t="inlineStr">
         <is>
-          <t>Ground Maintenance – Countywide – Zones 1 through 8</t>
+          <t>Digital Information Kiosks &amp; System</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>IT &amp; Technology</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -31411,7 +31419,7 @@
       <c r="I595" s="3" t="inlineStr"/>
       <c r="J595" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-229/</t>
+          <t>https://www.polkfl.gov/bid-form/iss-26-065/</t>
         </is>
       </c>
       <c r="K595" s="4" t="inlineStr">
@@ -31434,20 +31442,24 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>CS 20-667</t>
+          <t>RFP 26-320</t>
         </is>
       </c>
       <c r="D596" s="2" t="inlineStr">
         <is>
-          <t>Heavy Equipment and Tool Rentals</t>
+          <t>Engineering Services for Water Infrastructure Repair &amp; Water Quality Improvement Solutions for the Lakeland to Bartow Lake Watershed</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
-        </is>
-      </c>
-      <c r="F596" t="inlineStr"/>
+          <t>Engineering &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>RFP</t>
+        </is>
+      </c>
       <c r="G596" t="inlineStr">
         <is>
           <t>Open</t>
@@ -31457,7 +31469,7 @@
       <c r="I596" s="3" t="inlineStr"/>
       <c r="J596" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-20-667/</t>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-320/</t>
         </is>
       </c>
       <c r="K596" s="4" t="inlineStr">
@@ -31475,22 +31487,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>City of Lakeland</t>
+          <t>Polk County BOCC</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>#320250</t>
+          <t>CS 13-294</t>
         </is>
       </c>
       <c r="D597" s="2" t="inlineStr">
         <is>
-          <t>Identity and Access Management (IAM) Solution</t>
+          <t>Environmental Lands Site Caretaker</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -31503,19 +31515,15 @@
       <c r="I597" s="3" t="inlineStr"/>
       <c r="J597" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/lakelandgov/projects/320250</t>
+          <t>https://www.polkfl.gov/bid-form/cs-13-294/</t>
         </is>
       </c>
       <c r="K597" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/lakelandgov</t>
-        </is>
-      </c>
-      <c r="L597" t="inlineStr">
-        <is>
-          <t>From the agency's email alert.</t>
-        </is>
-      </c>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -31530,20 +31538,24 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>CS 20-1111</t>
+          <t>RFP 26-370</t>
         </is>
       </c>
       <c r="D598" s="2" t="inlineStr">
         <is>
-          <t>Janitorial Supplies</t>
+          <t>Grant Administration for Community Development Block Grant (CDBG) Disaster Recovery (DR) Infrastructure Repair Program</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="F598" t="inlineStr"/>
+          <t>Consulting &amp; Professional Services</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>RFP</t>
+        </is>
+      </c>
       <c r="G598" t="inlineStr">
         <is>
           <t>Open</t>
@@ -31553,7 +31565,7 @@
       <c r="I598" s="3" t="inlineStr"/>
       <c r="J598" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-20-1111/</t>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-370/</t>
         </is>
       </c>
       <c r="K598" s="4" t="inlineStr">
@@ -31576,17 +31588,17 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>CS 20-633</t>
+          <t>Bid 26-229</t>
         </is>
       </c>
       <c r="D599" s="2" t="inlineStr">
         <is>
-          <t>Litter Pickup</t>
+          <t>Ground Maintenance – Countywide – Zones 1 through 8</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -31599,7 +31611,7 @@
       <c r="I599" s="3" t="inlineStr"/>
       <c r="J599" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-20-633/</t>
+          <t>https://www.polkfl.gov/bid-form/bid-26-229/</t>
         </is>
       </c>
       <c r="K599" s="4" t="inlineStr">
@@ -31622,17 +31634,17 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>CQ 26-214</t>
+          <t>CS 20-667</t>
         </is>
       </c>
       <c r="D600" s="2" t="inlineStr">
         <is>
-          <t>Loyce Harpe Basketball Court and Sidewalks</t>
+          <t>Heavy Equipment and Tool Rentals</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -31645,7 +31657,7 @@
       <c r="I600" s="3" t="inlineStr"/>
       <c r="J600" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cq-26-214/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-20-667/</t>
         </is>
       </c>
       <c r="K600" s="4" t="inlineStr">
@@ -31663,22 +31675,22 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Polk County BOCC</t>
+          <t>City of Lakeland</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>CS 26-296</t>
+          <t>#320250</t>
         </is>
       </c>
       <c r="D601" s="2" t="inlineStr">
         <is>
-          <t>MUTCD Regulatory &amp; Warning Signs</t>
+          <t>Identity and Access Management (IAM) Solution</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
@@ -31691,15 +31703,19 @@
       <c r="I601" s="3" t="inlineStr"/>
       <c r="J601" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-26-296/</t>
+          <t>https://procurement.opengov.com/portal/lakelandgov/projects/320250</t>
         </is>
       </c>
       <c r="K601" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/business/procurement/</t>
-        </is>
-      </c>
-      <c r="L601" t="inlineStr"/>
+          <t>https://procurement.opengov.com/portal/lakelandgov</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -31714,24 +31730,20 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>RFP 26-352</t>
+          <t>CS 20-1111</t>
         </is>
       </c>
       <c r="D602" s="2" t="inlineStr">
         <is>
-          <t>Masterpiece Cattle Lease</t>
+          <t>Janitorial Supplies</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F602" t="inlineStr">
-        <is>
-          <t>RFP</t>
-        </is>
-      </c>
+          <t>Facilities &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr"/>
       <c r="G602" t="inlineStr">
         <is>
           <t>Open</t>
@@ -31741,7 +31753,7 @@
       <c r="I602" s="3" t="inlineStr"/>
       <c r="J602" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-352/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-20-1111/</t>
         </is>
       </c>
       <c r="K602" s="4" t="inlineStr">
@@ -31764,17 +31776,17 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Bid 26-367</t>
+          <t>CS 20-633</t>
         </is>
       </c>
       <c r="D603" s="2" t="inlineStr">
         <is>
-          <t>Mowing &amp; Maintenance for Utilities – North Region</t>
+          <t>Litter Pickup</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -31787,7 +31799,7 @@
       <c r="I603" s="3" t="inlineStr"/>
       <c r="J603" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-367/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-20-633/</t>
         </is>
       </c>
       <c r="K603" s="4" t="inlineStr">
@@ -31810,17 +31822,17 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Bid 26-350</t>
+          <t>CQ 26-214</t>
         </is>
       </c>
       <c r="D604" s="2" t="inlineStr">
         <is>
-          <t>Mowing and Maintenance for Solid Waste</t>
+          <t>Loyce Harpe Basketball Court and Sidewalks</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -31833,7 +31845,7 @@
       <c r="I604" s="3" t="inlineStr"/>
       <c r="J604" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-350/</t>
+          <t>https://www.polkfl.gov/bid-form/cq-26-214/</t>
         </is>
       </c>
       <c r="K604" s="4" t="inlineStr">
@@ -31856,17 +31868,17 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Bid 26-295</t>
+          <t>CS 26-296</t>
         </is>
       </c>
       <c r="D605" s="2" t="inlineStr">
         <is>
-          <t>Onsite Clinic Services</t>
+          <t>MUTCD Regulatory &amp; Warning Signs</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
@@ -31879,7 +31891,7 @@
       <c r="I605" s="3" t="inlineStr"/>
       <c r="J605" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-295/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-26-296/</t>
         </is>
       </c>
       <c r="K605" s="4" t="inlineStr">
@@ -31902,20 +31914,24 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>CS 24-194</t>
+          <t>RFP 26-352</t>
         </is>
       </c>
       <c r="D606" s="2" t="inlineStr">
         <is>
-          <t>Overgrowth and Large Lot Clearing</t>
+          <t>Masterpiece Cattle Lease</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="F606" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>RFP</t>
+        </is>
+      </c>
       <c r="G606" t="inlineStr">
         <is>
           <t>Open</t>
@@ -31925,7 +31941,7 @@
       <c r="I606" s="3" t="inlineStr"/>
       <c r="J606" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-24-194/</t>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-352/</t>
         </is>
       </c>
       <c r="K606" s="4" t="inlineStr">
@@ -31948,12 +31964,12 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>CS 24-195</t>
+          <t>Bid 26-367</t>
         </is>
       </c>
       <c r="D607" s="2" t="inlineStr">
         <is>
-          <t>Overgrowth and Small Lot Clearing</t>
+          <t>Mowing &amp; Maintenance for Utilities – North Region</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -31971,7 +31987,7 @@
       <c r="I607" s="3" t="inlineStr"/>
       <c r="J607" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-24-195/</t>
+          <t>https://www.polkfl.gov/bid-form/bid-26-367/</t>
         </is>
       </c>
       <c r="K607" s="4" t="inlineStr">
@@ -31994,17 +32010,17 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>CQ 26-343</t>
+          <t>Bid 26-350</t>
         </is>
       </c>
       <c r="D608" s="2" t="inlineStr">
         <is>
-          <t>PCU Administration Building – Conference Room Remodel.</t>
+          <t>Mowing and Maintenance for Solid Waste</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -32017,7 +32033,7 @@
       <c r="I608" s="3" t="inlineStr"/>
       <c r="J608" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cq-26-343/</t>
+          <t>https://www.polkfl.gov/bid-form/bid-26-350/</t>
         </is>
       </c>
       <c r="K608" s="4" t="inlineStr">
@@ -32040,12 +32056,12 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>CS 09-007</t>
+          <t>Bid 26-295</t>
         </is>
       </c>
       <c r="D609" s="2" t="inlineStr">
         <is>
-          <t>Park Service Residents</t>
+          <t>Onsite Clinic Services</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
@@ -32063,7 +32079,7 @@
       <c r="I609" s="3" t="inlineStr"/>
       <c r="J609" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-09-007/</t>
+          <t>https://www.polkfl.gov/bid-form/bid-26-295/</t>
         </is>
       </c>
       <c r="K609" s="4" t="inlineStr">
@@ -32086,17 +32102,17 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>CS 18-824</t>
+          <t>CS 24-194</t>
         </is>
       </c>
       <c r="D610" s="2" t="inlineStr">
         <is>
-          <t>Pharmaceuticals for Fire Rescue</t>
+          <t>Overgrowth and Large Lot Clearing</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -32109,7 +32125,7 @@
       <c r="I610" s="3" t="inlineStr"/>
       <c r="J610" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-18-824/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-24-194/</t>
         </is>
       </c>
       <c r="K610" s="4" t="inlineStr">
@@ -32132,17 +32148,17 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>CS 25-303</t>
+          <t>CS 24-195</t>
         </is>
       </c>
       <c r="D611" s="2" t="inlineStr">
         <is>
-          <t>Plumbing Equipment, Fixtures, and Supplies</t>
+          <t>Overgrowth and Small Lot Clearing</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -32155,7 +32171,7 @@
       <c r="I611" s="3" t="inlineStr"/>
       <c r="J611" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-25-303/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-24-195/</t>
         </is>
       </c>
       <c r="K611" s="4" t="inlineStr">
@@ -32178,17 +32194,17 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Bid 26-349</t>
+          <t>CQ 26-343</t>
         </is>
       </c>
       <c r="D612" s="2" t="inlineStr">
         <is>
-          <t>Pond Mowing and Maintenance – Roads and Drainage</t>
+          <t>PCU Administration Building – Conference Room Remodel.</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F612" t="inlineStr"/>
@@ -32201,7 +32217,7 @@
       <c r="I612" s="3" t="inlineStr"/>
       <c r="J612" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-349/</t>
+          <t>https://www.polkfl.gov/bid-form/cq-26-343/</t>
         </is>
       </c>
       <c r="K612" s="4" t="inlineStr">
@@ -32224,24 +32240,20 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>RFP 26-387</t>
+          <t>CS 09-007</t>
         </is>
       </c>
       <c r="D613" s="2" t="inlineStr">
         <is>
-          <t>Professional Survey &amp; Mapping Services (CCNA)</t>
+          <t>Park Service Residents</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
-        </is>
-      </c>
-      <c r="F613" t="inlineStr">
-        <is>
-          <t>RFQ (qualifications)</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr"/>
       <c r="G613" t="inlineStr">
         <is>
           <t>Open</t>
@@ -32251,7 +32263,7 @@
       <c r="I613" s="3" t="inlineStr"/>
       <c r="J613" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-387/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-09-007/</t>
         </is>
       </c>
       <c r="K613" s="4" t="inlineStr">
@@ -32274,12 +32286,12 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>CS 26-059</t>
+          <t>CS 18-824</t>
         </is>
       </c>
       <c r="D614" s="2" t="inlineStr">
         <is>
-          <t>Protective Footwear for Employees</t>
+          <t>Pharmaceuticals for Fire Rescue</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
@@ -32297,7 +32309,7 @@
       <c r="I614" s="3" t="inlineStr"/>
       <c r="J614" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-26-059/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-18-824/</t>
         </is>
       </c>
       <c r="K614" s="4" t="inlineStr">
@@ -32320,17 +32332,17 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>CS 17-633</t>
+          <t>CS 25-303</t>
         </is>
       </c>
       <c r="D615" s="2" t="inlineStr">
         <is>
-          <t>Radiology Services</t>
+          <t>Plumbing Equipment, Fixtures, and Supplies</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>Consulting &amp; Professional Services</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -32343,7 +32355,7 @@
       <c r="I615" s="3" t="inlineStr"/>
       <c r="J615" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-17-633/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-25-303/</t>
         </is>
       </c>
       <c r="K615" s="4" t="inlineStr">
@@ -32366,12 +32378,12 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Bid 26-372</t>
+          <t>Bid 26-349</t>
         </is>
       </c>
       <c r="D616" s="2" t="inlineStr">
         <is>
-          <t>Saddle Creek New Office and Maintenance Buildings</t>
+          <t>Pond Mowing and Maintenance – Roads and Drainage</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
@@ -32389,7 +32401,7 @@
       <c r="I616" s="3" t="inlineStr"/>
       <c r="J616" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-372/</t>
+          <t>https://www.polkfl.gov/bid-form/bid-26-349/</t>
         </is>
       </c>
       <c r="K616" s="4" t="inlineStr">
@@ -32412,20 +32424,24 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>CS 25-463</t>
+          <t>RFP 26-387</t>
         </is>
       </c>
       <c r="D617" s="2" t="inlineStr">
         <is>
-          <t>Safety Products and Equipment</t>
+          <t>Professional Survey &amp; Mapping Services (CCNA)</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
-        </is>
-      </c>
-      <c r="F617" t="inlineStr"/>
+          <t>Engineering &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>RFQ (qualifications)</t>
+        </is>
+      </c>
       <c r="G617" t="inlineStr">
         <is>
           <t>Open</t>
@@ -32435,7 +32451,7 @@
       <c r="I617" s="3" t="inlineStr"/>
       <c r="J617" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-25-463/</t>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-387/</t>
         </is>
       </c>
       <c r="K617" s="4" t="inlineStr">
@@ -32458,17 +32474,17 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>CS 19-642</t>
+          <t>CS 26-059</t>
         </is>
       </c>
       <c r="D618" s="2" t="inlineStr">
         <is>
-          <t>Securing of Structures</t>
+          <t>Protective Footwear for Employees</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -32481,7 +32497,7 @@
       <c r="I618" s="3" t="inlineStr"/>
       <c r="J618" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-19-642/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-26-059/</t>
         </is>
       </c>
       <c r="K618" s="4" t="inlineStr">
@@ -32504,17 +32520,17 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>CS 25-475</t>
+          <t>CS 17-633</t>
         </is>
       </c>
       <c r="D619" s="2" t="inlineStr">
         <is>
-          <t>Sherwin Williams Paint and Supplies</t>
+          <t>Radiology Services</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Consulting &amp; Professional Services</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -32527,7 +32543,7 @@
       <c r="I619" s="3" t="inlineStr"/>
       <c r="J619" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-25-475/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-17-633/</t>
         </is>
       </c>
       <c r="K619" s="4" t="inlineStr">
@@ -32550,12 +32566,12 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>CS 26-238</t>
+          <t>Bid 26-372</t>
         </is>
       </c>
       <c r="D620" s="2" t="inlineStr">
         <is>
-          <t>Sign Removal from Rights-of-Way</t>
+          <t>Saddle Creek New Office and Maintenance Buildings</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
@@ -32573,7 +32589,7 @@
       <c r="I620" s="3" t="inlineStr"/>
       <c r="J620" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-26-238/</t>
+          <t>https://www.polkfl.gov/bid-form/bid-26-372/</t>
         </is>
       </c>
       <c r="K620" s="4" t="inlineStr">
@@ -32596,24 +32612,20 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>RFP 26-384</t>
+          <t>CS 25-463</t>
         </is>
       </c>
       <c r="D621" s="2" t="inlineStr">
         <is>
-          <t>TPA for Off-Site Inmate Medical and Pharmacy Services</t>
+          <t>Safety Products and Equipment</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F621" t="inlineStr">
-        <is>
-          <t>RFP</t>
-        </is>
-      </c>
+          <t>Goods &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr"/>
       <c r="G621" t="inlineStr">
         <is>
           <t>Open</t>
@@ -32623,7 +32635,7 @@
       <c r="I621" s="3" t="inlineStr"/>
       <c r="J621" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/rfp-26-384/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-25-463/</t>
         </is>
       </c>
       <c r="K621" s="4" t="inlineStr">
@@ -32646,17 +32658,17 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>CS 24-022</t>
+          <t>CS 19-642</t>
         </is>
       </c>
       <c r="D622" s="2" t="inlineStr">
         <is>
-          <t>Towing Services for Polk County</t>
+          <t>Securing of Structures</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F622" t="inlineStr"/>
@@ -32669,7 +32681,7 @@
       <c r="I622" s="3" t="inlineStr"/>
       <c r="J622" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-24-022/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-19-642/</t>
         </is>
       </c>
       <c r="K622" s="4" t="inlineStr">
@@ -32692,17 +32704,17 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Bid 26-412</t>
+          <t>CS 25-475</t>
         </is>
       </c>
       <c r="D623" s="2" t="inlineStr">
         <is>
-          <t>Vacuum Truck Cleaning Services for Underground Stormwater Baffle Boxes</t>
+          <t>Sherwin Williams Paint and Supplies</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>Facilities &amp; Maintenance</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -32715,7 +32727,7 @@
       <c r="I623" s="3" t="inlineStr"/>
       <c r="J623" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/bid-26-412/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-25-475/</t>
         </is>
       </c>
       <c r="K623" s="4" t="inlineStr">
@@ -32738,17 +32750,17 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>CS 21-380</t>
+          <t>CS 26-238</t>
         </is>
       </c>
       <c r="D624" s="2" t="inlineStr">
         <is>
-          <t>Various Medical Related Supplies</t>
+          <t>Sign Removal from Rights-of-Way</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>Goods &amp; Supplies</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -32761,7 +32773,7 @@
       <c r="I624" s="3" t="inlineStr"/>
       <c r="J624" s="4" t="inlineStr">
         <is>
-          <t>https://www.polkfl.gov/bid-form/cs-21-380/</t>
+          <t>https://www.polkfl.gov/bid-form/cs-26-238/</t>
         </is>
       </c>
       <c r="K624" s="4" t="inlineStr">
@@ -32774,32 +32786,32 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>Putnam</t>
+          <t>Polk</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Putnam County School District</t>
+          <t>Polk County BOCC</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>#319082</t>
+          <t>RFP 26-384</t>
         </is>
       </c>
       <c r="D625" s="2" t="inlineStr">
         <is>
-          <t>Invitation to Bid (ITB): NEFEC Roofing and Building Envelope Services</t>
+          <t>TPA for Off-Site Inmate Medical and Pharmacy Services</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>RFP</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
@@ -32811,44 +32823,40 @@
       <c r="I625" s="3" t="inlineStr"/>
       <c r="J625" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/myputnamschools/projects/319082</t>
+          <t>https://www.polkfl.gov/bid-form/rfp-26-384/</t>
         </is>
       </c>
       <c r="K625" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/myputnamschools</t>
-        </is>
-      </c>
-      <c r="L625" t="inlineStr">
-        <is>
-          <t>From the agency's email alert.</t>
-        </is>
-      </c>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>Sarasota</t>
+          <t>Polk</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Sarasota County BOCC</t>
+          <t>Polk County BOCC</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>#320036</t>
+          <t>CS 24-022</t>
         </is>
       </c>
       <c r="D626" s="2" t="inlineStr">
         <is>
-          <t>KBI FLEXI-PAVE</t>
+          <t>Towing Services for Polk County</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F626" t="inlineStr"/>
@@ -32861,44 +32869,40 @@
       <c r="I626" s="3" t="inlineStr"/>
       <c r="J626" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/scgov/projects/320036</t>
+          <t>https://www.polkfl.gov/bid-form/cs-24-022/</t>
         </is>
       </c>
       <c r="K626" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/scgov</t>
-        </is>
-      </c>
-      <c r="L626" t="inlineStr">
-        <is>
-          <t>From the agency's email alert.</t>
-        </is>
-      </c>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>Sarasota</t>
+          <t>Polk</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Sarasota County BOCC</t>
+          <t>Polk County BOCC</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>#318555</t>
+          <t>Bid 26-412</t>
         </is>
       </c>
       <c r="D627" s="2" t="inlineStr">
         <is>
-          <t>Sarasota County Parking Lot Sweeping</t>
+          <t>Vacuum Truck Cleaning Services for Underground Stormwater Baffle Boxes</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Facilities &amp; Maintenance</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -32911,44 +32915,40 @@
       <c r="I627" s="3" t="inlineStr"/>
       <c r="J627" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/scgov/projects/318555</t>
+          <t>https://www.polkfl.gov/bid-form/bid-26-412/</t>
         </is>
       </c>
       <c r="K627" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/scgov</t>
-        </is>
-      </c>
-      <c r="L627" t="inlineStr">
-        <is>
-          <t>From the agency's email alert.</t>
-        </is>
-      </c>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>Sarasota</t>
+          <t>Polk</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Sarasota County BOCC</t>
+          <t>Polk County BOCC</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>#311618</t>
+          <t>CS 21-380</t>
         </is>
       </c>
       <c r="D628" s="2" t="inlineStr">
         <is>
-          <t>Self-Contained Interactive Touchscreen Learning Hub</t>
+          <t>Various Medical Related Supplies</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Goods &amp; Supplies</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -32961,47 +32961,47 @@
       <c r="I628" s="3" t="inlineStr"/>
       <c r="J628" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/scgov/projects/311618</t>
+          <t>https://www.polkfl.gov/bid-form/cs-21-380/</t>
         </is>
       </c>
       <c r="K628" s="4" t="inlineStr">
         <is>
-          <t>https://procurement.opengov.com/portal/scgov</t>
-        </is>
-      </c>
-      <c r="L628" t="inlineStr">
-        <is>
-          <t>From the agency's email alert.</t>
-        </is>
-      </c>
+          <t>https://www.polkfl.gov/business/procurement/</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>Volusia</t>
+          <t>Putnam</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Volusia County</t>
+          <t>Putnam County School District</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>#315986</t>
+          <t>#319082</t>
         </is>
       </c>
       <c r="D629" s="2" t="inlineStr">
         <is>
-          <t>Professional Solid Waste Management Engineering Services</t>
+          <t>Invitation to Bid (ITB): NEFEC Roofing and Building Envelope Services</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>Engineering &amp; Architecture</t>
-        </is>
-      </c>
-      <c r="F629" t="inlineStr"/>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>ITB</t>
+        </is>
+      </c>
       <c r="G629" t="inlineStr">
         <is>
           <t>Open</t>
@@ -33011,22 +33011,222 @@
       <c r="I629" s="3" t="inlineStr"/>
       <c r="J629" s="4" t="inlineStr">
         <is>
+          <t>https://procurement.opengov.com/portal/myputnamschools/projects/319082</t>
+        </is>
+      </c>
+      <c r="K629" s="4" t="inlineStr">
+        <is>
+          <t>https://procurement.opengov.com/portal/myputnamschools</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Sarasota</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Sarasota County BOCC</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>#320036</t>
+        </is>
+      </c>
+      <c r="D630" s="2" t="inlineStr">
+        <is>
+          <t>KBI FLEXI-PAVE</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr"/>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H630" s="5" t="inlineStr"/>
+      <c r="I630" s="3" t="inlineStr"/>
+      <c r="J630" s="4" t="inlineStr">
+        <is>
+          <t>https://procurement.opengov.com/portal/scgov/projects/320036</t>
+        </is>
+      </c>
+      <c r="K630" s="4" t="inlineStr">
+        <is>
+          <t>https://procurement.opengov.com/portal/scgov</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Sarasota</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Sarasota County BOCC</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>#318555</t>
+        </is>
+      </c>
+      <c r="D631" s="2" t="inlineStr">
+        <is>
+          <t>Sarasota County Parking Lot Sweeping</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr"/>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H631" s="5" t="inlineStr"/>
+      <c r="I631" s="3" t="inlineStr"/>
+      <c r="J631" s="4" t="inlineStr">
+        <is>
+          <t>https://procurement.opengov.com/portal/scgov/projects/318555</t>
+        </is>
+      </c>
+      <c r="K631" s="4" t="inlineStr">
+        <is>
+          <t>https://procurement.opengov.com/portal/scgov</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Sarasota</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Sarasota County BOCC</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>#311618</t>
+        </is>
+      </c>
+      <c r="D632" s="2" t="inlineStr">
+        <is>
+          <t>Self-Contained Interactive Touchscreen Learning Hub</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr"/>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H632" s="5" t="inlineStr"/>
+      <c r="I632" s="3" t="inlineStr"/>
+      <c r="J632" s="4" t="inlineStr">
+        <is>
+          <t>https://procurement.opengov.com/portal/scgov/projects/311618</t>
+        </is>
+      </c>
+      <c r="K632" s="4" t="inlineStr">
+        <is>
+          <t>https://procurement.opengov.com/portal/scgov</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>From the agency's email alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Volusia</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Volusia County</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>#315986</t>
+        </is>
+      </c>
+      <c r="D633" s="2" t="inlineStr">
+        <is>
+          <t>Professional Solid Waste Management Engineering Services</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr"/>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H633" s="5" t="inlineStr"/>
+      <c r="I633" s="3" t="inlineStr"/>
+      <c r="J633" s="4" t="inlineStr">
+        <is>
           <t>https://procurement.opengov.com/portal/volusia/projects/315986</t>
         </is>
       </c>
-      <c r="K629" s="4" t="inlineStr">
+      <c r="K633" s="4" t="inlineStr">
         <is>
           <t>https://procurement.opengov.com/portal/volusia</t>
         </is>
       </c>
-      <c r="L629" t="inlineStr">
+      <c r="L633" t="inlineStr">
         <is>
           <t>From the agency's email alert.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L629"/>
+  <autoFilter ref="A1:L633"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId2"/>
@@ -34262,6 +34462,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K628" r:id="rId1232"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J629" r:id="rId1233"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K629" r:id="rId1234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J630" r:id="rId1235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K630" r:id="rId1236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J631" r:id="rId1237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K631" r:id="rId1238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J632" r:id="rId1239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K632" r:id="rId1240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J633" r:id="rId1241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K633" r:id="rId1242"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34286,7 +34494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 2026-10-27 09:06 AM (Eastern time)</t>
+          <t>Updated 2026-10-27 09:23 AM (Eastern time)</t>
         </is>
       </c>
     </row>

--- a/site/data/florida-open-bids.xlsx
+++ b/site/data/florida-open-bids.xlsx
@@ -34494,7 +34494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 2026-10-27 09:23 AM (Eastern time)</t>
+          <t>Updated 2026-10-27 10:22 AM (Eastern time)</t>
         </is>
       </c>
     </row>
